--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -675,45 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128103821</v>
+        <v>128103715</v>
       </c>
       <c r="B2" t="n">
-        <v>98467</v>
+        <v>57672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626754</v>
+        <v>626715</v>
       </c>
       <c r="R2" t="n">
-        <v>7217270</v>
+        <v>7217390</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +754,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färsk</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128103750</v>
+        <v>128103712</v>
       </c>
       <c r="B3" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +796,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626688</v>
+        <v>626667</v>
       </c>
       <c r="R3" t="n">
-        <v>7217164</v>
+        <v>7217072</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,6 +864,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,7 +895,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128103748</v>
+        <v>128103750</v>
       </c>
       <c r="B4" t="n">
         <v>80132</v>
@@ -904,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626663</v>
+        <v>626688</v>
       </c>
       <c r="R4" t="n">
-        <v>7217050</v>
+        <v>7217164</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +992,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128103715</v>
+        <v>128103748</v>
       </c>
       <c r="B5" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,42 +1003,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626715</v>
+        <v>626663</v>
       </c>
       <c r="R5" t="n">
-        <v>7217390</v>
+        <v>7217050</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1045,11 +1063,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färsk</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,53 +1089,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128103712</v>
+        <v>128103821</v>
       </c>
       <c r="B6" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626667</v>
+        <v>626754</v>
       </c>
       <c r="R6" t="n">
-        <v>7217072</v>
+        <v>7217270</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1155,11 +1160,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Bohål</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1186,10 +1186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128103815</v>
+        <v>128103861</v>
       </c>
       <c r="B7" t="n">
-        <v>98467</v>
+        <v>91924</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1197,21 +1197,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1221,10 +1221,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626821</v>
+        <v>626733</v>
       </c>
       <c r="R7" t="n">
-        <v>7217074</v>
+        <v>7217284</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1259,12 +1259,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Bild</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1283,10 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128103861</v>
+        <v>128103815</v>
       </c>
       <c r="B8" t="n">
-        <v>91923</v>
+        <v>98468</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1294,21 +1300,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1318,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626733</v>
+        <v>626821</v>
       </c>
       <c r="R8" t="n">
-        <v>7217284</v>
+        <v>7217074</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1356,18 +1362,12 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Bild</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>128103803</v>
       </c>
       <c r="B9" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1774,10 +1774,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128103747</v>
+        <v>128103738</v>
       </c>
       <c r="B13" t="n">
-        <v>80132</v>
+        <v>80133</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1785,21 +1785,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626821</v>
+        <v>626739</v>
       </c>
       <c r="R13" t="n">
-        <v>7217089</v>
+        <v>7217280</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1871,32 +1871,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128103777</v>
+        <v>128103814</v>
       </c>
       <c r="B14" t="n">
-        <v>80168</v>
+        <v>98468</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626745</v>
+        <v>626811</v>
       </c>
       <c r="R14" t="n">
-        <v>7217253</v>
+        <v>7217114</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1968,32 +1968,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128103738</v>
+        <v>128103795</v>
       </c>
       <c r="B15" t="n">
-        <v>80133</v>
+        <v>98468</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626739</v>
+        <v>626797</v>
       </c>
       <c r="R15" t="n">
-        <v>7217280</v>
+        <v>7217132</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2065,32 +2065,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128103814</v>
+        <v>128103747</v>
       </c>
       <c r="B16" t="n">
-        <v>98467</v>
+        <v>80132</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626811</v>
+        <v>626821</v>
       </c>
       <c r="R16" t="n">
-        <v>7217114</v>
+        <v>7217089</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2162,32 +2162,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128103795</v>
+        <v>128103777</v>
       </c>
       <c r="B17" t="n">
-        <v>98467</v>
+        <v>80168</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626797</v>
+        <v>626745</v>
       </c>
       <c r="R17" t="n">
-        <v>7217132</v>
+        <v>7217253</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2372,7 +2372,7 @@
         <v>128103820</v>
       </c>
       <c r="B19" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>128103817</v>
       </c>
       <c r="B21" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>128103805</v>
       </c>
       <c r="B24" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3339,32 +3339,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128103873</v>
+        <v>128103862</v>
       </c>
       <c r="B29" t="n">
-        <v>78435</v>
+        <v>80167</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6437</v>
+        <v>6463</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3374,10 +3374,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>626652</v>
+        <v>626687</v>
       </c>
       <c r="R29" t="n">
-        <v>7217184</v>
+        <v>7217145</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3436,32 +3436,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128103862</v>
+        <v>128103873</v>
       </c>
       <c r="B30" t="n">
-        <v>80167</v>
+        <v>78435</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6463</v>
+        <v>6437</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>626687</v>
+        <v>626652</v>
       </c>
       <c r="R30" t="n">
-        <v>7217145</v>
+        <v>7217184</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3533,27 +3533,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128103846</v>
+        <v>128103865</v>
       </c>
       <c r="B31" t="n">
-        <v>79029</v>
+        <v>80167</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3568,10 +3568,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>626685</v>
+        <v>626739</v>
       </c>
       <c r="R31" t="n">
-        <v>7217148</v>
+        <v>7217280</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3630,27 +3630,27 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128103865</v>
+        <v>128103846</v>
       </c>
       <c r="B32" t="n">
-        <v>80167</v>
+        <v>79029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3665,10 +3665,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>626739</v>
+        <v>626685</v>
       </c>
       <c r="R32" t="n">
-        <v>7217280</v>
+        <v>7217148</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3840,7 +3840,7 @@
         <v>128103798</v>
       </c>
       <c r="B34" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         <v>128103799</v>
       </c>
       <c r="B35" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4031,10 +4031,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128103789</v>
+        <v>128103749</v>
       </c>
       <c r="B36" t="n">
-        <v>78787</v>
+        <v>80132</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4042,21 +4042,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4066,10 +4066,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>626633</v>
+        <v>626686</v>
       </c>
       <c r="R36" t="n">
-        <v>7217153</v>
+        <v>7217075</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4128,32 +4128,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128103800</v>
+        <v>128103789</v>
       </c>
       <c r="B37" t="n">
-        <v>98467</v>
+        <v>78787</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4163,10 +4163,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>626843</v>
+        <v>626633</v>
       </c>
       <c r="R37" t="n">
-        <v>7217062</v>
+        <v>7217153</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4225,10 +4225,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128103816</v>
+        <v>128103800</v>
       </c>
       <c r="B38" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4260,10 +4260,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626837</v>
+        <v>626843</v>
       </c>
       <c r="R38" t="n">
-        <v>7217076</v>
+        <v>7217062</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4322,32 +4322,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128103749</v>
+        <v>128103816</v>
       </c>
       <c r="B39" t="n">
-        <v>80132</v>
+        <v>98468</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4357,10 +4357,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626686</v>
+        <v>626837</v>
       </c>
       <c r="R39" t="n">
-        <v>7217075</v>
+        <v>7217076</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4626,32 +4626,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128103841</v>
+        <v>128103732</v>
       </c>
       <c r="B42" t="n">
-        <v>79029</v>
+        <v>98489</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4661,10 +4661,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>626739</v>
+        <v>626665</v>
       </c>
       <c r="R42" t="n">
-        <v>7217304</v>
+        <v>7217113</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4726,7 +4726,7 @@
         <v>128103804</v>
       </c>
       <c r="B43" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4820,53 +4820,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128103707</v>
+        <v>128103802</v>
       </c>
       <c r="B44" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>626786</v>
+        <v>626806</v>
       </c>
       <c r="R44" t="n">
-        <v>7217295</v>
+        <v>7217042</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4899,11 +4891,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4930,10 +4917,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128103708</v>
+        <v>128103841</v>
       </c>
       <c r="B45" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4941,42 +4928,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>626743</v>
+        <v>626739</v>
       </c>
       <c r="R45" t="n">
-        <v>7217219</v>
+        <v>7217304</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5009,11 +4988,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Bohål</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5142,45 +5116,53 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128103802</v>
+        <v>128103707</v>
       </c>
       <c r="B47" t="n">
-        <v>98467</v>
+        <v>57672</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>626806</v>
+        <v>626786</v>
       </c>
       <c r="R47" t="n">
-        <v>7217042</v>
+        <v>7217295</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5213,6 +5195,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5239,45 +5226,53 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128103732</v>
+        <v>128103708</v>
       </c>
       <c r="B48" t="n">
-        <v>98488</v>
+        <v>57672</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>626665</v>
+        <v>626743</v>
       </c>
       <c r="R48" t="n">
-        <v>7217113</v>
+        <v>7217219</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5310,6 +5305,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5627,32 +5627,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128103726</v>
+        <v>128103849</v>
       </c>
       <c r="B52" t="n">
-        <v>80161</v>
+        <v>79029</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5662,10 +5662,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>626745</v>
+        <v>626701</v>
       </c>
       <c r="R52" t="n">
-        <v>7217244</v>
+        <v>7217242</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5724,10 +5724,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128103849</v>
+        <v>128103713</v>
       </c>
       <c r="B53" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5735,34 +5735,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>626701</v>
+        <v>626703</v>
       </c>
       <c r="R53" t="n">
-        <v>7217242</v>
+        <v>7217299</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5795,6 +5803,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5821,53 +5834,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128103713</v>
+        <v>128103796</v>
       </c>
       <c r="B54" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>626703</v>
+        <v>626803</v>
       </c>
       <c r="R54" t="n">
-        <v>7217299</v>
+        <v>7217099</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5900,11 +5905,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5931,10 +5931,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128103796</v>
+        <v>128103797</v>
       </c>
       <c r="B55" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5966,10 +5966,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>626803</v>
+        <v>626820</v>
       </c>
       <c r="R55" t="n">
-        <v>7217099</v>
+        <v>7217037</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6028,32 +6028,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128103855</v>
+        <v>128103726</v>
       </c>
       <c r="B56" t="n">
-        <v>82870</v>
+        <v>80161</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6063,10 +6063,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>626723</v>
+        <v>626745</v>
       </c>
       <c r="R56" t="n">
-        <v>7217326</v>
+        <v>7217244</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6125,32 +6125,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128103797</v>
+        <v>128103779</v>
       </c>
       <c r="B57" t="n">
-        <v>98467</v>
+        <v>80168</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6160,10 +6160,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>626820</v>
+        <v>626819</v>
       </c>
       <c r="R57" t="n">
-        <v>7217037</v>
+        <v>7217095</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6222,32 +6222,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128103779</v>
+        <v>128103855</v>
       </c>
       <c r="B58" t="n">
-        <v>80168</v>
+        <v>82870</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>626819</v>
+        <v>626723</v>
       </c>
       <c r="R58" t="n">
-        <v>7217095</v>
+        <v>7217326</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6322,7 +6322,7 @@
         <v>128103818</v>
       </c>
       <c r="B59" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128103715</v>
+        <v>128103821</v>
       </c>
       <c r="B2" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626715</v>
+        <v>626754</v>
       </c>
       <c r="R2" t="n">
-        <v>7217390</v>
+        <v>7217270</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färsk</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128103712</v>
+        <v>128103750</v>
       </c>
       <c r="B3" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,42 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626667</v>
+        <v>626688</v>
       </c>
       <c r="R3" t="n">
-        <v>7217072</v>
+        <v>7217164</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Bohål</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128103750</v>
+        <v>128103748</v>
       </c>
       <c r="B4" t="n">
         <v>80132</v>
@@ -930,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626688</v>
+        <v>626663</v>
       </c>
       <c r="R4" t="n">
-        <v>7217164</v>
+        <v>7217050</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128103748</v>
+        <v>128103715</v>
       </c>
       <c r="B5" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1003,34 +977,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626663</v>
+        <v>626715</v>
       </c>
       <c r="R5" t="n">
-        <v>7217050</v>
+        <v>7217390</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,6 +1045,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färsk</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,45 +1076,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128103821</v>
+        <v>128103712</v>
       </c>
       <c r="B6" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626754</v>
+        <v>626667</v>
       </c>
       <c r="R6" t="n">
-        <v>7217270</v>
+        <v>7217072</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,6 +1155,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1774,10 +1774,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128103738</v>
+        <v>128103747</v>
       </c>
       <c r="B13" t="n">
-        <v>80133</v>
+        <v>80132</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1785,21 +1785,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626739</v>
+        <v>626821</v>
       </c>
       <c r="R13" t="n">
-        <v>7217280</v>
+        <v>7217089</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1871,32 +1871,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128103814</v>
+        <v>128103777</v>
       </c>
       <c r="B14" t="n">
-        <v>98468</v>
+        <v>80168</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626811</v>
+        <v>626745</v>
       </c>
       <c r="R14" t="n">
-        <v>7217114</v>
+        <v>7217253</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1968,32 +1968,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128103795</v>
+        <v>128103738</v>
       </c>
       <c r="B15" t="n">
-        <v>98468</v>
+        <v>80133</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626797</v>
+        <v>626739</v>
       </c>
       <c r="R15" t="n">
-        <v>7217132</v>
+        <v>7217280</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2065,32 +2065,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128103747</v>
+        <v>128103795</v>
       </c>
       <c r="B16" t="n">
-        <v>80132</v>
+        <v>98468</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626821</v>
+        <v>626797</v>
       </c>
       <c r="R16" t="n">
-        <v>7217089</v>
+        <v>7217132</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2162,32 +2162,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128103777</v>
+        <v>128103814</v>
       </c>
       <c r="B17" t="n">
-        <v>80168</v>
+        <v>98468</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626745</v>
+        <v>626811</v>
       </c>
       <c r="R17" t="n">
-        <v>7217253</v>
+        <v>7217114</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2854,32 +2854,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128103805</v>
+        <v>128103693</v>
       </c>
       <c r="B24" t="n">
-        <v>98468</v>
+        <v>79647</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626744</v>
+        <v>626633</v>
       </c>
       <c r="R24" t="n">
-        <v>7217285</v>
+        <v>7217153</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2951,32 +2951,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128103693</v>
+        <v>128103805</v>
       </c>
       <c r="B25" t="n">
-        <v>79647</v>
+        <v>98468</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2986,10 +2986,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>626633</v>
+        <v>626744</v>
       </c>
       <c r="R25" t="n">
-        <v>7217153</v>
+        <v>7217285</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3048,32 +3048,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128103691</v>
+        <v>128103864</v>
       </c>
       <c r="B26" t="n">
-        <v>79061</v>
+        <v>80167</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>185</v>
+        <v>6463</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>626657</v>
+        <v>626755</v>
       </c>
       <c r="R26" t="n">
-        <v>7217200</v>
+        <v>7217274</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3145,32 +3145,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128103864</v>
+        <v>128103751</v>
       </c>
       <c r="B27" t="n">
-        <v>80167</v>
+        <v>80132</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>626755</v>
+        <v>626665</v>
       </c>
       <c r="R27" t="n">
-        <v>7217274</v>
+        <v>7217186</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3242,10 +3242,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128103751</v>
+        <v>128103691</v>
       </c>
       <c r="B28" t="n">
-        <v>80132</v>
+        <v>79061</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3253,21 +3253,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3277,10 +3277,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>626665</v>
+        <v>626657</v>
       </c>
       <c r="R28" t="n">
-        <v>7217186</v>
+        <v>7217200</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3339,32 +3339,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128103862</v>
+        <v>128103873</v>
       </c>
       <c r="B29" t="n">
-        <v>80167</v>
+        <v>78435</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6463</v>
+        <v>6437</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3374,10 +3374,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>626687</v>
+        <v>626652</v>
       </c>
       <c r="R29" t="n">
-        <v>7217145</v>
+        <v>7217184</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3436,32 +3436,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128103873</v>
+        <v>128103862</v>
       </c>
       <c r="B30" t="n">
-        <v>78435</v>
+        <v>80167</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6437</v>
+        <v>6463</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>626652</v>
+        <v>626687</v>
       </c>
       <c r="R30" t="n">
-        <v>7217184</v>
+        <v>7217145</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3533,27 +3533,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128103865</v>
+        <v>128103846</v>
       </c>
       <c r="B31" t="n">
-        <v>80167</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3568,10 +3568,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>626739</v>
+        <v>626685</v>
       </c>
       <c r="R31" t="n">
-        <v>7217280</v>
+        <v>7217148</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3630,27 +3630,27 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128103846</v>
+        <v>128103865</v>
       </c>
       <c r="B32" t="n">
-        <v>79029</v>
+        <v>80167</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3665,10 +3665,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>626685</v>
+        <v>626739</v>
       </c>
       <c r="R32" t="n">
-        <v>7217148</v>
+        <v>7217280</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3727,53 +3727,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128103710</v>
+        <v>128103798</v>
       </c>
       <c r="B33" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>626769</v>
+        <v>626811</v>
       </c>
       <c r="R33" t="n">
-        <v>7217062</v>
+        <v>7217065</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3806,11 +3798,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3837,7 +3824,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128103798</v>
+        <v>128103799</v>
       </c>
       <c r="B34" t="n">
         <v>98468</v>
@@ -3872,10 +3859,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>626811</v>
+        <v>626796</v>
       </c>
       <c r="R34" t="n">
-        <v>7217065</v>
+        <v>7217064</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3934,45 +3921,53 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128103799</v>
+        <v>128103710</v>
       </c>
       <c r="B35" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>626796</v>
+        <v>626769</v>
       </c>
       <c r="R35" t="n">
-        <v>7217064</v>
+        <v>7217062</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4005,6 +4000,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4031,10 +4031,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128103749</v>
+        <v>128103789</v>
       </c>
       <c r="B36" t="n">
-        <v>80132</v>
+        <v>78787</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4042,21 +4042,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4066,10 +4066,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>626686</v>
+        <v>626633</v>
       </c>
       <c r="R36" t="n">
-        <v>7217075</v>
+        <v>7217153</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4128,10 +4128,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128103789</v>
+        <v>128103749</v>
       </c>
       <c r="B37" t="n">
-        <v>78787</v>
+        <v>80132</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4139,21 +4139,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4163,10 +4163,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>626633</v>
+        <v>626686</v>
       </c>
       <c r="R37" t="n">
-        <v>7217153</v>
+        <v>7217075</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4626,32 +4626,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128103732</v>
+        <v>128103841</v>
       </c>
       <c r="B42" t="n">
-        <v>98489</v>
+        <v>79029</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4661,10 +4661,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>626665</v>
+        <v>626739</v>
       </c>
       <c r="R42" t="n">
-        <v>7217113</v>
+        <v>7217304</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4723,32 +4723,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128103804</v>
+        <v>128103847</v>
       </c>
       <c r="B43" t="n">
-        <v>98468</v>
+        <v>79029</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4758,10 +4758,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>626622</v>
+        <v>626677</v>
       </c>
       <c r="R43" t="n">
-        <v>7217121</v>
+        <v>7217181</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4794,6 +4794,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4820,45 +4825,53 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128103802</v>
+        <v>128103707</v>
       </c>
       <c r="B44" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>626806</v>
+        <v>626786</v>
       </c>
       <c r="R44" t="n">
-        <v>7217042</v>
+        <v>7217295</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4891,6 +4904,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4917,32 +4935,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128103841</v>
+        <v>128103732</v>
       </c>
       <c r="B45" t="n">
-        <v>79029</v>
+        <v>98489</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4952,10 +4970,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>626739</v>
+        <v>626665</v>
       </c>
       <c r="R45" t="n">
-        <v>7217304</v>
+        <v>7217113</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5014,10 +5032,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128103847</v>
+        <v>128103708</v>
       </c>
       <c r="B46" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5025,34 +5043,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>626677</v>
+        <v>626743</v>
       </c>
       <c r="R46" t="n">
-        <v>7217181</v>
+        <v>7217219</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5089,7 +5115,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Med apothecier</t>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5116,53 +5142,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128103707</v>
+        <v>128103804</v>
       </c>
       <c r="B47" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>626786</v>
+        <v>626622</v>
       </c>
       <c r="R47" t="n">
-        <v>7217295</v>
+        <v>7217121</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5195,11 +5213,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5226,53 +5239,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128103708</v>
+        <v>128103802</v>
       </c>
       <c r="B48" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>626743</v>
+        <v>626806</v>
       </c>
       <c r="R48" t="n">
-        <v>7217219</v>
+        <v>7217042</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5305,11 +5310,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Bohål</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5627,32 +5627,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128103849</v>
+        <v>128103726</v>
       </c>
       <c r="B52" t="n">
-        <v>79029</v>
+        <v>80161</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5662,10 +5662,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>626701</v>
+        <v>626745</v>
       </c>
       <c r="R52" t="n">
-        <v>7217242</v>
+        <v>7217244</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5724,10 +5724,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128103713</v>
+        <v>128103849</v>
       </c>
       <c r="B53" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5735,42 +5735,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>626703</v>
+        <v>626701</v>
       </c>
       <c r="R53" t="n">
-        <v>7217299</v>
+        <v>7217242</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5803,11 +5795,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5834,32 +5821,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128103796</v>
+        <v>128103779</v>
       </c>
       <c r="B54" t="n">
-        <v>98468</v>
+        <v>80168</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5869,10 +5856,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>626803</v>
+        <v>626819</v>
       </c>
       <c r="R54" t="n">
-        <v>7217099</v>
+        <v>7217095</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5931,32 +5918,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128103797</v>
+        <v>128103855</v>
       </c>
       <c r="B55" t="n">
-        <v>98468</v>
+        <v>82870</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5966,10 +5953,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>626820</v>
+        <v>626723</v>
       </c>
       <c r="R55" t="n">
-        <v>7217037</v>
+        <v>7217326</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6028,45 +6015,53 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128103726</v>
+        <v>128103713</v>
       </c>
       <c r="B56" t="n">
-        <v>80161</v>
+        <v>57672</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>626745</v>
+        <v>626703</v>
       </c>
       <c r="R56" t="n">
-        <v>7217244</v>
+        <v>7217299</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6099,6 +6094,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6125,32 +6125,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128103779</v>
+        <v>128103797</v>
       </c>
       <c r="B57" t="n">
-        <v>80168</v>
+        <v>98468</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6160,10 +6160,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>626819</v>
+        <v>626820</v>
       </c>
       <c r="R57" t="n">
-        <v>7217095</v>
+        <v>7217037</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6222,32 +6222,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128103855</v>
+        <v>128103796</v>
       </c>
       <c r="B58" t="n">
-        <v>82870</v>
+        <v>98468</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>626723</v>
+        <v>626803</v>
       </c>
       <c r="R58" t="n">
-        <v>7217326</v>
+        <v>7217099</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>

--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -675,45 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128103821</v>
+        <v>128103715</v>
       </c>
       <c r="B2" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626754</v>
+        <v>626715</v>
       </c>
       <c r="R2" t="n">
-        <v>7217270</v>
+        <v>7217390</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +754,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färsk</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128103750</v>
+        <v>128103712</v>
       </c>
       <c r="B3" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +796,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626688</v>
+        <v>626667</v>
       </c>
       <c r="R3" t="n">
-        <v>7217164</v>
+        <v>7217072</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,6 +864,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,7 +895,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128103748</v>
+        <v>128103750</v>
       </c>
       <c r="B4" t="n">
         <v>80132</v>
@@ -904,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626663</v>
+        <v>626688</v>
       </c>
       <c r="R4" t="n">
-        <v>7217050</v>
+        <v>7217164</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +992,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128103715</v>
+        <v>128103748</v>
       </c>
       <c r="B5" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,42 +1003,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626715</v>
+        <v>626663</v>
       </c>
       <c r="R5" t="n">
-        <v>7217390</v>
+        <v>7217050</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1045,11 +1063,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färsk</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,53 +1089,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128103712</v>
+        <v>128103821</v>
       </c>
       <c r="B6" t="n">
-        <v>57672</v>
+        <v>98469</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626667</v>
+        <v>626754</v>
       </c>
       <c r="R6" t="n">
-        <v>7217072</v>
+        <v>7217270</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1155,11 +1160,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Bohål</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1186,10 +1186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128103861</v>
+        <v>128103815</v>
       </c>
       <c r="B7" t="n">
-        <v>91924</v>
+        <v>98469</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1197,21 +1197,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1221,10 +1221,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626733</v>
+        <v>626821</v>
       </c>
       <c r="R7" t="n">
-        <v>7217284</v>
+        <v>7217074</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1259,18 +1259,12 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Bild</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1289,10 +1283,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128103815</v>
+        <v>128103803</v>
       </c>
       <c r="B8" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1324,10 +1318,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626821</v>
+        <v>626709</v>
       </c>
       <c r="R8" t="n">
-        <v>7217074</v>
+        <v>7217057</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,10 +1380,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128103803</v>
+        <v>128103861</v>
       </c>
       <c r="B9" t="n">
-        <v>98468</v>
+        <v>91925</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1397,21 +1391,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1421,10 +1415,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626709</v>
+        <v>626733</v>
       </c>
       <c r="R9" t="n">
-        <v>7217057</v>
+        <v>7217284</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,12 +1453,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Bild</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -2065,10 +2065,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128103795</v>
+        <v>128103814</v>
       </c>
       <c r="B16" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626797</v>
+        <v>626811</v>
       </c>
       <c r="R16" t="n">
-        <v>7217132</v>
+        <v>7217114</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2162,10 +2162,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128103814</v>
+        <v>128103795</v>
       </c>
       <c r="B17" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626811</v>
+        <v>626797</v>
       </c>
       <c r="R17" t="n">
-        <v>7217114</v>
+        <v>7217132</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2372,7 +2372,7 @@
         <v>128103820</v>
       </c>
       <c r="B19" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2466,32 +2466,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128103752</v>
+        <v>128103817</v>
       </c>
       <c r="B20" t="n">
-        <v>80132</v>
+        <v>98469</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2501,10 +2501,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626739</v>
+        <v>626705</v>
       </c>
       <c r="R20" t="n">
-        <v>7217280</v>
+        <v>7217045</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2563,32 +2563,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128103817</v>
+        <v>128103752</v>
       </c>
       <c r="B21" t="n">
-        <v>98468</v>
+        <v>80132</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626705</v>
+        <v>626739</v>
       </c>
       <c r="R21" t="n">
-        <v>7217045</v>
+        <v>7217280</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2954,7 +2954,7 @@
         <v>128103805</v>
       </c>
       <c r="B25" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3727,10 +3727,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128103798</v>
+        <v>128103799</v>
       </c>
       <c r="B33" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3762,10 +3762,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>626811</v>
+        <v>626796</v>
       </c>
       <c r="R33" t="n">
-        <v>7217065</v>
+        <v>7217064</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3824,45 +3824,53 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128103799</v>
+        <v>128103710</v>
       </c>
       <c r="B34" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>626796</v>
+        <v>626769</v>
       </c>
       <c r="R34" t="n">
-        <v>7217064</v>
+        <v>7217062</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3895,6 +3903,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3921,53 +3934,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128103710</v>
+        <v>128103798</v>
       </c>
       <c r="B35" t="n">
-        <v>57672</v>
+        <v>98469</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>626769</v>
+        <v>626811</v>
       </c>
       <c r="R35" t="n">
-        <v>7217062</v>
+        <v>7217065</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4000,11 +4005,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4031,32 +4031,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128103789</v>
+        <v>128103800</v>
       </c>
       <c r="B36" t="n">
-        <v>78787</v>
+        <v>98469</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4066,10 +4066,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>626633</v>
+        <v>626843</v>
       </c>
       <c r="R36" t="n">
-        <v>7217153</v>
+        <v>7217062</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4128,32 +4128,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128103749</v>
+        <v>128103816</v>
       </c>
       <c r="B37" t="n">
-        <v>80132</v>
+        <v>98469</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4163,10 +4163,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>626686</v>
+        <v>626837</v>
       </c>
       <c r="R37" t="n">
-        <v>7217075</v>
+        <v>7217076</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4225,32 +4225,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128103800</v>
+        <v>128103789</v>
       </c>
       <c r="B38" t="n">
-        <v>98468</v>
+        <v>78787</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4260,10 +4260,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626843</v>
+        <v>626633</v>
       </c>
       <c r="R38" t="n">
-        <v>7217062</v>
+        <v>7217153</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4322,32 +4322,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128103816</v>
+        <v>128103749</v>
       </c>
       <c r="B39" t="n">
-        <v>98468</v>
+        <v>80132</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4357,10 +4357,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626837</v>
+        <v>626686</v>
       </c>
       <c r="R39" t="n">
-        <v>7217076</v>
+        <v>7217075</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4626,32 +4626,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128103841</v>
+        <v>128103804</v>
       </c>
       <c r="B42" t="n">
-        <v>79029</v>
+        <v>98469</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4661,10 +4661,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>626739</v>
+        <v>626622</v>
       </c>
       <c r="R42" t="n">
-        <v>7217304</v>
+        <v>7217121</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4723,32 +4723,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128103847</v>
+        <v>128103802</v>
       </c>
       <c r="B43" t="n">
-        <v>79029</v>
+        <v>98469</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4758,10 +4758,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>626677</v>
+        <v>626806</v>
       </c>
       <c r="R43" t="n">
-        <v>7217181</v>
+        <v>7217042</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4794,11 +4794,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4825,10 +4820,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128103707</v>
+        <v>128103841</v>
       </c>
       <c r="B44" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4836,42 +4831,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>626786</v>
+        <v>626739</v>
       </c>
       <c r="R44" t="n">
-        <v>7217295</v>
+        <v>7217304</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4904,11 +4891,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4935,32 +4917,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128103732</v>
+        <v>128103847</v>
       </c>
       <c r="B45" t="n">
-        <v>98489</v>
+        <v>79029</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4970,10 +4952,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>626665</v>
+        <v>626677</v>
       </c>
       <c r="R45" t="n">
-        <v>7217113</v>
+        <v>7217181</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5006,6 +4988,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5032,7 +5019,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128103708</v>
+        <v>128103707</v>
       </c>
       <c r="B46" t="n">
         <v>57672</v>
@@ -5065,7 +5052,7 @@
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -5075,10 +5062,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>626743</v>
+        <v>626786</v>
       </c>
       <c r="R46" t="n">
-        <v>7217219</v>
+        <v>7217295</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5115,7 +5102,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Bohål</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5142,45 +5129,53 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128103804</v>
+        <v>128103708</v>
       </c>
       <c r="B47" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>626622</v>
+        <v>626743</v>
       </c>
       <c r="R47" t="n">
-        <v>7217121</v>
+        <v>7217219</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5213,6 +5208,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5239,32 +5239,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128103802</v>
+        <v>128103732</v>
       </c>
       <c r="B48" t="n">
-        <v>98468</v>
+        <v>98490</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5274,10 +5274,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>626806</v>
+        <v>626665</v>
       </c>
       <c r="R48" t="n">
-        <v>7217042</v>
+        <v>7217113</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5336,10 +5336,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128103840</v>
+        <v>128103790</v>
       </c>
       <c r="B49" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5347,21 +5347,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5371,10 +5371,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>626757</v>
+        <v>626730</v>
       </c>
       <c r="R49" t="n">
-        <v>7217294</v>
+        <v>7217238</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5433,10 +5433,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128103790</v>
+        <v>128103848</v>
       </c>
       <c r="B50" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5444,21 +5444,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>626730</v>
+        <v>626660</v>
       </c>
       <c r="R50" t="n">
-        <v>7217238</v>
+        <v>7217210</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5530,7 +5530,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128103848</v>
+        <v>128103840</v>
       </c>
       <c r="B51" t="n">
         <v>79029</v>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>626660</v>
+        <v>626757</v>
       </c>
       <c r="R51" t="n">
-        <v>7217210</v>
+        <v>7217294</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6125,10 +6125,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128103797</v>
+        <v>128103796</v>
       </c>
       <c r="B57" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6160,10 +6160,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>626820</v>
+        <v>626803</v>
       </c>
       <c r="R57" t="n">
-        <v>7217037</v>
+        <v>7217099</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6222,10 +6222,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128103796</v>
+        <v>128103797</v>
       </c>
       <c r="B58" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>626803</v>
+        <v>626820</v>
       </c>
       <c r="R58" t="n">
-        <v>7217099</v>
+        <v>7217037</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6322,7 +6322,7 @@
         <v>128103818</v>
       </c>
       <c r="B59" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -1092,7 +1092,7 @@
         <v>128103821</v>
       </c>
       <c r="B6" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,10 +1186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128103815</v>
+        <v>128103861</v>
       </c>
       <c r="B7" t="n">
-        <v>98469</v>
+        <v>91926</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1197,21 +1197,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1221,10 +1221,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626821</v>
+        <v>626733</v>
       </c>
       <c r="R7" t="n">
-        <v>7217074</v>
+        <v>7217284</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1259,12 +1259,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Bild</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1283,10 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128103803</v>
+        <v>128103815</v>
       </c>
       <c r="B8" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626709</v>
+        <v>626821</v>
       </c>
       <c r="R8" t="n">
-        <v>7217057</v>
+        <v>7217074</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1380,10 +1386,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128103861</v>
+        <v>128103803</v>
       </c>
       <c r="B9" t="n">
-        <v>91925</v>
+        <v>98470</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1391,21 +1397,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1415,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626733</v>
+        <v>626709</v>
       </c>
       <c r="R9" t="n">
-        <v>7217284</v>
+        <v>7217057</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1453,18 +1459,12 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Bild</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1774,10 +1774,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128103747</v>
+        <v>128103738</v>
       </c>
       <c r="B13" t="n">
-        <v>80132</v>
+        <v>80133</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1785,21 +1785,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626821</v>
+        <v>626739</v>
       </c>
       <c r="R13" t="n">
-        <v>7217089</v>
+        <v>7217280</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1871,32 +1871,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128103777</v>
+        <v>128103747</v>
       </c>
       <c r="B14" t="n">
-        <v>80168</v>
+        <v>80132</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626745</v>
+        <v>626821</v>
       </c>
       <c r="R14" t="n">
-        <v>7217253</v>
+        <v>7217089</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1968,32 +1968,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128103738</v>
+        <v>128103777</v>
       </c>
       <c r="B15" t="n">
-        <v>80133</v>
+        <v>80168</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626739</v>
+        <v>626745</v>
       </c>
       <c r="R15" t="n">
-        <v>7217280</v>
+        <v>7217253</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2068,7 +2068,7 @@
         <v>128103814</v>
       </c>
       <c r="B16" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>128103795</v>
       </c>
       <c r="B17" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>128103820</v>
       </c>
       <c r="B19" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2466,32 +2466,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128103817</v>
+        <v>128103752</v>
       </c>
       <c r="B20" t="n">
-        <v>98469</v>
+        <v>80132</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2501,10 +2501,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626705</v>
+        <v>626739</v>
       </c>
       <c r="R20" t="n">
-        <v>7217045</v>
+        <v>7217280</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2563,32 +2563,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128103752</v>
+        <v>128103817</v>
       </c>
       <c r="B21" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626739</v>
+        <v>626705</v>
       </c>
       <c r="R21" t="n">
-        <v>7217280</v>
+        <v>7217045</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2954,7 +2954,7 @@
         <v>128103805</v>
       </c>
       <c r="B25" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3048,32 +3048,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128103864</v>
+        <v>128103691</v>
       </c>
       <c r="B26" t="n">
-        <v>80167</v>
+        <v>79061</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6463</v>
+        <v>185</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>626755</v>
+        <v>626657</v>
       </c>
       <c r="R26" t="n">
-        <v>7217274</v>
+        <v>7217200</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3145,32 +3145,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128103751</v>
+        <v>128103864</v>
       </c>
       <c r="B27" t="n">
-        <v>80132</v>
+        <v>80167</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>626665</v>
+        <v>626755</v>
       </c>
       <c r="R27" t="n">
-        <v>7217186</v>
+        <v>7217274</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3242,10 +3242,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128103691</v>
+        <v>128103751</v>
       </c>
       <c r="B28" t="n">
-        <v>79061</v>
+        <v>80132</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3253,21 +3253,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3277,10 +3277,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>626657</v>
+        <v>626665</v>
       </c>
       <c r="R28" t="n">
-        <v>7217200</v>
+        <v>7217186</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3727,45 +3727,53 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128103799</v>
+        <v>128103710</v>
       </c>
       <c r="B33" t="n">
-        <v>98469</v>
+        <v>57672</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>626796</v>
+        <v>626769</v>
       </c>
       <c r="R33" t="n">
-        <v>7217064</v>
+        <v>7217062</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3798,6 +3806,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3824,53 +3837,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128103710</v>
+        <v>128103798</v>
       </c>
       <c r="B34" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>626769</v>
+        <v>626811</v>
       </c>
       <c r="R34" t="n">
-        <v>7217062</v>
+        <v>7217065</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3903,11 +3908,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3934,10 +3934,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128103798</v>
+        <v>128103799</v>
       </c>
       <c r="B35" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3969,10 +3969,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>626811</v>
+        <v>626796</v>
       </c>
       <c r="R35" t="n">
-        <v>7217065</v>
+        <v>7217064</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4031,32 +4031,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128103800</v>
+        <v>128103789</v>
       </c>
       <c r="B36" t="n">
-        <v>98469</v>
+        <v>78787</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4066,10 +4066,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>626843</v>
+        <v>626633</v>
       </c>
       <c r="R36" t="n">
-        <v>7217062</v>
+        <v>7217153</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4128,32 +4128,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128103816</v>
+        <v>128103749</v>
       </c>
       <c r="B37" t="n">
-        <v>98469</v>
+        <v>80132</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4163,10 +4163,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>626837</v>
+        <v>626686</v>
       </c>
       <c r="R37" t="n">
-        <v>7217076</v>
+        <v>7217075</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4225,32 +4225,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128103789</v>
+        <v>128103800</v>
       </c>
       <c r="B38" t="n">
-        <v>78787</v>
+        <v>98470</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4260,10 +4260,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626633</v>
+        <v>626843</v>
       </c>
       <c r="R38" t="n">
-        <v>7217153</v>
+        <v>7217062</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4322,32 +4322,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128103749</v>
+        <v>128103816</v>
       </c>
       <c r="B39" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4357,10 +4357,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626686</v>
+        <v>626837</v>
       </c>
       <c r="R39" t="n">
-        <v>7217075</v>
+        <v>7217076</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4629,7 +4629,7 @@
         <v>128103804</v>
       </c>
       <c r="B42" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         <v>128103802</v>
       </c>
       <c r="B43" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4820,32 +4820,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128103841</v>
+        <v>128103732</v>
       </c>
       <c r="B44" t="n">
-        <v>79029</v>
+        <v>98491</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4855,10 +4855,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>626739</v>
+        <v>626665</v>
       </c>
       <c r="R44" t="n">
-        <v>7217304</v>
+        <v>7217113</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4917,10 +4917,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128103847</v>
+        <v>128103707</v>
       </c>
       <c r="B45" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4928,34 +4928,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>626677</v>
+        <v>626786</v>
       </c>
       <c r="R45" t="n">
-        <v>7217181</v>
+        <v>7217295</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4992,7 +5000,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Med apothecier</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5019,7 +5027,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128103707</v>
+        <v>128103708</v>
       </c>
       <c r="B46" t="n">
         <v>57672</v>
@@ -5052,7 +5060,7 @@
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -5062,10 +5070,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>626786</v>
+        <v>626743</v>
       </c>
       <c r="R46" t="n">
-        <v>7217295</v>
+        <v>7217219</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5102,7 +5110,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5129,10 +5137,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128103708</v>
+        <v>128103847</v>
       </c>
       <c r="B47" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5140,42 +5148,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>626743</v>
+        <v>626677</v>
       </c>
       <c r="R47" t="n">
-        <v>7217219</v>
+        <v>7217181</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5212,7 +5212,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Bohål</t>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5239,32 +5239,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128103732</v>
+        <v>128103841</v>
       </c>
       <c r="B48" t="n">
-        <v>98490</v>
+        <v>79029</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5274,10 +5274,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>626665</v>
+        <v>626739</v>
       </c>
       <c r="R48" t="n">
-        <v>7217113</v>
+        <v>7217304</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5336,10 +5336,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128103790</v>
+        <v>128103848</v>
       </c>
       <c r="B49" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5347,21 +5347,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5371,10 +5371,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>626730</v>
+        <v>626660</v>
       </c>
       <c r="R49" t="n">
-        <v>7217238</v>
+        <v>7217210</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5433,7 +5433,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128103848</v>
+        <v>128103840</v>
       </c>
       <c r="B50" t="n">
         <v>79029</v>
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>626660</v>
+        <v>626757</v>
       </c>
       <c r="R50" t="n">
-        <v>7217210</v>
+        <v>7217294</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5530,10 +5530,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128103840</v>
+        <v>128103790</v>
       </c>
       <c r="B51" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5541,21 +5541,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>626757</v>
+        <v>626730</v>
       </c>
       <c r="R51" t="n">
-        <v>7217294</v>
+        <v>7217238</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5627,32 +5627,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128103726</v>
+        <v>128103855</v>
       </c>
       <c r="B52" t="n">
-        <v>80161</v>
+        <v>82870</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5662,10 +5662,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>626745</v>
+        <v>626723</v>
       </c>
       <c r="R52" t="n">
-        <v>7217244</v>
+        <v>7217326</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5724,32 +5724,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128103849</v>
+        <v>128103726</v>
       </c>
       <c r="B53" t="n">
-        <v>79029</v>
+        <v>80161</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5759,10 +5759,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>626701</v>
+        <v>626745</v>
       </c>
       <c r="R53" t="n">
-        <v>7217242</v>
+        <v>7217244</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5918,10 +5918,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128103855</v>
+        <v>128103849</v>
       </c>
       <c r="B55" t="n">
-        <v>82870</v>
+        <v>79029</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5929,21 +5929,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5953,10 +5953,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>626723</v>
+        <v>626701</v>
       </c>
       <c r="R55" t="n">
-        <v>7217326</v>
+        <v>7217242</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6128,7 +6128,7 @@
         <v>128103796</v>
       </c>
       <c r="B57" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>128103797</v>
       </c>
       <c r="B58" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>128103818</v>
       </c>
       <c r="B59" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128103715</v>
+        <v>128103750</v>
       </c>
       <c r="B2" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626715</v>
+        <v>626688</v>
       </c>
       <c r="R2" t="n">
-        <v>7217390</v>
+        <v>7217164</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färsk</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128103712</v>
+        <v>128103748</v>
       </c>
       <c r="B3" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,42 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626667</v>
+        <v>626663</v>
       </c>
       <c r="R3" t="n">
-        <v>7217072</v>
+        <v>7217050</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Bohål</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128103750</v>
+        <v>128103715</v>
       </c>
       <c r="B4" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,34 +880,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626688</v>
+        <v>626715</v>
       </c>
       <c r="R4" t="n">
-        <v>7217164</v>
+        <v>7217390</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,6 +948,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färsk</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128103748</v>
+        <v>128103712</v>
       </c>
       <c r="B5" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1003,34 +990,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626663</v>
+        <v>626667</v>
       </c>
       <c r="R5" t="n">
-        <v>7217050</v>
+        <v>7217072</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,6 +1058,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1186,10 +1186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128103861</v>
+        <v>128103815</v>
       </c>
       <c r="B7" t="n">
-        <v>91926</v>
+        <v>98470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1197,21 +1197,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1221,10 +1221,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626733</v>
+        <v>626821</v>
       </c>
       <c r="R7" t="n">
-        <v>7217284</v>
+        <v>7217074</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1259,18 +1259,12 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Bild</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1289,7 +1283,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128103815</v>
+        <v>128103803</v>
       </c>
       <c r="B8" t="n">
         <v>98470</v>
@@ -1324,10 +1318,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626821</v>
+        <v>626709</v>
       </c>
       <c r="R8" t="n">
-        <v>7217074</v>
+        <v>7217057</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,10 +1380,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128103803</v>
+        <v>128103861</v>
       </c>
       <c r="B9" t="n">
-        <v>98470</v>
+        <v>91926</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1397,21 +1391,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1421,10 +1415,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626709</v>
+        <v>626733</v>
       </c>
       <c r="R9" t="n">
-        <v>7217057</v>
+        <v>7217284</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,12 +1453,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Bild</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -2466,32 +2466,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128103752</v>
+        <v>128103817</v>
       </c>
       <c r="B20" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2501,10 +2501,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626739</v>
+        <v>626705</v>
       </c>
       <c r="R20" t="n">
-        <v>7217280</v>
+        <v>7217045</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2563,32 +2563,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128103817</v>
+        <v>128103752</v>
       </c>
       <c r="B21" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626705</v>
+        <v>626739</v>
       </c>
       <c r="R21" t="n">
-        <v>7217045</v>
+        <v>7217280</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3339,32 +3339,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128103873</v>
+        <v>128103862</v>
       </c>
       <c r="B29" t="n">
-        <v>78435</v>
+        <v>80167</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6437</v>
+        <v>6463</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3374,10 +3374,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>626652</v>
+        <v>626687</v>
       </c>
       <c r="R29" t="n">
-        <v>7217184</v>
+        <v>7217145</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3436,32 +3436,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128103862</v>
+        <v>128103873</v>
       </c>
       <c r="B30" t="n">
-        <v>80167</v>
+        <v>78435</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6463</v>
+        <v>6437</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>626687</v>
+        <v>626652</v>
       </c>
       <c r="R30" t="n">
-        <v>7217145</v>
+        <v>7217184</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3533,27 +3533,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128103846</v>
+        <v>128103865</v>
       </c>
       <c r="B31" t="n">
-        <v>79029</v>
+        <v>80167</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3568,10 +3568,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>626685</v>
+        <v>626739</v>
       </c>
       <c r="R31" t="n">
-        <v>7217148</v>
+        <v>7217280</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3630,27 +3630,27 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128103865</v>
+        <v>128103846</v>
       </c>
       <c r="B32" t="n">
-        <v>80167</v>
+        <v>79029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3665,10 +3665,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>626739</v>
+        <v>626685</v>
       </c>
       <c r="R32" t="n">
-        <v>7217280</v>
+        <v>7217148</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3727,53 +3727,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128103710</v>
+        <v>128103798</v>
       </c>
       <c r="B33" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>626769</v>
+        <v>626811</v>
       </c>
       <c r="R33" t="n">
-        <v>7217062</v>
+        <v>7217065</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3806,11 +3798,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3837,7 +3824,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128103798</v>
+        <v>128103799</v>
       </c>
       <c r="B34" t="n">
         <v>98470</v>
@@ -3872,10 +3859,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>626811</v>
+        <v>626796</v>
       </c>
       <c r="R34" t="n">
-        <v>7217065</v>
+        <v>7217064</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3934,45 +3921,53 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128103799</v>
+        <v>128103710</v>
       </c>
       <c r="B35" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>626796</v>
+        <v>626769</v>
       </c>
       <c r="R35" t="n">
-        <v>7217064</v>
+        <v>7217062</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4005,6 +4000,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4031,32 +4031,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128103789</v>
+        <v>128103800</v>
       </c>
       <c r="B36" t="n">
-        <v>78787</v>
+        <v>98470</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4066,10 +4066,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>626633</v>
+        <v>626843</v>
       </c>
       <c r="R36" t="n">
-        <v>7217153</v>
+        <v>7217062</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4128,32 +4128,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128103749</v>
+        <v>128103816</v>
       </c>
       <c r="B37" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4163,10 +4163,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>626686</v>
+        <v>626837</v>
       </c>
       <c r="R37" t="n">
-        <v>7217075</v>
+        <v>7217076</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4225,32 +4225,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128103800</v>
+        <v>128103789</v>
       </c>
       <c r="B38" t="n">
-        <v>98470</v>
+        <v>78787</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4260,10 +4260,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626843</v>
+        <v>626633</v>
       </c>
       <c r="R38" t="n">
-        <v>7217062</v>
+        <v>7217153</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4322,32 +4322,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128103816</v>
+        <v>128103749</v>
       </c>
       <c r="B39" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4357,10 +4357,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626837</v>
+        <v>626686</v>
       </c>
       <c r="R39" t="n">
-        <v>7217076</v>
+        <v>7217075</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4626,32 +4626,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128103804</v>
+        <v>128103732</v>
       </c>
       <c r="B42" t="n">
-        <v>98470</v>
+        <v>98491</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4661,10 +4661,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>626622</v>
+        <v>626665</v>
       </c>
       <c r="R42" t="n">
-        <v>7217121</v>
+        <v>7217113</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4723,32 +4723,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128103802</v>
+        <v>128103841</v>
       </c>
       <c r="B43" t="n">
-        <v>98470</v>
+        <v>79029</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4758,10 +4758,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>626806</v>
+        <v>626739</v>
       </c>
       <c r="R43" t="n">
-        <v>7217042</v>
+        <v>7217304</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4820,32 +4820,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128103732</v>
+        <v>128103847</v>
       </c>
       <c r="B44" t="n">
-        <v>98491</v>
+        <v>79029</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4855,10 +4855,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>626665</v>
+        <v>626677</v>
       </c>
       <c r="R44" t="n">
-        <v>7217113</v>
+        <v>7217181</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4891,6 +4891,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5137,32 +5142,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128103847</v>
+        <v>128103804</v>
       </c>
       <c r="B47" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5172,10 +5177,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>626677</v>
+        <v>626622</v>
       </c>
       <c r="R47" t="n">
-        <v>7217181</v>
+        <v>7217121</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5208,11 +5213,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5239,32 +5239,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128103841</v>
+        <v>128103802</v>
       </c>
       <c r="B48" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5274,10 +5274,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>626739</v>
+        <v>626806</v>
       </c>
       <c r="R48" t="n">
-        <v>7217304</v>
+        <v>7217042</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5336,7 +5336,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128103848</v>
+        <v>128103840</v>
       </c>
       <c r="B49" t="n">
         <v>79029</v>
@@ -5371,10 +5371,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>626660</v>
+        <v>626757</v>
       </c>
       <c r="R49" t="n">
-        <v>7217210</v>
+        <v>7217294</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5433,10 +5433,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128103840</v>
+        <v>128103790</v>
       </c>
       <c r="B50" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5444,21 +5444,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>626757</v>
+        <v>626730</v>
       </c>
       <c r="R50" t="n">
-        <v>7217294</v>
+        <v>7217238</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5530,10 +5530,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128103790</v>
+        <v>128103848</v>
       </c>
       <c r="B51" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5541,21 +5541,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>626730</v>
+        <v>626660</v>
       </c>
       <c r="R51" t="n">
-        <v>7217238</v>
+        <v>7217210</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5627,32 +5627,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128103855</v>
+        <v>128103796</v>
       </c>
       <c r="B52" t="n">
-        <v>82870</v>
+        <v>98470</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5662,10 +5662,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>626723</v>
+        <v>626803</v>
       </c>
       <c r="R52" t="n">
-        <v>7217326</v>
+        <v>7217099</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5724,32 +5724,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128103726</v>
+        <v>128103797</v>
       </c>
       <c r="B53" t="n">
-        <v>80161</v>
+        <v>98470</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5759,10 +5759,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>626745</v>
+        <v>626820</v>
       </c>
       <c r="R53" t="n">
-        <v>7217244</v>
+        <v>7217037</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5821,32 +5821,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128103779</v>
+        <v>128103855</v>
       </c>
       <c r="B54" t="n">
-        <v>80168</v>
+        <v>82870</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5856,10 +5856,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>626819</v>
+        <v>626723</v>
       </c>
       <c r="R54" t="n">
-        <v>7217095</v>
+        <v>7217326</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5918,32 +5918,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128103849</v>
+        <v>128103726</v>
       </c>
       <c r="B55" t="n">
-        <v>79029</v>
+        <v>80161</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5953,10 +5953,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>626701</v>
+        <v>626745</v>
       </c>
       <c r="R55" t="n">
-        <v>7217242</v>
+        <v>7217244</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6015,10 +6015,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128103713</v>
+        <v>128103849</v>
       </c>
       <c r="B56" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6026,42 +6026,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>626703</v>
+        <v>626701</v>
       </c>
       <c r="R56" t="n">
-        <v>7217299</v>
+        <v>7217242</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6094,11 +6086,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6125,32 +6112,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128103796</v>
+        <v>128103779</v>
       </c>
       <c r="B57" t="n">
-        <v>98470</v>
+        <v>80168</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6160,10 +6147,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>626803</v>
+        <v>626819</v>
       </c>
       <c r="R57" t="n">
-        <v>7217099</v>
+        <v>7217095</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6222,45 +6209,53 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128103797</v>
+        <v>128103713</v>
       </c>
       <c r="B58" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>626820</v>
+        <v>626703</v>
       </c>
       <c r="R58" t="n">
-        <v>7217037</v>
+        <v>7217299</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6293,6 +6288,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -4626,32 +4626,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128103732</v>
+        <v>128103841</v>
       </c>
       <c r="B42" t="n">
-        <v>98491</v>
+        <v>79029</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4661,10 +4661,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>626665</v>
+        <v>626739</v>
       </c>
       <c r="R42" t="n">
-        <v>7217113</v>
+        <v>7217304</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4723,7 +4723,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128103841</v>
+        <v>128103847</v>
       </c>
       <c r="B43" t="n">
         <v>79029</v>
@@ -4758,10 +4758,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>626739</v>
+        <v>626677</v>
       </c>
       <c r="R43" t="n">
-        <v>7217304</v>
+        <v>7217181</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4794,6 +4794,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4820,32 +4825,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128103847</v>
+        <v>128103804</v>
       </c>
       <c r="B44" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4855,10 +4860,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>626677</v>
+        <v>626622</v>
       </c>
       <c r="R44" t="n">
-        <v>7217181</v>
+        <v>7217121</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4891,11 +4896,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4922,53 +4922,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128103707</v>
+        <v>128103802</v>
       </c>
       <c r="B45" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>626786</v>
+        <v>626806</v>
       </c>
       <c r="R45" t="n">
-        <v>7217295</v>
+        <v>7217042</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5001,11 +4993,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5032,7 +5019,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128103708</v>
+        <v>128103707</v>
       </c>
       <c r="B46" t="n">
         <v>57672</v>
@@ -5065,7 +5052,7 @@
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -5075,10 +5062,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>626743</v>
+        <v>626786</v>
       </c>
       <c r="R46" t="n">
-        <v>7217219</v>
+        <v>7217295</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5115,7 +5102,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Bohål</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5142,45 +5129,53 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128103804</v>
+        <v>128103708</v>
       </c>
       <c r="B47" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>626622</v>
+        <v>626743</v>
       </c>
       <c r="R47" t="n">
-        <v>7217121</v>
+        <v>7217219</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5213,6 +5208,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5239,32 +5239,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128103802</v>
+        <v>128103732</v>
       </c>
       <c r="B48" t="n">
-        <v>98470</v>
+        <v>98491</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5274,10 +5274,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>626806</v>
+        <v>626665</v>
       </c>
       <c r="R48" t="n">
-        <v>7217042</v>
+        <v>7217113</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -2466,32 +2466,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128103817</v>
+        <v>128103752</v>
       </c>
       <c r="B20" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2501,10 +2501,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626705</v>
+        <v>626739</v>
       </c>
       <c r="R20" t="n">
-        <v>7217045</v>
+        <v>7217280</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2563,32 +2563,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128103752</v>
+        <v>128103817</v>
       </c>
       <c r="B21" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626739</v>
+        <v>626705</v>
       </c>
       <c r="R21" t="n">
-        <v>7217280</v>
+        <v>7217045</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -4031,32 +4031,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128103800</v>
+        <v>128103749</v>
       </c>
       <c r="B36" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4066,10 +4066,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>626843</v>
+        <v>626686</v>
       </c>
       <c r="R36" t="n">
-        <v>7217062</v>
+        <v>7217075</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4128,7 +4128,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128103816</v>
+        <v>128103800</v>
       </c>
       <c r="B37" t="n">
         <v>98470</v>
@@ -4163,10 +4163,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>626837</v>
+        <v>626843</v>
       </c>
       <c r="R37" t="n">
-        <v>7217076</v>
+        <v>7217062</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4322,32 +4322,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128103749</v>
+        <v>128103816</v>
       </c>
       <c r="B39" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4357,10 +4357,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626686</v>
+        <v>626837</v>
       </c>
       <c r="R39" t="n">
-        <v>7217075</v>
+        <v>7217076</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4419,45 +4419,53 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128103776</v>
+        <v>128103709</v>
       </c>
       <c r="B40" t="n">
-        <v>80168</v>
+        <v>57672</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>626665</v>
+        <v>626740</v>
       </c>
       <c r="R40" t="n">
-        <v>7217186</v>
+        <v>7217219</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4490,6 +4498,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4516,53 +4529,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128103709</v>
+        <v>128103776</v>
       </c>
       <c r="B41" t="n">
-        <v>57672</v>
+        <v>80168</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>626740</v>
+        <v>626665</v>
       </c>
       <c r="R41" t="n">
-        <v>7217219</v>
+        <v>7217186</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4595,11 +4600,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4626,32 +4626,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128103841</v>
+        <v>128103732</v>
       </c>
       <c r="B42" t="n">
-        <v>79029</v>
+        <v>98491</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4661,10 +4661,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>626739</v>
+        <v>626665</v>
       </c>
       <c r="R42" t="n">
-        <v>7217304</v>
+        <v>7217113</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4723,7 +4723,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128103847</v>
+        <v>128103841</v>
       </c>
       <c r="B43" t="n">
         <v>79029</v>
@@ -4758,10 +4758,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>626677</v>
+        <v>626739</v>
       </c>
       <c r="R43" t="n">
-        <v>7217181</v>
+        <v>7217304</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4794,11 +4794,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4825,32 +4820,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128103804</v>
+        <v>128103847</v>
       </c>
       <c r="B44" t="n">
-        <v>98470</v>
+        <v>79029</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4860,10 +4855,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>626622</v>
+        <v>626677</v>
       </c>
       <c r="R44" t="n">
-        <v>7217121</v>
+        <v>7217181</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4896,6 +4891,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4922,45 +4922,53 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128103802</v>
+        <v>128103707</v>
       </c>
       <c r="B45" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>626806</v>
+        <v>626786</v>
       </c>
       <c r="R45" t="n">
-        <v>7217042</v>
+        <v>7217295</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4993,6 +5001,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5019,7 +5032,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128103707</v>
+        <v>128103708</v>
       </c>
       <c r="B46" t="n">
         <v>57672</v>
@@ -5052,7 +5065,7 @@
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -5062,10 +5075,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>626786</v>
+        <v>626743</v>
       </c>
       <c r="R46" t="n">
-        <v>7217295</v>
+        <v>7217219</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5102,7 +5115,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5129,53 +5142,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128103708</v>
+        <v>128103804</v>
       </c>
       <c r="B47" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>626743</v>
+        <v>626622</v>
       </c>
       <c r="R47" t="n">
-        <v>7217219</v>
+        <v>7217121</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5208,11 +5213,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Bohål</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5239,32 +5239,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128103732</v>
+        <v>128103802</v>
       </c>
       <c r="B48" t="n">
-        <v>98491</v>
+        <v>98470</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5274,10 +5274,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>626665</v>
+        <v>626806</v>
       </c>
       <c r="R48" t="n">
-        <v>7217113</v>
+        <v>7217042</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6015,32 +6015,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128103849</v>
+        <v>128103779</v>
       </c>
       <c r="B56" t="n">
-        <v>79029</v>
+        <v>80168</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6050,10 +6050,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>626701</v>
+        <v>626819</v>
       </c>
       <c r="R56" t="n">
-        <v>7217242</v>
+        <v>7217095</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6112,32 +6112,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128103779</v>
+        <v>128103849</v>
       </c>
       <c r="B57" t="n">
-        <v>80168</v>
+        <v>79029</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6147,10 +6147,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>626819</v>
+        <v>626701</v>
       </c>
       <c r="R57" t="n">
-        <v>7217095</v>
+        <v>7217242</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>

--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -4031,32 +4031,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128103749</v>
+        <v>128103800</v>
       </c>
       <c r="B36" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4066,10 +4066,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>626686</v>
+        <v>626843</v>
       </c>
       <c r="R36" t="n">
-        <v>7217075</v>
+        <v>7217062</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4128,7 +4128,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128103800</v>
+        <v>128103816</v>
       </c>
       <c r="B37" t="n">
         <v>98470</v>
@@ -4163,10 +4163,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>626843</v>
+        <v>626837</v>
       </c>
       <c r="R37" t="n">
-        <v>7217062</v>
+        <v>7217076</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4322,32 +4322,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128103816</v>
+        <v>128103749</v>
       </c>
       <c r="B39" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4357,10 +4357,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626837</v>
+        <v>626686</v>
       </c>
       <c r="R39" t="n">
-        <v>7217076</v>
+        <v>7217075</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4419,53 +4419,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128103709</v>
+        <v>128103776</v>
       </c>
       <c r="B40" t="n">
-        <v>57672</v>
+        <v>80168</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>626740</v>
+        <v>626665</v>
       </c>
       <c r="R40" t="n">
-        <v>7217219</v>
+        <v>7217186</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4498,11 +4490,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4529,45 +4516,53 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128103776</v>
+        <v>128103709</v>
       </c>
       <c r="B41" t="n">
-        <v>80168</v>
+        <v>57672</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>626665</v>
+        <v>626740</v>
       </c>
       <c r="R41" t="n">
-        <v>7217186</v>
+        <v>7217219</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4600,6 +4595,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -1871,32 +1871,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128103747</v>
+        <v>128103795</v>
       </c>
       <c r="B14" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626821</v>
+        <v>626797</v>
       </c>
       <c r="R14" t="n">
-        <v>7217089</v>
+        <v>7217132</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1968,32 +1968,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128103777</v>
+        <v>128103814</v>
       </c>
       <c r="B15" t="n">
-        <v>80168</v>
+        <v>98470</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626745</v>
+        <v>626811</v>
       </c>
       <c r="R15" t="n">
-        <v>7217253</v>
+        <v>7217114</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2065,32 +2065,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128103814</v>
+        <v>128103747</v>
       </c>
       <c r="B16" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626811</v>
+        <v>626821</v>
       </c>
       <c r="R16" t="n">
-        <v>7217114</v>
+        <v>7217089</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2162,32 +2162,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128103795</v>
+        <v>128103777</v>
       </c>
       <c r="B17" t="n">
-        <v>98470</v>
+        <v>80168</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626797</v>
+        <v>626745</v>
       </c>
       <c r="R17" t="n">
-        <v>7217132</v>
+        <v>7217253</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2466,32 +2466,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128103752</v>
+        <v>128103817</v>
       </c>
       <c r="B20" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2501,10 +2501,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626739</v>
+        <v>626705</v>
       </c>
       <c r="R20" t="n">
-        <v>7217280</v>
+        <v>7217045</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2563,32 +2563,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128103817</v>
+        <v>128103752</v>
       </c>
       <c r="B21" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626705</v>
+        <v>626739</v>
       </c>
       <c r="R21" t="n">
-        <v>7217045</v>
+        <v>7217280</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3727,45 +3727,53 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128103798</v>
+        <v>128103710</v>
       </c>
       <c r="B33" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>626811</v>
+        <v>626769</v>
       </c>
       <c r="R33" t="n">
-        <v>7217065</v>
+        <v>7217062</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3798,6 +3806,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3824,7 +3837,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128103799</v>
+        <v>128103798</v>
       </c>
       <c r="B34" t="n">
         <v>98470</v>
@@ -3859,10 +3872,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>626796</v>
+        <v>626811</v>
       </c>
       <c r="R34" t="n">
-        <v>7217064</v>
+        <v>7217065</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3921,53 +3934,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128103710</v>
+        <v>128103799</v>
       </c>
       <c r="B35" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>626769</v>
+        <v>626796</v>
       </c>
       <c r="R35" t="n">
-        <v>7217062</v>
+        <v>7217064</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4000,11 +4005,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -2466,32 +2466,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128103817</v>
+        <v>128103752</v>
       </c>
       <c r="B20" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2501,10 +2501,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626705</v>
+        <v>626739</v>
       </c>
       <c r="R20" t="n">
-        <v>7217045</v>
+        <v>7217280</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2563,32 +2563,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128103752</v>
+        <v>128103817</v>
       </c>
       <c r="B21" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626739</v>
+        <v>626705</v>
       </c>
       <c r="R21" t="n">
-        <v>7217280</v>
+        <v>7217045</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -4031,32 +4031,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128103800</v>
+        <v>128103749</v>
       </c>
       <c r="B36" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4066,10 +4066,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>626843</v>
+        <v>626686</v>
       </c>
       <c r="R36" t="n">
-        <v>7217062</v>
+        <v>7217075</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4128,7 +4128,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128103816</v>
+        <v>128103800</v>
       </c>
       <c r="B37" t="n">
         <v>98470</v>
@@ -4163,10 +4163,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>626837</v>
+        <v>626843</v>
       </c>
       <c r="R37" t="n">
-        <v>7217076</v>
+        <v>7217062</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4322,32 +4322,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128103749</v>
+        <v>128103816</v>
       </c>
       <c r="B39" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4357,10 +4357,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626686</v>
+        <v>626837</v>
       </c>
       <c r="R39" t="n">
-        <v>7217075</v>
+        <v>7217076</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -6015,32 +6015,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128103779</v>
+        <v>128103849</v>
       </c>
       <c r="B56" t="n">
-        <v>80168</v>
+        <v>79029</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6050,10 +6050,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>626819</v>
+        <v>626701</v>
       </c>
       <c r="R56" t="n">
-        <v>7217095</v>
+        <v>7217242</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6112,32 +6112,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128103849</v>
+        <v>128103779</v>
       </c>
       <c r="B57" t="n">
-        <v>79029</v>
+        <v>80168</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6147,10 +6147,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>626701</v>
+        <v>626819</v>
       </c>
       <c r="R57" t="n">
-        <v>7217242</v>
+        <v>7217095</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>

--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128103750</v>
+        <v>128103821</v>
       </c>
       <c r="B2" t="n">
-        <v>80132</v>
+        <v>98478</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626688</v>
+        <v>626754</v>
       </c>
       <c r="R2" t="n">
-        <v>7217164</v>
+        <v>7217270</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128103748</v>
+        <v>128103750</v>
       </c>
       <c r="B3" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626663</v>
+        <v>626688</v>
       </c>
       <c r="R3" t="n">
-        <v>7217050</v>
+        <v>7217164</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128103715</v>
+        <v>128103748</v>
       </c>
       <c r="B4" t="n">
-        <v>57672</v>
+        <v>80135</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,42 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626715</v>
+        <v>626663</v>
       </c>
       <c r="R4" t="n">
-        <v>7217390</v>
+        <v>7217050</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färsk</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128103712</v>
+        <v>128103715</v>
       </c>
       <c r="B5" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,7 +999,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1022,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626667</v>
+        <v>626715</v>
       </c>
       <c r="R5" t="n">
-        <v>7217072</v>
+        <v>7217390</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,7 +1049,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Bohål</t>
+          <t>Färsk</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,45 +1076,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128103821</v>
+        <v>128103712</v>
       </c>
       <c r="B6" t="n">
-        <v>98470</v>
+        <v>57673</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626754</v>
+        <v>626667</v>
       </c>
       <c r="R6" t="n">
-        <v>7217270</v>
+        <v>7217072</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,6 +1155,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1189,7 +1189,7 @@
         <v>128103815</v>
       </c>
       <c r="B7" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>128103803</v>
       </c>
       <c r="B8" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>128103861</v>
       </c>
       <c r="B9" t="n">
-        <v>91926</v>
+        <v>91934</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>128103760</v>
       </c>
       <c r="B10" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>128103778</v>
       </c>
       <c r="B11" t="n">
-        <v>80168</v>
+        <v>80171</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>128103854</v>
       </c>
       <c r="B12" t="n">
-        <v>82870</v>
+        <v>82873</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1774,32 +1774,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128103738</v>
+        <v>128103814</v>
       </c>
       <c r="B13" t="n">
-        <v>80133</v>
+        <v>98478</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626739</v>
+        <v>626811</v>
       </c>
       <c r="R13" t="n">
-        <v>7217280</v>
+        <v>7217114</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1874,7 +1874,7 @@
         <v>128103795</v>
       </c>
       <c r="B14" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1968,32 +1968,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128103814</v>
+        <v>128103747</v>
       </c>
       <c r="B15" t="n">
-        <v>98470</v>
+        <v>80135</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626811</v>
+        <v>626821</v>
       </c>
       <c r="R15" t="n">
-        <v>7217114</v>
+        <v>7217089</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2065,32 +2065,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128103747</v>
+        <v>128103777</v>
       </c>
       <c r="B16" t="n">
-        <v>80132</v>
+        <v>80171</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626821</v>
+        <v>626745</v>
       </c>
       <c r="R16" t="n">
-        <v>7217089</v>
+        <v>7217253</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2162,32 +2162,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128103777</v>
+        <v>128103738</v>
       </c>
       <c r="B17" t="n">
-        <v>80168</v>
+        <v>80136</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626745</v>
+        <v>626739</v>
       </c>
       <c r="R17" t="n">
-        <v>7217253</v>
+        <v>7217280</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2262,7 +2262,7 @@
         <v>128103714</v>
       </c>
       <c r="B18" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>128103820</v>
       </c>
       <c r="B19" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>128103752</v>
       </c>
       <c r="B20" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>128103817</v>
       </c>
       <c r="B21" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>128103780</v>
       </c>
       <c r="B22" t="n">
-        <v>80168</v>
+        <v>80171</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>128103775</v>
       </c>
       <c r="B23" t="n">
-        <v>80168</v>
+        <v>80171</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>128103693</v>
       </c>
       <c r="B24" t="n">
-        <v>79647</v>
+        <v>79650</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>128103805</v>
       </c>
       <c r="B25" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3048,32 +3048,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128103691</v>
+        <v>128103864</v>
       </c>
       <c r="B26" t="n">
-        <v>79061</v>
+        <v>80170</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>185</v>
+        <v>6463</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>626657</v>
+        <v>626755</v>
       </c>
       <c r="R26" t="n">
-        <v>7217200</v>
+        <v>7217274</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3145,32 +3145,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128103864</v>
+        <v>128103751</v>
       </c>
       <c r="B27" t="n">
-        <v>80167</v>
+        <v>80135</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>626755</v>
+        <v>626665</v>
       </c>
       <c r="R27" t="n">
-        <v>7217274</v>
+        <v>7217186</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3242,10 +3242,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128103751</v>
+        <v>128103691</v>
       </c>
       <c r="B28" t="n">
-        <v>80132</v>
+        <v>79064</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3253,21 +3253,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3277,10 +3277,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>626665</v>
+        <v>626657</v>
       </c>
       <c r="R28" t="n">
-        <v>7217186</v>
+        <v>7217200</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3339,32 +3339,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128103862</v>
+        <v>128103873</v>
       </c>
       <c r="B29" t="n">
-        <v>80167</v>
+        <v>78438</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6463</v>
+        <v>6437</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3374,10 +3374,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>626687</v>
+        <v>626652</v>
       </c>
       <c r="R29" t="n">
-        <v>7217145</v>
+        <v>7217184</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3436,32 +3436,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128103873</v>
+        <v>128103862</v>
       </c>
       <c r="B30" t="n">
-        <v>78435</v>
+        <v>80170</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6437</v>
+        <v>6463</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>626652</v>
+        <v>626687</v>
       </c>
       <c r="R30" t="n">
-        <v>7217184</v>
+        <v>7217145</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3533,27 +3533,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128103865</v>
+        <v>128103846</v>
       </c>
       <c r="B31" t="n">
-        <v>80167</v>
+        <v>79032</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3568,10 +3568,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>626739</v>
+        <v>626685</v>
       </c>
       <c r="R31" t="n">
-        <v>7217280</v>
+        <v>7217148</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3630,27 +3630,27 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128103846</v>
+        <v>128103865</v>
       </c>
       <c r="B32" t="n">
-        <v>79029</v>
+        <v>80170</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3665,10 +3665,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>626685</v>
+        <v>626739</v>
       </c>
       <c r="R32" t="n">
-        <v>7217148</v>
+        <v>7217280</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3727,53 +3727,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128103710</v>
+        <v>128103798</v>
       </c>
       <c r="B33" t="n">
-        <v>57672</v>
+        <v>98478</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>626769</v>
+        <v>626811</v>
       </c>
       <c r="R33" t="n">
-        <v>7217062</v>
+        <v>7217065</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3806,11 +3798,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3837,10 +3824,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128103798</v>
+        <v>128103799</v>
       </c>
       <c r="B34" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3872,10 +3859,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>626811</v>
+        <v>626796</v>
       </c>
       <c r="R34" t="n">
-        <v>7217065</v>
+        <v>7217064</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3934,45 +3921,53 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128103799</v>
+        <v>128103710</v>
       </c>
       <c r="B35" t="n">
-        <v>98470</v>
+        <v>57673</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>626796</v>
+        <v>626769</v>
       </c>
       <c r="R35" t="n">
-        <v>7217064</v>
+        <v>7217062</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4005,6 +4000,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4031,10 +4031,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128103749</v>
+        <v>128103789</v>
       </c>
       <c r="B36" t="n">
-        <v>80132</v>
+        <v>78790</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4042,21 +4042,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4066,10 +4066,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>626686</v>
+        <v>626633</v>
       </c>
       <c r="R36" t="n">
-        <v>7217075</v>
+        <v>7217153</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4128,32 +4128,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128103800</v>
+        <v>128103749</v>
       </c>
       <c r="B37" t="n">
-        <v>98470</v>
+        <v>80135</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4163,10 +4163,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>626843</v>
+        <v>626686</v>
       </c>
       <c r="R37" t="n">
-        <v>7217062</v>
+        <v>7217075</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4225,32 +4225,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128103789</v>
+        <v>128103800</v>
       </c>
       <c r="B38" t="n">
-        <v>78787</v>
+        <v>98478</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4260,10 +4260,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626633</v>
+        <v>626843</v>
       </c>
       <c r="R38" t="n">
-        <v>7217153</v>
+        <v>7217062</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4325,7 +4325,7 @@
         <v>128103816</v>
       </c>
       <c r="B39" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4419,45 +4419,53 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128103776</v>
+        <v>128103709</v>
       </c>
       <c r="B40" t="n">
-        <v>80168</v>
+        <v>57673</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>626665</v>
+        <v>626740</v>
       </c>
       <c r="R40" t="n">
-        <v>7217186</v>
+        <v>7217219</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4490,6 +4498,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4516,53 +4529,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128103709</v>
+        <v>128103776</v>
       </c>
       <c r="B41" t="n">
-        <v>57672</v>
+        <v>80171</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>626740</v>
+        <v>626665</v>
       </c>
       <c r="R41" t="n">
-        <v>7217219</v>
+        <v>7217186</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4595,11 +4600,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4626,32 +4626,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128103841</v>
+        <v>128103732</v>
       </c>
       <c r="B42" t="n">
-        <v>79029</v>
+        <v>98499</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4661,10 +4661,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>626739</v>
+        <v>626665</v>
       </c>
       <c r="R42" t="n">
-        <v>7217304</v>
+        <v>7217113</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4723,32 +4723,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128103847</v>
+        <v>128103804</v>
       </c>
       <c r="B43" t="n">
-        <v>79029</v>
+        <v>98478</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4758,10 +4758,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>626677</v>
+        <v>626622</v>
       </c>
       <c r="R43" t="n">
-        <v>7217181</v>
+        <v>7217121</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4794,11 +4794,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4825,10 +4820,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128103804</v>
+        <v>128103802</v>
       </c>
       <c r="B44" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4860,10 +4855,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>626622</v>
+        <v>626806</v>
       </c>
       <c r="R44" t="n">
-        <v>7217121</v>
+        <v>7217042</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4922,32 +4917,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128103802</v>
+        <v>128103841</v>
       </c>
       <c r="B45" t="n">
-        <v>98470</v>
+        <v>79032</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4957,10 +4952,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>626806</v>
+        <v>626739</v>
       </c>
       <c r="R45" t="n">
-        <v>7217042</v>
+        <v>7217304</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5019,10 +5014,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128103707</v>
+        <v>128103847</v>
       </c>
       <c r="B46" t="n">
-        <v>57672</v>
+        <v>79032</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5030,42 +5025,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>626786</v>
+        <v>626677</v>
       </c>
       <c r="R46" t="n">
-        <v>7217295</v>
+        <v>7217181</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5102,7 +5089,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5129,10 +5116,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128103708</v>
+        <v>128103707</v>
       </c>
       <c r="B47" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5162,7 +5149,7 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -5172,10 +5159,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>626743</v>
+        <v>626786</v>
       </c>
       <c r="R47" t="n">
-        <v>7217219</v>
+        <v>7217295</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5212,7 +5199,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Bohål</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5239,45 +5226,53 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128103732</v>
+        <v>128103708</v>
       </c>
       <c r="B48" t="n">
-        <v>98491</v>
+        <v>57673</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>626665</v>
+        <v>626743</v>
       </c>
       <c r="R48" t="n">
-        <v>7217113</v>
+        <v>7217219</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5310,6 +5305,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5339,7 +5339,7 @@
         <v>128103840</v>
       </c>
       <c r="B49" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5436,7 +5436,7 @@
         <v>128103790</v>
       </c>
       <c r="B50" t="n">
-        <v>78787</v>
+        <v>78790</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>128103848</v>
       </c>
       <c r="B51" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5627,32 +5627,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128103796</v>
+        <v>128103855</v>
       </c>
       <c r="B52" t="n">
-        <v>98470</v>
+        <v>82873</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5662,10 +5662,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>626803</v>
+        <v>626723</v>
       </c>
       <c r="R52" t="n">
-        <v>7217099</v>
+        <v>7217326</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5724,10 +5724,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128103797</v>
+        <v>128103796</v>
       </c>
       <c r="B53" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5759,10 +5759,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>626820</v>
+        <v>626803</v>
       </c>
       <c r="R53" t="n">
-        <v>7217037</v>
+        <v>7217099</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5821,32 +5821,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128103855</v>
+        <v>128103797</v>
       </c>
       <c r="B54" t="n">
-        <v>82870</v>
+        <v>98478</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5856,10 +5856,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>626723</v>
+        <v>626820</v>
       </c>
       <c r="R54" t="n">
-        <v>7217326</v>
+        <v>7217037</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5921,7 +5921,7 @@
         <v>128103726</v>
       </c>
       <c r="B55" t="n">
-        <v>80161</v>
+        <v>80164</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
         <v>128103849</v>
       </c>
       <c r="B56" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>128103779</v>
       </c>
       <c r="B57" t="n">
-        <v>80168</v>
+        <v>80171</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>128103713</v>
       </c>
       <c r="B58" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>128103818</v>
       </c>
       <c r="B59" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -4626,32 +4626,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128103732</v>
+        <v>128103804</v>
       </c>
       <c r="B42" t="n">
-        <v>98499</v>
+        <v>98478</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4661,10 +4661,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>626665</v>
+        <v>626622</v>
       </c>
       <c r="R42" t="n">
-        <v>7217113</v>
+        <v>7217121</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4723,7 +4723,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128103804</v>
+        <v>128103802</v>
       </c>
       <c r="B43" t="n">
         <v>98478</v>
@@ -4758,10 +4758,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>626622</v>
+        <v>626806</v>
       </c>
       <c r="R43" t="n">
-        <v>7217121</v>
+        <v>7217042</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4820,32 +4820,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128103802</v>
+        <v>128103732</v>
       </c>
       <c r="B44" t="n">
-        <v>98478</v>
+        <v>98499</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4855,10 +4855,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>626806</v>
+        <v>626665</v>
       </c>
       <c r="R44" t="n">
-        <v>7217042</v>
+        <v>7217113</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128103821</v>
+        <v>128103750</v>
       </c>
       <c r="B2" t="n">
-        <v>98478</v>
+        <v>80188</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626754</v>
+        <v>626688</v>
       </c>
       <c r="R2" t="n">
-        <v>7217270</v>
+        <v>7217164</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128103750</v>
+        <v>128103748</v>
       </c>
       <c r="B3" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626688</v>
+        <v>626663</v>
       </c>
       <c r="R3" t="n">
-        <v>7217164</v>
+        <v>7217050</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128103748</v>
+        <v>128103821</v>
       </c>
       <c r="B4" t="n">
-        <v>80135</v>
+        <v>98571</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626663</v>
+        <v>626754</v>
       </c>
       <c r="R4" t="n">
-        <v>7217050</v>
+        <v>7217270</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>128103715</v>
       </c>
       <c r="B5" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>128103712</v>
       </c>
       <c r="B6" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,10 +1186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128103815</v>
+        <v>128103861</v>
       </c>
       <c r="B7" t="n">
-        <v>98478</v>
+        <v>92026</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1197,21 +1197,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1221,10 +1221,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626821</v>
+        <v>626733</v>
       </c>
       <c r="R7" t="n">
-        <v>7217074</v>
+        <v>7217284</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1259,12 +1259,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Bild</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1283,10 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128103803</v>
+        <v>128103815</v>
       </c>
       <c r="B8" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626709</v>
+        <v>626821</v>
       </c>
       <c r="R8" t="n">
-        <v>7217057</v>
+        <v>7217074</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1380,10 +1386,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128103861</v>
+        <v>128103803</v>
       </c>
       <c r="B9" t="n">
-        <v>91934</v>
+        <v>98571</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1391,21 +1397,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1415,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626733</v>
+        <v>626709</v>
       </c>
       <c r="R9" t="n">
-        <v>7217284</v>
+        <v>7217057</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1453,18 +1459,12 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Bild</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1486,7 +1486,7 @@
         <v>128103760</v>
       </c>
       <c r="B10" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>128103778</v>
       </c>
       <c r="B11" t="n">
-        <v>80171</v>
+        <v>80224</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>128103854</v>
       </c>
       <c r="B12" t="n">
-        <v>82873</v>
+        <v>82942</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1774,32 +1774,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128103814</v>
+        <v>128103747</v>
       </c>
       <c r="B13" t="n">
-        <v>98478</v>
+        <v>80188</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626811</v>
+        <v>626821</v>
       </c>
       <c r="R13" t="n">
-        <v>7217114</v>
+        <v>7217089</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1871,32 +1871,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128103795</v>
+        <v>128103777</v>
       </c>
       <c r="B14" t="n">
-        <v>98478</v>
+        <v>80224</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626797</v>
+        <v>626745</v>
       </c>
       <c r="R14" t="n">
-        <v>7217132</v>
+        <v>7217253</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1968,10 +1968,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128103747</v>
+        <v>128103738</v>
       </c>
       <c r="B15" t="n">
-        <v>80135</v>
+        <v>80189</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1979,21 +1979,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626821</v>
+        <v>626739</v>
       </c>
       <c r="R15" t="n">
-        <v>7217089</v>
+        <v>7217280</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2065,32 +2065,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128103777</v>
+        <v>128103814</v>
       </c>
       <c r="B16" t="n">
-        <v>80171</v>
+        <v>98571</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626745</v>
+        <v>626811</v>
       </c>
       <c r="R16" t="n">
-        <v>7217253</v>
+        <v>7217114</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2162,32 +2162,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128103738</v>
+        <v>128103795</v>
       </c>
       <c r="B17" t="n">
-        <v>80136</v>
+        <v>98571</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626739</v>
+        <v>626797</v>
       </c>
       <c r="R17" t="n">
-        <v>7217280</v>
+        <v>7217132</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2262,7 +2262,7 @@
         <v>128103714</v>
       </c>
       <c r="B18" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>128103820</v>
       </c>
       <c r="B19" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>128103752</v>
       </c>
       <c r="B20" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>128103817</v>
       </c>
       <c r="B21" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>128103780</v>
       </c>
       <c r="B22" t="n">
-        <v>80171</v>
+        <v>80224</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>128103775</v>
       </c>
       <c r="B23" t="n">
-        <v>80171</v>
+        <v>80224</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>128103693</v>
       </c>
       <c r="B24" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>128103805</v>
       </c>
       <c r="B25" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3048,32 +3048,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128103864</v>
+        <v>128103691</v>
       </c>
       <c r="B26" t="n">
-        <v>80170</v>
+        <v>79115</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6463</v>
+        <v>185</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>626755</v>
+        <v>626657</v>
       </c>
       <c r="R26" t="n">
-        <v>7217274</v>
+        <v>7217200</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3145,32 +3145,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128103751</v>
+        <v>128103864</v>
       </c>
       <c r="B27" t="n">
-        <v>80135</v>
+        <v>80223</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>626665</v>
+        <v>626755</v>
       </c>
       <c r="R27" t="n">
-        <v>7217186</v>
+        <v>7217274</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3242,10 +3242,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128103691</v>
+        <v>128103751</v>
       </c>
       <c r="B28" t="n">
-        <v>79064</v>
+        <v>80188</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3253,21 +3253,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3277,10 +3277,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>626657</v>
+        <v>626665</v>
       </c>
       <c r="R28" t="n">
-        <v>7217200</v>
+        <v>7217186</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3339,32 +3339,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128103873</v>
+        <v>128103862</v>
       </c>
       <c r="B29" t="n">
-        <v>78438</v>
+        <v>80223</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6437</v>
+        <v>6463</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3374,10 +3374,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>626652</v>
+        <v>626687</v>
       </c>
       <c r="R29" t="n">
-        <v>7217184</v>
+        <v>7217145</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3436,32 +3436,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128103862</v>
+        <v>128103873</v>
       </c>
       <c r="B30" t="n">
-        <v>80170</v>
+        <v>78486</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6463</v>
+        <v>6437</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>626687</v>
+        <v>626652</v>
       </c>
       <c r="R30" t="n">
-        <v>7217145</v>
+        <v>7217184</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3536,7 +3536,7 @@
         <v>128103846</v>
       </c>
       <c r="B31" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>128103865</v>
       </c>
       <c r="B32" t="n">
-        <v>80170</v>
+        <v>80223</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>128103798</v>
       </c>
       <c r="B33" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>128103799</v>
       </c>
       <c r="B34" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>128103710</v>
       </c>
       <c r="B35" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4031,10 +4031,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128103789</v>
+        <v>128103749</v>
       </c>
       <c r="B36" t="n">
-        <v>78790</v>
+        <v>80188</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4042,21 +4042,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4066,10 +4066,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>626633</v>
+        <v>626686</v>
       </c>
       <c r="R36" t="n">
-        <v>7217153</v>
+        <v>7217075</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4128,10 +4128,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128103749</v>
+        <v>128103789</v>
       </c>
       <c r="B37" t="n">
-        <v>80135</v>
+        <v>78840</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4139,21 +4139,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4163,10 +4163,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>626686</v>
+        <v>626633</v>
       </c>
       <c r="R37" t="n">
-        <v>7217075</v>
+        <v>7217153</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4228,7 +4228,7 @@
         <v>128103800</v>
       </c>
       <c r="B38" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>128103816</v>
       </c>
       <c r="B39" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4419,53 +4419,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128103709</v>
+        <v>128103776</v>
       </c>
       <c r="B40" t="n">
-        <v>57673</v>
+        <v>80224</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>626740</v>
+        <v>626665</v>
       </c>
       <c r="R40" t="n">
-        <v>7217219</v>
+        <v>7217186</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4498,11 +4490,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4529,45 +4516,53 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128103776</v>
+        <v>128103709</v>
       </c>
       <c r="B41" t="n">
-        <v>80171</v>
+        <v>57685</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>626665</v>
+        <v>626740</v>
       </c>
       <c r="R41" t="n">
-        <v>7217186</v>
+        <v>7217219</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4600,6 +4595,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4626,32 +4626,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128103804</v>
+        <v>128103841</v>
       </c>
       <c r="B42" t="n">
-        <v>98478</v>
+        <v>79083</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4661,10 +4661,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>626622</v>
+        <v>626739</v>
       </c>
       <c r="R42" t="n">
-        <v>7217121</v>
+        <v>7217304</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4723,32 +4723,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128103802</v>
+        <v>128103847</v>
       </c>
       <c r="B43" t="n">
-        <v>98478</v>
+        <v>79083</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4758,10 +4758,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>626806</v>
+        <v>626677</v>
       </c>
       <c r="R43" t="n">
-        <v>7217042</v>
+        <v>7217181</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4794,6 +4794,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4820,45 +4825,53 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128103732</v>
+        <v>128103707</v>
       </c>
       <c r="B44" t="n">
-        <v>98499</v>
+        <v>57685</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>626665</v>
+        <v>626786</v>
       </c>
       <c r="R44" t="n">
-        <v>7217113</v>
+        <v>7217295</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4891,6 +4904,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4917,10 +4935,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128103841</v>
+        <v>128103708</v>
       </c>
       <c r="B45" t="n">
-        <v>79032</v>
+        <v>57685</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4928,34 +4946,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>626739</v>
+        <v>626743</v>
       </c>
       <c r="R45" t="n">
-        <v>7217304</v>
+        <v>7217219</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4988,6 +5014,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5014,32 +5045,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128103847</v>
+        <v>128103732</v>
       </c>
       <c r="B46" t="n">
-        <v>79032</v>
+        <v>98592</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5049,10 +5080,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>626677</v>
+        <v>626665</v>
       </c>
       <c r="R46" t="n">
-        <v>7217181</v>
+        <v>7217113</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5085,11 +5116,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5116,53 +5142,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128103707</v>
+        <v>128103804</v>
       </c>
       <c r="B47" t="n">
-        <v>57673</v>
+        <v>98571</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>626786</v>
+        <v>626622</v>
       </c>
       <c r="R47" t="n">
-        <v>7217295</v>
+        <v>7217121</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5195,11 +5213,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5226,53 +5239,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128103708</v>
+        <v>128103802</v>
       </c>
       <c r="B48" t="n">
-        <v>57673</v>
+        <v>98571</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>626743</v>
+        <v>626806</v>
       </c>
       <c r="R48" t="n">
-        <v>7217219</v>
+        <v>7217042</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5305,11 +5310,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Bohål</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5339,7 +5339,7 @@
         <v>128103840</v>
       </c>
       <c r="B49" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5436,7 +5436,7 @@
         <v>128103790</v>
       </c>
       <c r="B50" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>128103848</v>
       </c>
       <c r="B51" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>128103855</v>
       </c>
       <c r="B52" t="n">
-        <v>82873</v>
+        <v>82942</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5724,32 +5724,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128103796</v>
+        <v>128103779</v>
       </c>
       <c r="B53" t="n">
-        <v>98478</v>
+        <v>80224</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5759,10 +5759,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>626803</v>
+        <v>626819</v>
       </c>
       <c r="R53" t="n">
-        <v>7217099</v>
+        <v>7217095</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5821,32 +5821,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128103797</v>
+        <v>128103849</v>
       </c>
       <c r="B54" t="n">
-        <v>98478</v>
+        <v>79083</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5856,10 +5856,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>626820</v>
+        <v>626701</v>
       </c>
       <c r="R54" t="n">
-        <v>7217037</v>
+        <v>7217242</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5918,45 +5918,53 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128103726</v>
+        <v>128103713</v>
       </c>
       <c r="B55" t="n">
-        <v>80164</v>
+        <v>57685</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>626745</v>
+        <v>626703</v>
       </c>
       <c r="R55" t="n">
-        <v>7217244</v>
+        <v>7217299</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5989,6 +5997,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6015,32 +6028,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128103849</v>
+        <v>128103726</v>
       </c>
       <c r="B56" t="n">
-        <v>79032</v>
+        <v>80217</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6050,10 +6063,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>626701</v>
+        <v>626745</v>
       </c>
       <c r="R56" t="n">
-        <v>7217242</v>
+        <v>7217244</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6112,32 +6125,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128103779</v>
+        <v>128103796</v>
       </c>
       <c r="B57" t="n">
-        <v>80171</v>
+        <v>98571</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6147,10 +6160,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>626819</v>
+        <v>626803</v>
       </c>
       <c r="R57" t="n">
-        <v>7217095</v>
+        <v>7217099</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6209,53 +6222,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128103713</v>
+        <v>128103797</v>
       </c>
       <c r="B58" t="n">
-        <v>57673</v>
+        <v>98571</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>626703</v>
+        <v>626820</v>
       </c>
       <c r="R58" t="n">
-        <v>7217299</v>
+        <v>7217037</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6288,11 +6293,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6322,7 +6322,7 @@
         <v>128103818</v>
       </c>
       <c r="B59" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128103750</v>
+        <v>128103821</v>
       </c>
       <c r="B2" t="n">
-        <v>80188</v>
+        <v>98571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626688</v>
+        <v>626754</v>
       </c>
       <c r="R2" t="n">
-        <v>7217164</v>
+        <v>7217270</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128103821</v>
+        <v>128103750</v>
       </c>
       <c r="B4" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626754</v>
+        <v>626688</v>
       </c>
       <c r="R4" t="n">
-        <v>7217270</v>
+        <v>7217164</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1774,10 +1774,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128103747</v>
+        <v>128103738</v>
       </c>
       <c r="B13" t="n">
-        <v>80188</v>
+        <v>80189</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1785,21 +1785,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626821</v>
+        <v>626739</v>
       </c>
       <c r="R13" t="n">
-        <v>7217089</v>
+        <v>7217280</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1968,10 +1968,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128103738</v>
+        <v>128103747</v>
       </c>
       <c r="B15" t="n">
-        <v>80189</v>
+        <v>80188</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1979,21 +1979,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626739</v>
+        <v>626821</v>
       </c>
       <c r="R15" t="n">
-        <v>7217280</v>
+        <v>7217089</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2466,32 +2466,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128103752</v>
+        <v>128103817</v>
       </c>
       <c r="B20" t="n">
-        <v>80188</v>
+        <v>98571</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2501,10 +2501,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626739</v>
+        <v>626705</v>
       </c>
       <c r="R20" t="n">
-        <v>7217280</v>
+        <v>7217045</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2563,32 +2563,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128103817</v>
+        <v>128103752</v>
       </c>
       <c r="B21" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626705</v>
+        <v>626739</v>
       </c>
       <c r="R21" t="n">
-        <v>7217045</v>
+        <v>7217280</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2854,32 +2854,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128103693</v>
+        <v>128103805</v>
       </c>
       <c r="B24" t="n">
-        <v>79702</v>
+        <v>98571</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626633</v>
+        <v>626744</v>
       </c>
       <c r="R24" t="n">
-        <v>7217153</v>
+        <v>7217285</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2951,32 +2951,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128103805</v>
+        <v>128103693</v>
       </c>
       <c r="B25" t="n">
-        <v>98571</v>
+        <v>79702</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2986,10 +2986,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>626744</v>
+        <v>626633</v>
       </c>
       <c r="R25" t="n">
-        <v>7217285</v>
+        <v>7217153</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3145,32 +3145,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128103864</v>
+        <v>128103751</v>
       </c>
       <c r="B27" t="n">
-        <v>80223</v>
+        <v>80188</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>626755</v>
+        <v>626665</v>
       </c>
       <c r="R27" t="n">
-        <v>7217274</v>
+        <v>7217186</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3242,32 +3242,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128103751</v>
+        <v>128103864</v>
       </c>
       <c r="B28" t="n">
-        <v>80188</v>
+        <v>80223</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3277,10 +3277,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>626665</v>
+        <v>626755</v>
       </c>
       <c r="R28" t="n">
-        <v>7217186</v>
+        <v>7217274</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3727,45 +3727,53 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128103798</v>
+        <v>128103710</v>
       </c>
       <c r="B33" t="n">
-        <v>98571</v>
+        <v>57685</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>626811</v>
+        <v>626769</v>
       </c>
       <c r="R33" t="n">
-        <v>7217065</v>
+        <v>7217062</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3798,6 +3806,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3824,7 +3837,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128103799</v>
+        <v>128103798</v>
       </c>
       <c r="B34" t="n">
         <v>98571</v>
@@ -3859,10 +3872,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>626796</v>
+        <v>626811</v>
       </c>
       <c r="R34" t="n">
-        <v>7217064</v>
+        <v>7217065</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3921,53 +3934,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128103710</v>
+        <v>128103799</v>
       </c>
       <c r="B35" t="n">
-        <v>57685</v>
+        <v>98571</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>626769</v>
+        <v>626796</v>
       </c>
       <c r="R35" t="n">
-        <v>7217062</v>
+        <v>7217064</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4000,11 +4005,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4626,7 +4626,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128103841</v>
+        <v>128103847</v>
       </c>
       <c r="B42" t="n">
         <v>79083</v>
@@ -4661,10 +4661,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>626739</v>
+        <v>626677</v>
       </c>
       <c r="R42" t="n">
-        <v>7217304</v>
+        <v>7217181</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4697,6 +4697,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4723,7 +4728,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128103847</v>
+        <v>128103841</v>
       </c>
       <c r="B43" t="n">
         <v>79083</v>
@@ -4758,10 +4763,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>626677</v>
+        <v>626739</v>
       </c>
       <c r="R43" t="n">
-        <v>7217181</v>
+        <v>7217304</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4794,11 +4799,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5336,7 +5336,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128103840</v>
+        <v>128103848</v>
       </c>
       <c r="B49" t="n">
         <v>79083</v>
@@ -5371,10 +5371,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>626757</v>
+        <v>626660</v>
       </c>
       <c r="R49" t="n">
-        <v>7217294</v>
+        <v>7217210</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5530,7 +5530,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128103848</v>
+        <v>128103840</v>
       </c>
       <c r="B51" t="n">
         <v>79083</v>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>626660</v>
+        <v>626757</v>
       </c>
       <c r="R51" t="n">
-        <v>7217210</v>
+        <v>7217294</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5627,32 +5627,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128103855</v>
+        <v>128103796</v>
       </c>
       <c r="B52" t="n">
-        <v>82942</v>
+        <v>98571</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5662,10 +5662,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>626723</v>
+        <v>626803</v>
       </c>
       <c r="R52" t="n">
-        <v>7217326</v>
+        <v>7217099</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5724,32 +5724,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128103779</v>
+        <v>128103855</v>
       </c>
       <c r="B53" t="n">
-        <v>80224</v>
+        <v>82942</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5759,10 +5759,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>626819</v>
+        <v>626723</v>
       </c>
       <c r="R53" t="n">
-        <v>7217095</v>
+        <v>7217326</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5918,53 +5918,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128103713</v>
+        <v>128103726</v>
       </c>
       <c r="B55" t="n">
-        <v>57685</v>
+        <v>80217</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>626703</v>
+        <v>626745</v>
       </c>
       <c r="R55" t="n">
-        <v>7217299</v>
+        <v>7217244</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5997,11 +5989,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6028,10 +6015,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128103726</v>
+        <v>128103779</v>
       </c>
       <c r="B56" t="n">
-        <v>80217</v>
+        <v>80224</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6039,21 +6026,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6063,10 +6050,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>626745</v>
+        <v>626819</v>
       </c>
       <c r="R56" t="n">
-        <v>7217244</v>
+        <v>7217095</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6125,45 +6112,53 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128103796</v>
+        <v>128103713</v>
       </c>
       <c r="B57" t="n">
-        <v>98571</v>
+        <v>57685</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>626803</v>
+        <v>626703</v>
       </c>
       <c r="R57" t="n">
-        <v>7217099</v>
+        <v>7217299</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6196,6 +6191,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128103821</v>
+        <v>128103750</v>
       </c>
       <c r="B2" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626754</v>
+        <v>626688</v>
       </c>
       <c r="R2" t="n">
-        <v>7217270</v>
+        <v>7217164</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128103750</v>
+        <v>128103715</v>
       </c>
       <c r="B4" t="n">
-        <v>80188</v>
+        <v>57685</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +880,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626688</v>
+        <v>626715</v>
       </c>
       <c r="R4" t="n">
-        <v>7217164</v>
+        <v>7217390</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,6 +948,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färsk</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,7 +979,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128103715</v>
+        <v>128103712</v>
       </c>
       <c r="B5" t="n">
         <v>57685</v>
@@ -999,7 +1012,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1009,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626715</v>
+        <v>626667</v>
       </c>
       <c r="R5" t="n">
-        <v>7217390</v>
+        <v>7217072</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1049,7 +1062,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färsk</t>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,53 +1089,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128103712</v>
+        <v>128103821</v>
       </c>
       <c r="B6" t="n">
-        <v>57685</v>
+        <v>98571</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626667</v>
+        <v>626754</v>
       </c>
       <c r="R6" t="n">
-        <v>7217072</v>
+        <v>7217270</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1155,11 +1160,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Bohål</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1774,32 +1774,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128103738</v>
+        <v>128103814</v>
       </c>
       <c r="B13" t="n">
-        <v>80189</v>
+        <v>98571</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626739</v>
+        <v>626811</v>
       </c>
       <c r="R13" t="n">
-        <v>7217280</v>
+        <v>7217114</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1871,32 +1871,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128103777</v>
+        <v>128103795</v>
       </c>
       <c r="B14" t="n">
-        <v>80224</v>
+        <v>98571</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626745</v>
+        <v>626797</v>
       </c>
       <c r="R14" t="n">
-        <v>7217253</v>
+        <v>7217132</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1968,10 +1968,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128103747</v>
+        <v>128103738</v>
       </c>
       <c r="B15" t="n">
-        <v>80188</v>
+        <v>80189</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1979,21 +1979,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626821</v>
+        <v>626739</v>
       </c>
       <c r="R15" t="n">
-        <v>7217089</v>
+        <v>7217280</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2065,32 +2065,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128103814</v>
+        <v>128103747</v>
       </c>
       <c r="B16" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626811</v>
+        <v>626821</v>
       </c>
       <c r="R16" t="n">
-        <v>7217114</v>
+        <v>7217089</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2162,32 +2162,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128103795</v>
+        <v>128103777</v>
       </c>
       <c r="B17" t="n">
-        <v>98571</v>
+        <v>80224</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626797</v>
+        <v>626745</v>
       </c>
       <c r="R17" t="n">
-        <v>7217132</v>
+        <v>7217253</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2854,32 +2854,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128103805</v>
+        <v>128103693</v>
       </c>
       <c r="B24" t="n">
-        <v>98571</v>
+        <v>79702</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626744</v>
+        <v>626633</v>
       </c>
       <c r="R24" t="n">
-        <v>7217285</v>
+        <v>7217153</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2951,32 +2951,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128103693</v>
+        <v>128103805</v>
       </c>
       <c r="B25" t="n">
-        <v>79702</v>
+        <v>98571</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2986,10 +2986,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>626633</v>
+        <v>626744</v>
       </c>
       <c r="R25" t="n">
-        <v>7217153</v>
+        <v>7217285</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3048,32 +3048,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128103691</v>
+        <v>128103864</v>
       </c>
       <c r="B26" t="n">
-        <v>79115</v>
+        <v>80223</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>185</v>
+        <v>6463</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>626657</v>
+        <v>626755</v>
       </c>
       <c r="R26" t="n">
-        <v>7217200</v>
+        <v>7217274</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3242,32 +3242,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128103864</v>
+        <v>128103691</v>
       </c>
       <c r="B28" t="n">
-        <v>80223</v>
+        <v>79115</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6463</v>
+        <v>185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3277,10 +3277,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>626755</v>
+        <v>626657</v>
       </c>
       <c r="R28" t="n">
-        <v>7217274</v>
+        <v>7217200</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3339,32 +3339,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128103862</v>
+        <v>128103873</v>
       </c>
       <c r="B29" t="n">
-        <v>80223</v>
+        <v>78486</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6463</v>
+        <v>6437</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3374,10 +3374,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>626687</v>
+        <v>626652</v>
       </c>
       <c r="R29" t="n">
-        <v>7217145</v>
+        <v>7217184</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3436,32 +3436,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128103873</v>
+        <v>128103862</v>
       </c>
       <c r="B30" t="n">
-        <v>78486</v>
+        <v>80223</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6437</v>
+        <v>6463</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>626652</v>
+        <v>626687</v>
       </c>
       <c r="R30" t="n">
-        <v>7217184</v>
+        <v>7217145</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4031,32 +4031,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128103749</v>
+        <v>128103800</v>
       </c>
       <c r="B36" t="n">
-        <v>80188</v>
+        <v>98571</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4066,10 +4066,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>626686</v>
+        <v>626843</v>
       </c>
       <c r="R36" t="n">
-        <v>7217075</v>
+        <v>7217062</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4128,32 +4128,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128103789</v>
+        <v>128103816</v>
       </c>
       <c r="B37" t="n">
-        <v>78840</v>
+        <v>98571</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4163,10 +4163,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>626633</v>
+        <v>626837</v>
       </c>
       <c r="R37" t="n">
-        <v>7217153</v>
+        <v>7217076</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4225,32 +4225,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128103800</v>
+        <v>128103789</v>
       </c>
       <c r="B38" t="n">
-        <v>98571</v>
+        <v>78840</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4260,10 +4260,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626843</v>
+        <v>626633</v>
       </c>
       <c r="R38" t="n">
-        <v>7217062</v>
+        <v>7217153</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4322,32 +4322,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128103816</v>
+        <v>128103749</v>
       </c>
       <c r="B39" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4357,10 +4357,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626837</v>
+        <v>626686</v>
       </c>
       <c r="R39" t="n">
-        <v>7217076</v>
+        <v>7217075</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4626,32 +4626,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128103847</v>
+        <v>128103804</v>
       </c>
       <c r="B42" t="n">
-        <v>79083</v>
+        <v>98571</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4661,10 +4661,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>626677</v>
+        <v>626622</v>
       </c>
       <c r="R42" t="n">
-        <v>7217181</v>
+        <v>7217121</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4697,11 +4697,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4728,32 +4723,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128103841</v>
+        <v>128103802</v>
       </c>
       <c r="B43" t="n">
-        <v>79083</v>
+        <v>98571</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4763,10 +4758,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>626739</v>
+        <v>626806</v>
       </c>
       <c r="R43" t="n">
-        <v>7217304</v>
+        <v>7217042</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5142,32 +5137,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128103804</v>
+        <v>128103841</v>
       </c>
       <c r="B47" t="n">
-        <v>98571</v>
+        <v>79083</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5177,10 +5172,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>626622</v>
+        <v>626739</v>
       </c>
       <c r="R47" t="n">
-        <v>7217121</v>
+        <v>7217304</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5239,32 +5234,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128103802</v>
+        <v>128103847</v>
       </c>
       <c r="B48" t="n">
-        <v>98571</v>
+        <v>79083</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5274,10 +5269,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>626806</v>
+        <v>626677</v>
       </c>
       <c r="R48" t="n">
-        <v>7217042</v>
+        <v>7217181</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5310,6 +5305,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5336,7 +5336,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128103848</v>
+        <v>128103840</v>
       </c>
       <c r="B49" t="n">
         <v>79083</v>
@@ -5371,10 +5371,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>626660</v>
+        <v>626757</v>
       </c>
       <c r="R49" t="n">
-        <v>7217210</v>
+        <v>7217294</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5530,7 +5530,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128103840</v>
+        <v>128103848</v>
       </c>
       <c r="B51" t="n">
         <v>79083</v>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>626757</v>
+        <v>626660</v>
       </c>
       <c r="R51" t="n">
-        <v>7217294</v>
+        <v>7217210</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5627,32 +5627,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128103796</v>
+        <v>128103726</v>
       </c>
       <c r="B52" t="n">
-        <v>98571</v>
+        <v>80217</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5662,10 +5662,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>626803</v>
+        <v>626745</v>
       </c>
       <c r="R52" t="n">
-        <v>7217099</v>
+        <v>7217244</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5724,10 +5724,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128103855</v>
+        <v>128103849</v>
       </c>
       <c r="B53" t="n">
-        <v>82942</v>
+        <v>79083</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5735,21 +5735,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5759,10 +5759,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>626723</v>
+        <v>626701</v>
       </c>
       <c r="R53" t="n">
-        <v>7217326</v>
+        <v>7217242</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5821,32 +5821,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128103849</v>
+        <v>128103779</v>
       </c>
       <c r="B54" t="n">
-        <v>79083</v>
+        <v>80224</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5856,10 +5856,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>626701</v>
+        <v>626819</v>
       </c>
       <c r="R54" t="n">
-        <v>7217242</v>
+        <v>7217095</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5918,32 +5918,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128103726</v>
+        <v>128103855</v>
       </c>
       <c r="B55" t="n">
-        <v>80217</v>
+        <v>82942</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5953,10 +5953,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>626745</v>
+        <v>626723</v>
       </c>
       <c r="R55" t="n">
-        <v>7217244</v>
+        <v>7217326</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6015,45 +6015,53 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128103779</v>
+        <v>128103713</v>
       </c>
       <c r="B56" t="n">
-        <v>80224</v>
+        <v>57685</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>626819</v>
+        <v>626703</v>
       </c>
       <c r="R56" t="n">
-        <v>7217095</v>
+        <v>7217299</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6086,6 +6094,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6112,53 +6125,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128103713</v>
+        <v>128103796</v>
       </c>
       <c r="B57" t="n">
-        <v>57685</v>
+        <v>98571</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>626703</v>
+        <v>626803</v>
       </c>
       <c r="R57" t="n">
-        <v>7217299</v>
+        <v>7217099</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6191,11 +6196,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128103750</v>
+        <v>128103715</v>
       </c>
       <c r="B2" t="n">
-        <v>80188</v>
+        <v>57685</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626688</v>
+        <v>626715</v>
       </c>
       <c r="R2" t="n">
-        <v>7217164</v>
+        <v>7217390</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +754,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färsk</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128103748</v>
+        <v>128103712</v>
       </c>
       <c r="B3" t="n">
-        <v>80188</v>
+        <v>57685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +796,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626663</v>
+        <v>626667</v>
       </c>
       <c r="R3" t="n">
-        <v>7217050</v>
+        <v>7217072</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,6 +864,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128103715</v>
+        <v>128103750</v>
       </c>
       <c r="B4" t="n">
-        <v>57685</v>
+        <v>80188</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,42 +906,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626715</v>
+        <v>626688</v>
       </c>
       <c r="R4" t="n">
-        <v>7217390</v>
+        <v>7217164</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,11 +966,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färsk</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,10 +992,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128103712</v>
+        <v>128103748</v>
       </c>
       <c r="B5" t="n">
-        <v>57685</v>
+        <v>80188</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,42 +1003,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626667</v>
+        <v>626663</v>
       </c>
       <c r="R5" t="n">
-        <v>7217072</v>
+        <v>7217050</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1058,11 +1063,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Bohål</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1774,32 +1774,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128103814</v>
+        <v>128103738</v>
       </c>
       <c r="B13" t="n">
-        <v>98571</v>
+        <v>80189</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626811</v>
+        <v>626739</v>
       </c>
       <c r="R13" t="n">
-        <v>7217114</v>
+        <v>7217280</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1871,7 +1871,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128103795</v>
+        <v>128103814</v>
       </c>
       <c r="B14" t="n">
         <v>98571</v>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626797</v>
+        <v>626811</v>
       </c>
       <c r="R14" t="n">
-        <v>7217132</v>
+        <v>7217114</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1968,32 +1968,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128103738</v>
+        <v>128103795</v>
       </c>
       <c r="B15" t="n">
-        <v>80189</v>
+        <v>98571</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626739</v>
+        <v>626797</v>
       </c>
       <c r="R15" t="n">
-        <v>7217280</v>
+        <v>7217132</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -4031,32 +4031,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128103800</v>
+        <v>128103789</v>
       </c>
       <c r="B36" t="n">
-        <v>98571</v>
+        <v>78840</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4066,10 +4066,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>626843</v>
+        <v>626633</v>
       </c>
       <c r="R36" t="n">
-        <v>7217062</v>
+        <v>7217153</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4128,32 +4128,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128103816</v>
+        <v>128103749</v>
       </c>
       <c r="B37" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4163,10 +4163,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>626837</v>
+        <v>626686</v>
       </c>
       <c r="R37" t="n">
-        <v>7217076</v>
+        <v>7217075</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4225,32 +4225,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128103789</v>
+        <v>128103800</v>
       </c>
       <c r="B38" t="n">
-        <v>78840</v>
+        <v>98571</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4260,10 +4260,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626633</v>
+        <v>626843</v>
       </c>
       <c r="R38" t="n">
-        <v>7217153</v>
+        <v>7217062</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4322,32 +4322,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128103749</v>
+        <v>128103816</v>
       </c>
       <c r="B39" t="n">
-        <v>80188</v>
+        <v>98571</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4357,10 +4357,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626686</v>
+        <v>626837</v>
       </c>
       <c r="R39" t="n">
-        <v>7217075</v>
+        <v>7217076</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>

--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128103715</v>
+        <v>128103712</v>
       </c>
       <c r="B2" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626715</v>
+        <v>626667</v>
       </c>
       <c r="R2" t="n">
-        <v>7217390</v>
+        <v>7217072</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Färsk</t>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128103712</v>
+        <v>128103715</v>
       </c>
       <c r="B3" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626667</v>
+        <v>626715</v>
       </c>
       <c r="R3" t="n">
-        <v>7217072</v>
+        <v>7217390</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,7 +868,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Bohål</t>
+          <t>Färsk</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,32 +895,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128103750</v>
+        <v>128103821</v>
       </c>
       <c r="B4" t="n">
-        <v>80188</v>
+        <v>98585</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626688</v>
+        <v>626754</v>
       </c>
       <c r="R4" t="n">
-        <v>7217164</v>
+        <v>7217270</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,10 +992,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128103748</v>
+        <v>128103750</v>
       </c>
       <c r="B5" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,10 +1027,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626663</v>
+        <v>626688</v>
       </c>
       <c r="R5" t="n">
-        <v>7217050</v>
+        <v>7217164</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,32 +1089,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128103821</v>
+        <v>128103748</v>
       </c>
       <c r="B6" t="n">
-        <v>98571</v>
+        <v>80192</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626754</v>
+        <v>626663</v>
       </c>
       <c r="R6" t="n">
-        <v>7217270</v>
+        <v>7217050</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1186,10 +1186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128103861</v>
+        <v>128103815</v>
       </c>
       <c r="B7" t="n">
-        <v>92026</v>
+        <v>98585</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1197,21 +1197,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1221,10 +1221,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626733</v>
+        <v>626821</v>
       </c>
       <c r="R7" t="n">
-        <v>7217284</v>
+        <v>7217074</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1259,18 +1259,12 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Bild</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1289,10 +1283,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128103815</v>
+        <v>128103803</v>
       </c>
       <c r="B8" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1324,10 +1318,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626821</v>
+        <v>626709</v>
       </c>
       <c r="R8" t="n">
-        <v>7217074</v>
+        <v>7217057</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,10 +1380,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128103803</v>
+        <v>128103861</v>
       </c>
       <c r="B9" t="n">
-        <v>98571</v>
+        <v>92038</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1397,21 +1391,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1421,10 +1415,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626709</v>
+        <v>626733</v>
       </c>
       <c r="R9" t="n">
-        <v>7217057</v>
+        <v>7217284</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,12 +1453,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Bild</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1486,7 +1486,7 @@
         <v>128103760</v>
       </c>
       <c r="B10" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>128103778</v>
       </c>
       <c r="B11" t="n">
-        <v>80224</v>
+        <v>80228</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>128103854</v>
       </c>
       <c r="B12" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>128103738</v>
       </c>
       <c r="B13" t="n">
-        <v>80189</v>
+        <v>80193</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,32 +1871,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128103814</v>
+        <v>128103747</v>
       </c>
       <c r="B14" t="n">
-        <v>98571</v>
+        <v>80192</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626811</v>
+        <v>626821</v>
       </c>
       <c r="R14" t="n">
-        <v>7217114</v>
+        <v>7217089</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1968,32 +1968,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128103795</v>
+        <v>128103777</v>
       </c>
       <c r="B15" t="n">
-        <v>98571</v>
+        <v>80228</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626797</v>
+        <v>626745</v>
       </c>
       <c r="R15" t="n">
-        <v>7217132</v>
+        <v>7217253</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2065,32 +2065,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128103747</v>
+        <v>128103814</v>
       </c>
       <c r="B16" t="n">
-        <v>80188</v>
+        <v>98585</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626821</v>
+        <v>626811</v>
       </c>
       <c r="R16" t="n">
-        <v>7217089</v>
+        <v>7217114</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2162,32 +2162,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128103777</v>
+        <v>128103795</v>
       </c>
       <c r="B17" t="n">
-        <v>80224</v>
+        <v>98585</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626745</v>
+        <v>626797</v>
       </c>
       <c r="R17" t="n">
-        <v>7217253</v>
+        <v>7217132</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2262,7 +2262,7 @@
         <v>128103714</v>
       </c>
       <c r="B18" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>128103820</v>
       </c>
       <c r="B19" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2466,32 +2466,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128103817</v>
+        <v>128103752</v>
       </c>
       <c r="B20" t="n">
-        <v>98571</v>
+        <v>80192</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2501,10 +2501,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626705</v>
+        <v>626739</v>
       </c>
       <c r="R20" t="n">
-        <v>7217045</v>
+        <v>7217280</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2563,32 +2563,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128103752</v>
+        <v>128103817</v>
       </c>
       <c r="B21" t="n">
-        <v>80188</v>
+        <v>98585</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626739</v>
+        <v>626705</v>
       </c>
       <c r="R21" t="n">
-        <v>7217280</v>
+        <v>7217045</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2663,7 +2663,7 @@
         <v>128103780</v>
       </c>
       <c r="B22" t="n">
-        <v>80224</v>
+        <v>80228</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>128103775</v>
       </c>
       <c r="B23" t="n">
-        <v>80224</v>
+        <v>80228</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>128103693</v>
       </c>
       <c r="B24" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>128103805</v>
       </c>
       <c r="B25" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3048,32 +3048,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128103864</v>
+        <v>128103691</v>
       </c>
       <c r="B26" t="n">
-        <v>80223</v>
+        <v>79119</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6463</v>
+        <v>185</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>626755</v>
+        <v>626657</v>
       </c>
       <c r="R26" t="n">
-        <v>7217274</v>
+        <v>7217200</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3145,32 +3145,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128103751</v>
+        <v>128103864</v>
       </c>
       <c r="B27" t="n">
-        <v>80188</v>
+        <v>80227</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>626665</v>
+        <v>626755</v>
       </c>
       <c r="R27" t="n">
-        <v>7217186</v>
+        <v>7217274</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3242,10 +3242,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128103691</v>
+        <v>128103751</v>
       </c>
       <c r="B28" t="n">
-        <v>79115</v>
+        <v>80192</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3253,21 +3253,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3277,10 +3277,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>626657</v>
+        <v>626665</v>
       </c>
       <c r="R28" t="n">
-        <v>7217200</v>
+        <v>7217186</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3342,7 +3342,7 @@
         <v>128103873</v>
       </c>
       <c r="B29" t="n">
-        <v>78486</v>
+        <v>78490</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>128103862</v>
       </c>
       <c r="B30" t="n">
-        <v>80223</v>
+        <v>80227</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>128103846</v>
       </c>
       <c r="B31" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>128103865</v>
       </c>
       <c r="B32" t="n">
-        <v>80223</v>
+        <v>80227</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>128103710</v>
       </c>
       <c r="B33" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>128103798</v>
       </c>
       <c r="B34" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         <v>128103799</v>
       </c>
       <c r="B35" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>128103789</v>
       </c>
       <c r="B36" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>128103749</v>
       </c>
       <c r="B37" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
         <v>128103800</v>
       </c>
       <c r="B38" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>128103816</v>
       </c>
       <c r="B39" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>128103776</v>
       </c>
       <c r="B40" t="n">
-        <v>80224</v>
+        <v>80228</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>128103709</v>
       </c>
       <c r="B41" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4626,32 +4626,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128103804</v>
+        <v>128103847</v>
       </c>
       <c r="B42" t="n">
-        <v>98571</v>
+        <v>79087</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4661,10 +4661,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>626622</v>
+        <v>626677</v>
       </c>
       <c r="R42" t="n">
-        <v>7217121</v>
+        <v>7217181</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4697,6 +4697,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4723,32 +4728,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128103802</v>
+        <v>128103841</v>
       </c>
       <c r="B43" t="n">
-        <v>98571</v>
+        <v>79087</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4758,10 +4763,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>626806</v>
+        <v>626739</v>
       </c>
       <c r="R43" t="n">
-        <v>7217042</v>
+        <v>7217304</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4820,10 +4825,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128103707</v>
+        <v>128103708</v>
       </c>
       <c r="B44" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4853,7 +4858,7 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -4863,10 +4868,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>626786</v>
+        <v>626743</v>
       </c>
       <c r="R44" t="n">
-        <v>7217295</v>
+        <v>7217219</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4903,7 +4908,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4930,10 +4935,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128103708</v>
+        <v>128103707</v>
       </c>
       <c r="B45" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4963,7 +4968,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -4973,10 +4978,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>626743</v>
+        <v>626786</v>
       </c>
       <c r="R45" t="n">
-        <v>7217219</v>
+        <v>7217295</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5013,7 +5018,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Bohål</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5040,32 +5045,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128103732</v>
+        <v>128103804</v>
       </c>
       <c r="B46" t="n">
-        <v>98592</v>
+        <v>98585</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5075,10 +5080,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>626665</v>
+        <v>626622</v>
       </c>
       <c r="R46" t="n">
-        <v>7217113</v>
+        <v>7217121</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5137,32 +5142,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128103841</v>
+        <v>128103802</v>
       </c>
       <c r="B47" t="n">
-        <v>79083</v>
+        <v>98585</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5172,10 +5177,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>626739</v>
+        <v>626806</v>
       </c>
       <c r="R47" t="n">
-        <v>7217304</v>
+        <v>7217042</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5234,32 +5239,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128103847</v>
+        <v>128103732</v>
       </c>
       <c r="B48" t="n">
-        <v>79083</v>
+        <v>98606</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5269,10 +5274,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>626677</v>
+        <v>626665</v>
       </c>
       <c r="R48" t="n">
-        <v>7217181</v>
+        <v>7217113</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5305,11 +5310,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5336,10 +5336,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128103840</v>
+        <v>128103848</v>
       </c>
       <c r="B49" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5371,10 +5371,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>626757</v>
+        <v>626660</v>
       </c>
       <c r="R49" t="n">
-        <v>7217294</v>
+        <v>7217210</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5433,10 +5433,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128103790</v>
+        <v>128103840</v>
       </c>
       <c r="B50" t="n">
-        <v>78840</v>
+        <v>79087</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5444,21 +5444,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>626730</v>
+        <v>626757</v>
       </c>
       <c r="R50" t="n">
-        <v>7217238</v>
+        <v>7217294</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5530,10 +5530,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128103848</v>
+        <v>128103790</v>
       </c>
       <c r="B51" t="n">
-        <v>79083</v>
+        <v>78844</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5541,21 +5541,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>626660</v>
+        <v>626730</v>
       </c>
       <c r="R51" t="n">
-        <v>7217210</v>
+        <v>7217238</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5627,32 +5627,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128103726</v>
+        <v>128103796</v>
       </c>
       <c r="B52" t="n">
-        <v>80217</v>
+        <v>98585</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5662,10 +5662,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>626745</v>
+        <v>626803</v>
       </c>
       <c r="R52" t="n">
-        <v>7217244</v>
+        <v>7217099</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5724,32 +5724,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128103849</v>
+        <v>128103797</v>
       </c>
       <c r="B53" t="n">
-        <v>79083</v>
+        <v>98585</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5759,10 +5759,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>626701</v>
+        <v>626820</v>
       </c>
       <c r="R53" t="n">
-        <v>7217242</v>
+        <v>7217037</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5821,32 +5821,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128103779</v>
+        <v>128103855</v>
       </c>
       <c r="B54" t="n">
-        <v>80224</v>
+        <v>82946</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5856,10 +5856,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>626819</v>
+        <v>626723</v>
       </c>
       <c r="R54" t="n">
-        <v>7217095</v>
+        <v>7217326</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5918,10 +5918,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128103855</v>
+        <v>128103849</v>
       </c>
       <c r="B55" t="n">
-        <v>82942</v>
+        <v>79087</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5929,21 +5929,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5953,10 +5953,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>626723</v>
+        <v>626701</v>
       </c>
       <c r="R55" t="n">
-        <v>7217326</v>
+        <v>7217242</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6015,53 +6015,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128103713</v>
+        <v>128103726</v>
       </c>
       <c r="B56" t="n">
-        <v>57685</v>
+        <v>80221</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>626703</v>
+        <v>626745</v>
       </c>
       <c r="R56" t="n">
-        <v>7217299</v>
+        <v>7217244</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6094,11 +6086,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6125,32 +6112,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128103796</v>
+        <v>128103779</v>
       </c>
       <c r="B57" t="n">
-        <v>98571</v>
+        <v>80228</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6160,10 +6147,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>626803</v>
+        <v>626819</v>
       </c>
       <c r="R57" t="n">
-        <v>7217099</v>
+        <v>7217095</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6222,45 +6209,53 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128103797</v>
+        <v>128103713</v>
       </c>
       <c r="B58" t="n">
-        <v>98571</v>
+        <v>57689</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>626820</v>
+        <v>626703</v>
       </c>
       <c r="R58" t="n">
-        <v>7217037</v>
+        <v>7217299</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6293,6 +6288,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6322,7 +6322,7 @@
         <v>128103818</v>
       </c>
       <c r="B59" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128103712</v>
+        <v>128103750</v>
       </c>
       <c r="B2" t="n">
-        <v>57689</v>
+        <v>80192</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626667</v>
+        <v>626688</v>
       </c>
       <c r="R2" t="n">
-        <v>7217072</v>
+        <v>7217164</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Bohål</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128103715</v>
+        <v>128103748</v>
       </c>
       <c r="B3" t="n">
-        <v>57689</v>
+        <v>80192</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,42 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626715</v>
+        <v>626663</v>
       </c>
       <c r="R3" t="n">
-        <v>7217390</v>
+        <v>7217050</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färsk</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,45 +869,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128103821</v>
+        <v>128103712</v>
       </c>
       <c r="B4" t="n">
-        <v>98585</v>
+        <v>57689</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626754</v>
+        <v>626667</v>
       </c>
       <c r="R4" t="n">
-        <v>7217270</v>
+        <v>7217072</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,6 +948,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128103750</v>
+        <v>128103715</v>
       </c>
       <c r="B5" t="n">
-        <v>80192</v>
+        <v>57689</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1003,34 +990,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626688</v>
+        <v>626715</v>
       </c>
       <c r="R5" t="n">
-        <v>7217164</v>
+        <v>7217390</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,6 +1058,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färsk</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,32 +1089,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128103748</v>
+        <v>128103821</v>
       </c>
       <c r="B6" t="n">
-        <v>80192</v>
+        <v>98585</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626663</v>
+        <v>626754</v>
       </c>
       <c r="R6" t="n">
-        <v>7217050</v>
+        <v>7217270</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -3339,32 +3339,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128103873</v>
+        <v>128103862</v>
       </c>
       <c r="B29" t="n">
-        <v>78490</v>
+        <v>80227</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6437</v>
+        <v>6463</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3374,10 +3374,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>626652</v>
+        <v>626687</v>
       </c>
       <c r="R29" t="n">
-        <v>7217184</v>
+        <v>7217145</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3436,32 +3436,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128103862</v>
+        <v>128103873</v>
       </c>
       <c r="B30" t="n">
-        <v>80227</v>
+        <v>78490</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6463</v>
+        <v>6437</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>626687</v>
+        <v>626652</v>
       </c>
       <c r="R30" t="n">
-        <v>7217145</v>
+        <v>7217184</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4031,32 +4031,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128103789</v>
+        <v>128103800</v>
       </c>
       <c r="B36" t="n">
-        <v>78844</v>
+        <v>98585</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4066,10 +4066,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>626633</v>
+        <v>626843</v>
       </c>
       <c r="R36" t="n">
-        <v>7217153</v>
+        <v>7217062</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4128,32 +4128,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128103749</v>
+        <v>128103816</v>
       </c>
       <c r="B37" t="n">
-        <v>80192</v>
+        <v>98585</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4163,10 +4163,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>626686</v>
+        <v>626837</v>
       </c>
       <c r="R37" t="n">
-        <v>7217075</v>
+        <v>7217076</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4225,32 +4225,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128103800</v>
+        <v>128103789</v>
       </c>
       <c r="B38" t="n">
-        <v>98585</v>
+        <v>78844</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4260,10 +4260,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626843</v>
+        <v>626633</v>
       </c>
       <c r="R38" t="n">
-        <v>7217062</v>
+        <v>7217153</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4322,32 +4322,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128103816</v>
+        <v>128103749</v>
       </c>
       <c r="B39" t="n">
-        <v>98585</v>
+        <v>80192</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4357,10 +4357,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626837</v>
+        <v>626686</v>
       </c>
       <c r="R39" t="n">
-        <v>7217076</v>
+        <v>7217075</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5627,32 +5627,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128103796</v>
+        <v>128103849</v>
       </c>
       <c r="B52" t="n">
-        <v>98585</v>
+        <v>79087</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5662,10 +5662,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>626803</v>
+        <v>626701</v>
       </c>
       <c r="R52" t="n">
-        <v>7217099</v>
+        <v>7217242</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5724,32 +5724,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128103797</v>
+        <v>128103779</v>
       </c>
       <c r="B53" t="n">
-        <v>98585</v>
+        <v>80228</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5759,10 +5759,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>626820</v>
+        <v>626819</v>
       </c>
       <c r="R53" t="n">
-        <v>7217037</v>
+        <v>7217095</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5821,10 +5821,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128103855</v>
+        <v>128103713</v>
       </c>
       <c r="B54" t="n">
-        <v>82946</v>
+        <v>57689</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5832,34 +5832,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>626723</v>
+        <v>626703</v>
       </c>
       <c r="R54" t="n">
-        <v>7217326</v>
+        <v>7217299</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5892,6 +5900,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5918,32 +5931,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128103849</v>
+        <v>128103796</v>
       </c>
       <c r="B55" t="n">
-        <v>79087</v>
+        <v>98585</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5953,10 +5966,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>626701</v>
+        <v>626803</v>
       </c>
       <c r="R55" t="n">
-        <v>7217242</v>
+        <v>7217099</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6015,32 +6028,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128103726</v>
+        <v>128103797</v>
       </c>
       <c r="B56" t="n">
-        <v>80221</v>
+        <v>98585</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6050,10 +6063,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>626745</v>
+        <v>626820</v>
       </c>
       <c r="R56" t="n">
-        <v>7217244</v>
+        <v>7217037</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6112,32 +6125,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128103779</v>
+        <v>128103855</v>
       </c>
       <c r="B57" t="n">
-        <v>80228</v>
+        <v>82946</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6147,10 +6160,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>626819</v>
+        <v>626723</v>
       </c>
       <c r="R57" t="n">
-        <v>7217095</v>
+        <v>7217326</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6209,53 +6222,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128103713</v>
+        <v>128103726</v>
       </c>
       <c r="B58" t="n">
-        <v>57689</v>
+        <v>80221</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>626703</v>
+        <v>626745</v>
       </c>
       <c r="R58" t="n">
-        <v>7217299</v>
+        <v>7217244</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6288,11 +6293,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128103750</v>
+        <v>128103712</v>
       </c>
       <c r="B2" t="n">
-        <v>80192</v>
+        <v>57689</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626688</v>
+        <v>626667</v>
       </c>
       <c r="R2" t="n">
-        <v>7217164</v>
+        <v>7217072</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +754,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128103748</v>
+        <v>128103715</v>
       </c>
       <c r="B3" t="n">
-        <v>80192</v>
+        <v>57689</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +796,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626663</v>
+        <v>626715</v>
       </c>
       <c r="R3" t="n">
-        <v>7217050</v>
+        <v>7217390</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,6 +864,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färsk</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,53 +895,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128103712</v>
+        <v>128103821</v>
       </c>
       <c r="B4" t="n">
-        <v>57689</v>
+        <v>98585</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626667</v>
+        <v>626754</v>
       </c>
       <c r="R4" t="n">
-        <v>7217072</v>
+        <v>7217270</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,11 +966,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Bohål</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,10 +992,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128103715</v>
+        <v>128103750</v>
       </c>
       <c r="B5" t="n">
-        <v>57689</v>
+        <v>80192</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,42 +1003,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626715</v>
+        <v>626688</v>
       </c>
       <c r="R5" t="n">
-        <v>7217390</v>
+        <v>7217164</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1058,11 +1063,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färsk</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,32 +1089,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128103821</v>
+        <v>128103748</v>
       </c>
       <c r="B6" t="n">
-        <v>98585</v>
+        <v>80192</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626754</v>
+        <v>626663</v>
       </c>
       <c r="R6" t="n">
-        <v>7217270</v>
+        <v>7217050</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -4626,10 +4626,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128103847</v>
+        <v>128103708</v>
       </c>
       <c r="B42" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4637,34 +4637,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>626677</v>
+        <v>626743</v>
       </c>
       <c r="R42" t="n">
-        <v>7217181</v>
+        <v>7217219</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4701,7 +4709,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Med apothecier</t>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4728,10 +4736,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128103841</v>
+        <v>128103707</v>
       </c>
       <c r="B43" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4739,34 +4747,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>626739</v>
+        <v>626786</v>
       </c>
       <c r="R43" t="n">
-        <v>7217304</v>
+        <v>7217295</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4799,6 +4815,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4825,10 +4846,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128103708</v>
+        <v>128103847</v>
       </c>
       <c r="B44" t="n">
-        <v>57689</v>
+        <v>79087</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4836,42 +4857,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>626743</v>
+        <v>626677</v>
       </c>
       <c r="R44" t="n">
-        <v>7217219</v>
+        <v>7217181</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4908,7 +4921,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Bohål</t>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4935,10 +4948,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128103707</v>
+        <v>128103841</v>
       </c>
       <c r="B45" t="n">
-        <v>57689</v>
+        <v>79087</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4946,42 +4959,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>626786</v>
+        <v>626739</v>
       </c>
       <c r="R45" t="n">
-        <v>7217295</v>
+        <v>7217304</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5014,11 +5019,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5724,10 +5724,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128103779</v>
+        <v>128103726</v>
       </c>
       <c r="B53" t="n">
-        <v>80228</v>
+        <v>80221</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5735,21 +5735,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5759,10 +5759,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>626819</v>
+        <v>626745</v>
       </c>
       <c r="R53" t="n">
-        <v>7217095</v>
+        <v>7217244</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5821,53 +5821,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128103713</v>
+        <v>128103779</v>
       </c>
       <c r="B54" t="n">
-        <v>57689</v>
+        <v>80228</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>626703</v>
+        <v>626819</v>
       </c>
       <c r="R54" t="n">
-        <v>7217299</v>
+        <v>7217095</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5900,11 +5892,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5931,45 +5918,53 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128103796</v>
+        <v>128103713</v>
       </c>
       <c r="B55" t="n">
-        <v>98585</v>
+        <v>57689</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>626803</v>
+        <v>626703</v>
       </c>
       <c r="R55" t="n">
-        <v>7217099</v>
+        <v>7217299</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6002,6 +5997,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6028,7 +6028,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128103797</v>
+        <v>128103796</v>
       </c>
       <c r="B56" t="n">
         <v>98585</v>
@@ -6063,10 +6063,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>626820</v>
+        <v>626803</v>
       </c>
       <c r="R56" t="n">
-        <v>7217037</v>
+        <v>7217099</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6125,32 +6125,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128103855</v>
+        <v>128103797</v>
       </c>
       <c r="B57" t="n">
-        <v>82946</v>
+        <v>98585</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6160,10 +6160,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>626723</v>
+        <v>626820</v>
       </c>
       <c r="R57" t="n">
-        <v>7217326</v>
+        <v>7217037</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6222,32 +6222,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128103726</v>
+        <v>128103855</v>
       </c>
       <c r="B58" t="n">
-        <v>80221</v>
+        <v>82946</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>626745</v>
+        <v>626723</v>
       </c>
       <c r="R58" t="n">
-        <v>7217244</v>
+        <v>7217326</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>

--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128103712</v>
+        <v>128103750</v>
       </c>
       <c r="B2" t="n">
-        <v>57689</v>
+        <v>80194</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626667</v>
+        <v>626688</v>
       </c>
       <c r="R2" t="n">
-        <v>7217072</v>
+        <v>7217164</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Bohål</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128103715</v>
+        <v>128103748</v>
       </c>
       <c r="B3" t="n">
-        <v>57689</v>
+        <v>80194</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,42 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626715</v>
+        <v>626663</v>
       </c>
       <c r="R3" t="n">
-        <v>7217390</v>
+        <v>7217050</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färsk</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,45 +869,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128103821</v>
+        <v>128103715</v>
       </c>
       <c r="B4" t="n">
-        <v>98585</v>
+        <v>57689</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626754</v>
+        <v>626715</v>
       </c>
       <c r="R4" t="n">
-        <v>7217270</v>
+        <v>7217390</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,6 +948,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färsk</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128103750</v>
+        <v>128103712</v>
       </c>
       <c r="B5" t="n">
-        <v>80192</v>
+        <v>57689</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1003,34 +990,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626688</v>
+        <v>626667</v>
       </c>
       <c r="R5" t="n">
-        <v>7217164</v>
+        <v>7217072</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,6 +1058,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,32 +1089,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128103748</v>
+        <v>128103821</v>
       </c>
       <c r="B6" t="n">
-        <v>80192</v>
+        <v>98591</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626663</v>
+        <v>626754</v>
       </c>
       <c r="R6" t="n">
-        <v>7217050</v>
+        <v>7217270</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,7 +1189,7 @@
         <v>128103815</v>
       </c>
       <c r="B7" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>128103803</v>
       </c>
       <c r="B8" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>128103861</v>
       </c>
       <c r="B9" t="n">
-        <v>92038</v>
+        <v>92040</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>128103760</v>
       </c>
       <c r="B10" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>128103778</v>
       </c>
       <c r="B11" t="n">
-        <v>80228</v>
+        <v>80230</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>128103854</v>
       </c>
       <c r="B12" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>128103738</v>
       </c>
       <c r="B13" t="n">
-        <v>80193</v>
+        <v>80195</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>128103747</v>
       </c>
       <c r="B14" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>128103777</v>
       </c>
       <c r="B15" t="n">
-        <v>80228</v>
+        <v>80230</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>128103814</v>
       </c>
       <c r="B16" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>128103795</v>
       </c>
       <c r="B17" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>128103820</v>
       </c>
       <c r="B19" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>128103752</v>
       </c>
       <c r="B20" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>128103817</v>
       </c>
       <c r="B21" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>128103780</v>
       </c>
       <c r="B22" t="n">
-        <v>80228</v>
+        <v>80230</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>128103775</v>
       </c>
       <c r="B23" t="n">
-        <v>80228</v>
+        <v>80230</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2854,32 +2854,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128103693</v>
+        <v>128103805</v>
       </c>
       <c r="B24" t="n">
-        <v>79706</v>
+        <v>98591</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626633</v>
+        <v>626744</v>
       </c>
       <c r="R24" t="n">
-        <v>7217153</v>
+        <v>7217285</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2951,32 +2951,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128103805</v>
+        <v>128103693</v>
       </c>
       <c r="B25" t="n">
-        <v>98585</v>
+        <v>79708</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2986,10 +2986,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>626744</v>
+        <v>626633</v>
       </c>
       <c r="R25" t="n">
-        <v>7217285</v>
+        <v>7217153</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3051,7 +3051,7 @@
         <v>128103691</v>
       </c>
       <c r="B26" t="n">
-        <v>79119</v>
+        <v>79121</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>128103864</v>
       </c>
       <c r="B27" t="n">
-        <v>80227</v>
+        <v>80229</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>128103751</v>
       </c>
       <c r="B28" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>128103862</v>
       </c>
       <c r="B29" t="n">
-        <v>80227</v>
+        <v>80229</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>128103873</v>
       </c>
       <c r="B30" t="n">
-        <v>78490</v>
+        <v>78492</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>128103846</v>
       </c>
       <c r="B31" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>128103865</v>
       </c>
       <c r="B32" t="n">
-        <v>80227</v>
+        <v>80229</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>128103798</v>
       </c>
       <c r="B34" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         <v>128103799</v>
       </c>
       <c r="B35" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>128103800</v>
       </c>
       <c r="B36" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4128,32 +4128,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128103816</v>
+        <v>128103789</v>
       </c>
       <c r="B37" t="n">
-        <v>98585</v>
+        <v>78846</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4163,10 +4163,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>626837</v>
+        <v>626633</v>
       </c>
       <c r="R37" t="n">
-        <v>7217076</v>
+        <v>7217153</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4225,10 +4225,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128103789</v>
+        <v>128103749</v>
       </c>
       <c r="B38" t="n">
-        <v>78844</v>
+        <v>80194</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4236,21 +4236,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4260,10 +4260,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626633</v>
+        <v>626686</v>
       </c>
       <c r="R38" t="n">
-        <v>7217153</v>
+        <v>7217075</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4322,32 +4322,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128103749</v>
+        <v>128103816</v>
       </c>
       <c r="B39" t="n">
-        <v>80192</v>
+        <v>98591</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4357,10 +4357,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626686</v>
+        <v>626837</v>
       </c>
       <c r="R39" t="n">
-        <v>7217075</v>
+        <v>7217076</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4419,45 +4419,53 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128103776</v>
+        <v>128103709</v>
       </c>
       <c r="B40" t="n">
-        <v>80228</v>
+        <v>57689</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>626665</v>
+        <v>626740</v>
       </c>
       <c r="R40" t="n">
-        <v>7217186</v>
+        <v>7217219</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4490,6 +4498,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4516,53 +4529,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128103709</v>
+        <v>128103776</v>
       </c>
       <c r="B41" t="n">
-        <v>57689</v>
+        <v>80230</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>626740</v>
+        <v>626665</v>
       </c>
       <c r="R41" t="n">
-        <v>7217219</v>
+        <v>7217186</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4595,11 +4600,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4626,10 +4626,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128103708</v>
+        <v>128103841</v>
       </c>
       <c r="B42" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4637,42 +4637,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>626743</v>
+        <v>626739</v>
       </c>
       <c r="R42" t="n">
-        <v>7217219</v>
+        <v>7217304</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4705,11 +4697,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Bohål</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4736,10 +4723,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128103707</v>
+        <v>128103847</v>
       </c>
       <c r="B43" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4747,42 +4734,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>626786</v>
+        <v>626677</v>
       </c>
       <c r="R43" t="n">
-        <v>7217295</v>
+        <v>7217181</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4819,7 +4798,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4846,32 +4825,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128103847</v>
+        <v>128103732</v>
       </c>
       <c r="B44" t="n">
-        <v>79087</v>
+        <v>98612</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4881,10 +4860,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>626677</v>
+        <v>626665</v>
       </c>
       <c r="R44" t="n">
-        <v>7217181</v>
+        <v>7217113</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4917,11 +4896,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4948,10 +4922,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128103841</v>
+        <v>128103707</v>
       </c>
       <c r="B45" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4959,34 +4933,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>626739</v>
+        <v>626786</v>
       </c>
       <c r="R45" t="n">
-        <v>7217304</v>
+        <v>7217295</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5019,6 +5001,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5045,45 +5032,53 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128103804</v>
+        <v>128103708</v>
       </c>
       <c r="B46" t="n">
-        <v>98585</v>
+        <v>57689</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>626622</v>
+        <v>626743</v>
       </c>
       <c r="R46" t="n">
-        <v>7217121</v>
+        <v>7217219</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5116,6 +5111,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5142,10 +5142,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128103802</v>
+        <v>128103804</v>
       </c>
       <c r="B47" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5177,10 +5177,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>626806</v>
+        <v>626622</v>
       </c>
       <c r="R47" t="n">
-        <v>7217042</v>
+        <v>7217121</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5239,32 +5239,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128103732</v>
+        <v>128103802</v>
       </c>
       <c r="B48" t="n">
-        <v>98606</v>
+        <v>98591</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5274,10 +5274,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>626665</v>
+        <v>626806</v>
       </c>
       <c r="R48" t="n">
-        <v>7217113</v>
+        <v>7217042</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5336,10 +5336,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128103848</v>
+        <v>128103840</v>
       </c>
       <c r="B49" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5371,10 +5371,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>626660</v>
+        <v>626757</v>
       </c>
       <c r="R49" t="n">
-        <v>7217210</v>
+        <v>7217294</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5433,10 +5433,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128103840</v>
+        <v>128103790</v>
       </c>
       <c r="B50" t="n">
-        <v>79087</v>
+        <v>78846</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5444,21 +5444,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>626757</v>
+        <v>626730</v>
       </c>
       <c r="R50" t="n">
-        <v>7217294</v>
+        <v>7217238</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5530,10 +5530,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128103790</v>
+        <v>128103848</v>
       </c>
       <c r="B51" t="n">
-        <v>78844</v>
+        <v>79089</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5541,21 +5541,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>626730</v>
+        <v>626660</v>
       </c>
       <c r="R51" t="n">
-        <v>7217238</v>
+        <v>7217210</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5627,32 +5627,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128103849</v>
+        <v>128103796</v>
       </c>
       <c r="B52" t="n">
-        <v>79087</v>
+        <v>98591</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5662,10 +5662,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>626701</v>
+        <v>626803</v>
       </c>
       <c r="R52" t="n">
-        <v>7217242</v>
+        <v>7217099</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5724,32 +5724,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128103726</v>
+        <v>128103797</v>
       </c>
       <c r="B53" t="n">
-        <v>80221</v>
+        <v>98591</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5759,10 +5759,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>626745</v>
+        <v>626820</v>
       </c>
       <c r="R53" t="n">
-        <v>7217244</v>
+        <v>7217037</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5821,10 +5821,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128103779</v>
+        <v>128103726</v>
       </c>
       <c r="B54" t="n">
-        <v>80228</v>
+        <v>80223</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5832,21 +5832,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5856,10 +5856,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>626819</v>
+        <v>626745</v>
       </c>
       <c r="R54" t="n">
-        <v>7217095</v>
+        <v>7217244</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5918,10 +5918,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128103713</v>
+        <v>128103849</v>
       </c>
       <c r="B55" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5929,42 +5929,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>626703</v>
+        <v>626701</v>
       </c>
       <c r="R55" t="n">
-        <v>7217299</v>
+        <v>7217242</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5997,11 +5989,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6028,32 +6015,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128103796</v>
+        <v>128103779</v>
       </c>
       <c r="B56" t="n">
-        <v>98585</v>
+        <v>80230</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6063,10 +6050,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>626803</v>
+        <v>626819</v>
       </c>
       <c r="R56" t="n">
-        <v>7217099</v>
+        <v>7217095</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6125,32 +6112,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128103797</v>
+        <v>128103855</v>
       </c>
       <c r="B57" t="n">
-        <v>98585</v>
+        <v>82948</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6160,10 +6147,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>626820</v>
+        <v>626723</v>
       </c>
       <c r="R57" t="n">
-        <v>7217037</v>
+        <v>7217326</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6222,10 +6209,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128103855</v>
+        <v>128103713</v>
       </c>
       <c r="B58" t="n">
-        <v>82946</v>
+        <v>57689</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6233,34 +6220,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>626723</v>
+        <v>626703</v>
       </c>
       <c r="R58" t="n">
-        <v>7217326</v>
+        <v>7217299</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6293,6 +6288,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6322,7 +6322,7 @@
         <v>128103818</v>
       </c>
       <c r="B59" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -1774,32 +1774,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128103738</v>
+        <v>128103814</v>
       </c>
       <c r="B13" t="n">
-        <v>80195</v>
+        <v>98591</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626739</v>
+        <v>626811</v>
       </c>
       <c r="R13" t="n">
-        <v>7217280</v>
+        <v>7217114</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1871,32 +1871,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128103747</v>
+        <v>128103795</v>
       </c>
       <c r="B14" t="n">
-        <v>80194</v>
+        <v>98591</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626821</v>
+        <v>626797</v>
       </c>
       <c r="R14" t="n">
-        <v>7217089</v>
+        <v>7217132</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1968,32 +1968,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128103777</v>
+        <v>128103738</v>
       </c>
       <c r="B15" t="n">
-        <v>80230</v>
+        <v>80195</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626745</v>
+        <v>626739</v>
       </c>
       <c r="R15" t="n">
-        <v>7217253</v>
+        <v>7217280</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2065,32 +2065,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128103814</v>
+        <v>128103747</v>
       </c>
       <c r="B16" t="n">
-        <v>98591</v>
+        <v>80194</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626811</v>
+        <v>626821</v>
       </c>
       <c r="R16" t="n">
-        <v>7217114</v>
+        <v>7217089</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2162,32 +2162,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128103795</v>
+        <v>128103777</v>
       </c>
       <c r="B17" t="n">
-        <v>98591</v>
+        <v>80230</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626797</v>
+        <v>626745</v>
       </c>
       <c r="R17" t="n">
-        <v>7217132</v>
+        <v>7217253</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -4031,7 +4031,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128103800</v>
+        <v>128103816</v>
       </c>
       <c r="B36" t="n">
         <v>98591</v>
@@ -4066,10 +4066,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>626843</v>
+        <v>626837</v>
       </c>
       <c r="R36" t="n">
-        <v>7217062</v>
+        <v>7217076</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4322,7 +4322,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128103816</v>
+        <v>128103800</v>
       </c>
       <c r="B39" t="n">
         <v>98591</v>
@@ -4357,10 +4357,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626837</v>
+        <v>626843</v>
       </c>
       <c r="R39" t="n">
-        <v>7217076</v>
+        <v>7217062</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>

--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128103750</v>
       </c>
       <c r="B2" t="n">
-        <v>80194</v>
+        <v>80225</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -768,14 +768,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>128103748</v>
       </c>
       <c r="B3" t="n">
-        <v>80194</v>
+        <v>80225</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -865,14 +869,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>128103715</v>
       </c>
       <c r="B4" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,14 +983,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>128103712</v>
       </c>
       <c r="B5" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1085,14 +1097,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>128103821</v>
       </c>
       <c r="B6" t="n">
-        <v>98591</v>
+        <v>98632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1182,14 +1198,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>128103815</v>
       </c>
       <c r="B7" t="n">
-        <v>98591</v>
+        <v>98632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1279,14 +1299,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>128103803</v>
       </c>
       <c r="B8" t="n">
-        <v>98591</v>
+        <v>98632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1376,14 +1400,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>128103861</v>
       </c>
       <c r="B9" t="n">
-        <v>92040</v>
+        <v>92078</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,14 +1507,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>128103760</v>
       </c>
       <c r="B10" t="n">
-        <v>80194</v>
+        <v>80225</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,14 +1608,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>128103778</v>
       </c>
       <c r="B11" t="n">
-        <v>80230</v>
+        <v>80261</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,14 +1709,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>128103854</v>
       </c>
       <c r="B12" t="n">
-        <v>82948</v>
+        <v>82979</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1770,14 +1810,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>128103814</v>
       </c>
       <c r="B13" t="n">
-        <v>98591</v>
+        <v>98632</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1867,14 +1911,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>128103795</v>
       </c>
       <c r="B14" t="n">
-        <v>98591</v>
+        <v>98632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1964,14 +2012,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>128103738</v>
       </c>
       <c r="B15" t="n">
-        <v>80195</v>
+        <v>80226</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2061,14 +2113,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>128103747</v>
       </c>
       <c r="B16" t="n">
-        <v>80194</v>
+        <v>80225</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2158,14 +2214,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>128103777</v>
       </c>
       <c r="B17" t="n">
-        <v>80230</v>
+        <v>80261</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2255,14 +2315,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>128103714</v>
       </c>
       <c r="B18" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2365,14 +2429,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>128103820</v>
       </c>
       <c r="B19" t="n">
-        <v>98591</v>
+        <v>98632</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2462,14 +2530,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>128103752</v>
       </c>
       <c r="B20" t="n">
-        <v>80194</v>
+        <v>80225</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2559,14 +2631,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>128103817</v>
       </c>
       <c r="B21" t="n">
-        <v>98591</v>
+        <v>98632</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2656,14 +2732,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>128103780</v>
       </c>
       <c r="B22" t="n">
-        <v>80230</v>
+        <v>80261</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2753,14 +2833,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>128103775</v>
       </c>
       <c r="B23" t="n">
-        <v>80230</v>
+        <v>80261</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2850,14 +2934,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>128103805</v>
       </c>
       <c r="B24" t="n">
-        <v>98591</v>
+        <v>98632</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2947,14 +3035,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>128103693</v>
       </c>
       <c r="B25" t="n">
-        <v>79708</v>
+        <v>79739</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3044,14 +3136,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>128103691</v>
       </c>
       <c r="B26" t="n">
-        <v>79121</v>
+        <v>79152</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3141,14 +3237,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>128103864</v>
       </c>
       <c r="B27" t="n">
-        <v>80229</v>
+        <v>80260</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3238,14 +3338,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>128103751</v>
       </c>
       <c r="B28" t="n">
-        <v>80194</v>
+        <v>80225</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3335,14 +3439,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY28" t="inlineStr"/>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>128103862</v>
       </c>
       <c r="B29" t="n">
-        <v>80229</v>
+        <v>80260</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3432,14 +3540,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
         <v>128103873</v>
       </c>
       <c r="B30" t="n">
-        <v>78492</v>
+        <v>78523</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3529,14 +3641,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY30" t="inlineStr"/>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
         <v>128103846</v>
       </c>
       <c r="B31" t="n">
-        <v>79089</v>
+        <v>79120</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3626,14 +3742,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY31" t="inlineStr"/>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
         <v>128103865</v>
       </c>
       <c r="B32" t="n">
-        <v>80229</v>
+        <v>80260</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3723,14 +3843,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY32" t="inlineStr"/>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>128103710</v>
       </c>
       <c r="B33" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3833,14 +3957,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY33" t="inlineStr"/>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
         <v>128103798</v>
       </c>
       <c r="B34" t="n">
-        <v>98591</v>
+        <v>98632</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3930,14 +4058,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY34" t="inlineStr"/>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
         <v>128103799</v>
       </c>
       <c r="B35" t="n">
-        <v>98591</v>
+        <v>98632</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4027,14 +4159,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY35" t="inlineStr"/>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
         <v>128103816</v>
       </c>
       <c r="B36" t="n">
-        <v>98591</v>
+        <v>98632</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4124,14 +4260,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY36" t="inlineStr"/>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
         <v>128103789</v>
       </c>
       <c r="B37" t="n">
-        <v>78846</v>
+        <v>78877</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4221,14 +4361,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY37" t="inlineStr"/>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
         <v>128103749</v>
       </c>
       <c r="B38" t="n">
-        <v>80194</v>
+        <v>80225</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4318,14 +4462,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY38" t="inlineStr"/>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
         <v>128103800</v>
       </c>
       <c r="B39" t="n">
-        <v>98591</v>
+        <v>98632</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4415,14 +4563,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY39" t="inlineStr"/>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
         <v>128103709</v>
       </c>
       <c r="B40" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4525,14 +4677,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY40" t="inlineStr"/>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
         <v>128103776</v>
       </c>
       <c r="B41" t="n">
-        <v>80230</v>
+        <v>80261</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4622,14 +4778,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY41" t="inlineStr"/>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
         <v>128103841</v>
       </c>
       <c r="B42" t="n">
-        <v>79089</v>
+        <v>79120</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4719,14 +4879,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY42" t="inlineStr"/>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
         <v>128103847</v>
       </c>
       <c r="B43" t="n">
-        <v>79089</v>
+        <v>79120</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4821,14 +4985,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY43" t="inlineStr"/>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
         <v>128103732</v>
       </c>
       <c r="B44" t="n">
-        <v>98612</v>
+        <v>98653</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4918,14 +5086,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY44" t="inlineStr"/>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
         <v>128103707</v>
       </c>
       <c r="B45" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5028,14 +5200,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY45" t="inlineStr"/>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
         <v>128103708</v>
       </c>
       <c r="B46" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5138,14 +5314,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY46" t="inlineStr"/>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
         <v>128103804</v>
       </c>
       <c r="B47" t="n">
-        <v>98591</v>
+        <v>98632</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5235,14 +5415,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY47" t="inlineStr"/>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
         <v>128103802</v>
       </c>
       <c r="B48" t="n">
-        <v>98591</v>
+        <v>98632</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5332,14 +5516,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY48" t="inlineStr"/>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
         <v>128103840</v>
       </c>
       <c r="B49" t="n">
-        <v>79089</v>
+        <v>79120</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5429,14 +5617,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY49" t="inlineStr"/>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
         <v>128103790</v>
       </c>
       <c r="B50" t="n">
-        <v>78846</v>
+        <v>78877</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5526,14 +5718,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY50" t="inlineStr"/>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
         <v>128103848</v>
       </c>
       <c r="B51" t="n">
-        <v>79089</v>
+        <v>79120</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5623,14 +5819,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY51" t="inlineStr"/>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
         <v>128103796</v>
       </c>
       <c r="B52" t="n">
-        <v>98591</v>
+        <v>98632</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5720,14 +5920,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY52" t="inlineStr"/>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
         <v>128103797</v>
       </c>
       <c r="B53" t="n">
-        <v>98591</v>
+        <v>98632</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5817,14 +6021,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY53" t="inlineStr"/>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
         <v>128103726</v>
       </c>
       <c r="B54" t="n">
-        <v>80223</v>
+        <v>80254</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5914,14 +6122,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY54" t="inlineStr"/>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
         <v>128103849</v>
       </c>
       <c r="B55" t="n">
-        <v>79089</v>
+        <v>79120</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6011,14 +6223,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY55" t="inlineStr"/>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
         <v>128103779</v>
       </c>
       <c r="B56" t="n">
-        <v>80230</v>
+        <v>80261</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6108,14 +6324,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY56" t="inlineStr"/>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
         <v>128103855</v>
       </c>
       <c r="B57" t="n">
-        <v>82948</v>
+        <v>82979</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6205,14 +6425,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY57" t="inlineStr"/>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
         <v>128103713</v>
       </c>
       <c r="B58" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6315,14 +6539,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY58" t="inlineStr"/>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
         <v>128103818</v>
       </c>
       <c r="B59" t="n">
-        <v>98591</v>
+        <v>98632</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6412,7 +6640,11 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY59" t="inlineStr"/>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128103750</v>
       </c>
       <c r="B2" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128103748</v>
       </c>
       <c r="B3" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>128103715</v>
       </c>
       <c r="B4" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>128103712</v>
       </c>
       <c r="B5" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>128103821</v>
       </c>
       <c r="B6" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>128103815</v>
       </c>
       <c r="B7" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>128103803</v>
       </c>
       <c r="B8" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>128103861</v>
       </c>
       <c r="B9" t="n">
-        <v>92078</v>
+        <v>92082</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>128103760</v>
       </c>
       <c r="B10" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>128103778</v>
       </c>
       <c r="B11" t="n">
-        <v>80261</v>
+        <v>80265</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>128103854</v>
       </c>
       <c r="B12" t="n">
-        <v>82979</v>
+        <v>82983</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>128103814</v>
       </c>
       <c r="B13" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>128103795</v>
       </c>
       <c r="B14" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>128103738</v>
       </c>
       <c r="B15" t="n">
-        <v>80226</v>
+        <v>80230</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>128103747</v>
       </c>
       <c r="B16" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>128103777</v>
       </c>
       <c r="B17" t="n">
-        <v>80261</v>
+        <v>80265</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>128103714</v>
       </c>
       <c r="B18" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>128103820</v>
       </c>
       <c r="B19" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>128103752</v>
       </c>
       <c r="B20" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>128103817</v>
       </c>
       <c r="B21" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>128103780</v>
       </c>
       <c r="B22" t="n">
-        <v>80261</v>
+        <v>80265</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>128103775</v>
       </c>
       <c r="B23" t="n">
-        <v>80261</v>
+        <v>80265</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>128103805</v>
       </c>
       <c r="B24" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>128103693</v>
       </c>
       <c r="B25" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>128103691</v>
       </c>
       <c r="B26" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>128103864</v>
       </c>
       <c r="B27" t="n">
-        <v>80260</v>
+        <v>80264</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>128103751</v>
       </c>
       <c r="B28" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>128103862</v>
       </c>
       <c r="B29" t="n">
-        <v>80260</v>
+        <v>80264</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>128103873</v>
       </c>
       <c r="B30" t="n">
-        <v>78523</v>
+        <v>78527</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>128103846</v>
       </c>
       <c r="B31" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         <v>128103865</v>
       </c>
       <c r="B32" t="n">
-        <v>80260</v>
+        <v>80264</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>128103710</v>
       </c>
       <c r="B33" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>128103798</v>
       </c>
       <c r="B34" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>128103799</v>
       </c>
       <c r="B35" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>128103816</v>
       </c>
       <c r="B36" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>128103789</v>
       </c>
       <c r="B37" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>128103749</v>
       </c>
       <c r="B38" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>128103800</v>
       </c>
       <c r="B39" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>128103709</v>
       </c>
       <c r="B40" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>128103776</v>
       </c>
       <c r="B41" t="n">
-        <v>80261</v>
+        <v>80265</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>128103841</v>
       </c>
       <c r="B42" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>128103847</v>
       </c>
       <c r="B43" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>128103732</v>
       </c>
       <c r="B44" t="n">
-        <v>98653</v>
+        <v>98657</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>128103707</v>
       </c>
       <c r="B45" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         <v>128103708</v>
       </c>
       <c r="B46" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>128103804</v>
       </c>
       <c r="B47" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>128103802</v>
       </c>
       <c r="B48" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>128103840</v>
       </c>
       <c r="B49" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>128103790</v>
       </c>
       <c r="B50" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>128103848</v>
       </c>
       <c r="B51" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>128103796</v>
       </c>
       <c r="B52" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>128103797</v>
       </c>
       <c r="B53" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>128103726</v>
       </c>
       <c r="B54" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         <v>128103849</v>
       </c>
       <c r="B55" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>128103779</v>
       </c>
       <c r="B56" t="n">
-        <v>80261</v>
+        <v>80265</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>128103855</v>
       </c>
       <c r="B57" t="n">
-        <v>82979</v>
+        <v>82983</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>128103713</v>
       </c>
       <c r="B58" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>128103818</v>
       </c>
       <c r="B59" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128103750</v>
       </c>
       <c r="B2" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128103748</v>
       </c>
       <c r="B3" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>128103715</v>
       </c>
       <c r="B4" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>128103712</v>
       </c>
       <c r="B5" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>128103821</v>
       </c>
       <c r="B6" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>128103815</v>
       </c>
       <c r="B7" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>128103803</v>
       </c>
       <c r="B8" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>128103861</v>
       </c>
       <c r="B9" t="n">
-        <v>92082</v>
+        <v>92087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>128103760</v>
       </c>
       <c r="B10" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>128103778</v>
       </c>
       <c r="B11" t="n">
-        <v>80265</v>
+        <v>80170</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>128103854</v>
       </c>
       <c r="B12" t="n">
-        <v>82983</v>
+        <v>82892</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>128103814</v>
       </c>
       <c r="B13" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>128103795</v>
       </c>
       <c r="B14" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>128103738</v>
       </c>
       <c r="B15" t="n">
-        <v>80230</v>
+        <v>80135</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>128103747</v>
       </c>
       <c r="B16" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>128103777</v>
       </c>
       <c r="B17" t="n">
-        <v>80265</v>
+        <v>80170</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>128103714</v>
       </c>
       <c r="B18" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>128103820</v>
       </c>
       <c r="B19" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>128103752</v>
       </c>
       <c r="B20" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>128103817</v>
       </c>
       <c r="B21" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>128103780</v>
       </c>
       <c r="B22" t="n">
-        <v>80265</v>
+        <v>80170</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>128103775</v>
       </c>
       <c r="B23" t="n">
-        <v>80265</v>
+        <v>80170</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>128103805</v>
       </c>
       <c r="B24" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>128103693</v>
       </c>
       <c r="B25" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>128103691</v>
       </c>
       <c r="B26" t="n">
-        <v>79156</v>
+        <v>79061</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>128103864</v>
       </c>
       <c r="B27" t="n">
-        <v>80264</v>
+        <v>80169</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>128103751</v>
       </c>
       <c r="B28" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>128103862</v>
       </c>
       <c r="B29" t="n">
-        <v>80264</v>
+        <v>80169</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>128103873</v>
       </c>
       <c r="B30" t="n">
-        <v>78527</v>
+        <v>78432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>128103846</v>
       </c>
       <c r="B31" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         <v>128103865</v>
       </c>
       <c r="B32" t="n">
-        <v>80264</v>
+        <v>80169</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>128103710</v>
       </c>
       <c r="B33" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>128103798</v>
       </c>
       <c r="B34" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>128103799</v>
       </c>
       <c r="B35" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>128103816</v>
       </c>
       <c r="B36" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>128103789</v>
       </c>
       <c r="B37" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>128103749</v>
       </c>
       <c r="B38" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>128103800</v>
       </c>
       <c r="B39" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>128103709</v>
       </c>
       <c r="B40" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>128103776</v>
       </c>
       <c r="B41" t="n">
-        <v>80265</v>
+        <v>80170</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>128103841</v>
       </c>
       <c r="B42" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>128103847</v>
       </c>
       <c r="B43" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>128103732</v>
       </c>
       <c r="B44" t="n">
-        <v>98657</v>
+        <v>98664</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>128103707</v>
       </c>
       <c r="B45" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         <v>128103708</v>
       </c>
       <c r="B46" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>128103804</v>
       </c>
       <c r="B47" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>128103802</v>
       </c>
       <c r="B48" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>128103840</v>
       </c>
       <c r="B49" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>128103790</v>
       </c>
       <c r="B50" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>128103848</v>
       </c>
       <c r="B51" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>128103796</v>
       </c>
       <c r="B52" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>128103797</v>
       </c>
       <c r="B53" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>128103726</v>
       </c>
       <c r="B54" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         <v>128103849</v>
       </c>
       <c r="B55" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>128103779</v>
       </c>
       <c r="B56" t="n">
-        <v>80265</v>
+        <v>80170</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>128103855</v>
       </c>
       <c r="B57" t="n">
-        <v>82983</v>
+        <v>82892</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>128103713</v>
       </c>
       <c r="B58" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>128103818</v>
       </c>
       <c r="B59" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -1108,7 +1108,7 @@
         <v>128103821</v>
       </c>
       <c r="B6" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>128103815</v>
       </c>
       <c r="B7" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>128103803</v>
       </c>
       <c r="B8" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>128103861</v>
       </c>
       <c r="B9" t="n">
-        <v>92095</v>
+        <v>92100</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>128103814</v>
       </c>
       <c r="B13" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>128103795</v>
       </c>
       <c r="B14" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>128103820</v>
       </c>
       <c r="B19" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>128103817</v>
       </c>
       <c r="B21" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>128103805</v>
       </c>
       <c r="B24" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>128103798</v>
       </c>
       <c r="B34" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>128103799</v>
       </c>
       <c r="B35" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>128103816</v>
       </c>
       <c r="B36" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>128103800</v>
       </c>
       <c r="B39" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>128103732</v>
       </c>
       <c r="B44" t="n">
-        <v>98672</v>
+        <v>98677</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>128103804</v>
       </c>
       <c r="B47" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>128103802</v>
       </c>
       <c r="B48" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>128103796</v>
       </c>
       <c r="B52" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>128103797</v>
       </c>
       <c r="B53" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>128103818</v>
       </c>
       <c r="B59" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128103750</v>
       </c>
       <c r="B2" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128103748</v>
       </c>
       <c r="B3" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>128103821</v>
       </c>
       <c r="B6" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>128103815</v>
       </c>
       <c r="B7" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>128103803</v>
       </c>
       <c r="B8" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>128103861</v>
       </c>
       <c r="B9" t="n">
-        <v>92100</v>
+        <v>92103</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>128103760</v>
       </c>
       <c r="B10" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>128103778</v>
       </c>
       <c r="B11" t="n">
-        <v>80175</v>
+        <v>80176</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>128103854</v>
       </c>
       <c r="B12" t="n">
-        <v>82897</v>
+        <v>82898</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>128103814</v>
       </c>
       <c r="B13" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>128103795</v>
       </c>
       <c r="B14" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>128103738</v>
       </c>
       <c r="B15" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>128103747</v>
       </c>
       <c r="B16" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>128103777</v>
       </c>
       <c r="B17" t="n">
-        <v>80175</v>
+        <v>80176</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>128103820</v>
       </c>
       <c r="B19" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>128103752</v>
       </c>
       <c r="B20" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>128103817</v>
       </c>
       <c r="B21" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>128103780</v>
       </c>
       <c r="B22" t="n">
-        <v>80175</v>
+        <v>80176</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>128103775</v>
       </c>
       <c r="B23" t="n">
-        <v>80175</v>
+        <v>80176</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>128103805</v>
       </c>
       <c r="B24" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>128103693</v>
       </c>
       <c r="B25" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>128103691</v>
       </c>
       <c r="B26" t="n">
-        <v>79066</v>
+        <v>79067</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>128103864</v>
       </c>
       <c r="B27" t="n">
-        <v>80174</v>
+        <v>80175</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>128103751</v>
       </c>
       <c r="B28" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>128103862</v>
       </c>
       <c r="B29" t="n">
-        <v>80174</v>
+        <v>80175</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>128103873</v>
       </c>
       <c r="B30" t="n">
-        <v>78437</v>
+        <v>78438</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>128103846</v>
       </c>
       <c r="B31" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         <v>128103865</v>
       </c>
       <c r="B32" t="n">
-        <v>80174</v>
+        <v>80175</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>128103798</v>
       </c>
       <c r="B34" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>128103799</v>
       </c>
       <c r="B35" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>128103816</v>
       </c>
       <c r="B36" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>128103789</v>
       </c>
       <c r="B37" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>128103749</v>
       </c>
       <c r="B38" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>128103800</v>
       </c>
       <c r="B39" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>128103776</v>
       </c>
       <c r="B41" t="n">
-        <v>80175</v>
+        <v>80176</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>128103841</v>
       </c>
       <c r="B42" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>128103847</v>
       </c>
       <c r="B43" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>128103732</v>
       </c>
       <c r="B44" t="n">
-        <v>98677</v>
+        <v>98680</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>128103804</v>
       </c>
       <c r="B47" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>128103802</v>
       </c>
       <c r="B48" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>128103840</v>
       </c>
       <c r="B49" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>128103790</v>
       </c>
       <c r="B50" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>128103848</v>
       </c>
       <c r="B51" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>128103796</v>
       </c>
       <c r="B52" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>128103797</v>
       </c>
       <c r="B53" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>128103726</v>
       </c>
       <c r="B54" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         <v>128103849</v>
       </c>
       <c r="B55" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>128103779</v>
       </c>
       <c r="B56" t="n">
-        <v>80175</v>
+        <v>80176</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>128103855</v>
       </c>
       <c r="B57" t="n">
-        <v>82897</v>
+        <v>82898</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>128103818</v>
       </c>
       <c r="B59" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128103750</v>
       </c>
       <c r="B2" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128103748</v>
       </c>
       <c r="B3" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>128103715</v>
       </c>
       <c r="B4" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>128103712</v>
       </c>
       <c r="B5" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>128103821</v>
       </c>
       <c r="B6" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>128103815</v>
       </c>
       <c r="B7" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>128103803</v>
       </c>
       <c r="B8" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>128103861</v>
       </c>
       <c r="B9" t="n">
-        <v>92103</v>
+        <v>92110</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>128103760</v>
       </c>
       <c r="B10" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>128103778</v>
       </c>
       <c r="B11" t="n">
-        <v>80176</v>
+        <v>80180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>128103854</v>
       </c>
       <c r="B12" t="n">
-        <v>82898</v>
+        <v>82902</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>128103814</v>
       </c>
       <c r="B13" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>128103795</v>
       </c>
       <c r="B14" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>128103738</v>
       </c>
       <c r="B15" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>128103747</v>
       </c>
       <c r="B16" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>128103777</v>
       </c>
       <c r="B17" t="n">
-        <v>80176</v>
+        <v>80180</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>128103714</v>
       </c>
       <c r="B18" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>128103820</v>
       </c>
       <c r="B19" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>128103752</v>
       </c>
       <c r="B20" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>128103817</v>
       </c>
       <c r="B21" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>128103780</v>
       </c>
       <c r="B22" t="n">
-        <v>80176</v>
+        <v>80180</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>128103775</v>
       </c>
       <c r="B23" t="n">
-        <v>80176</v>
+        <v>80180</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>128103805</v>
       </c>
       <c r="B24" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>128103693</v>
       </c>
       <c r="B25" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>128103691</v>
       </c>
       <c r="B26" t="n">
-        <v>79067</v>
+        <v>79071</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>128103864</v>
       </c>
       <c r="B27" t="n">
-        <v>80175</v>
+        <v>80179</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>128103751</v>
       </c>
       <c r="B28" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>128103862</v>
       </c>
       <c r="B29" t="n">
-        <v>80175</v>
+        <v>80179</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>128103873</v>
       </c>
       <c r="B30" t="n">
-        <v>78438</v>
+        <v>78442</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>128103846</v>
       </c>
       <c r="B31" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         <v>128103865</v>
       </c>
       <c r="B32" t="n">
-        <v>80175</v>
+        <v>80179</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>128103710</v>
       </c>
       <c r="B33" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>128103798</v>
       </c>
       <c r="B34" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>128103799</v>
       </c>
       <c r="B35" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>128103816</v>
       </c>
       <c r="B36" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>128103789</v>
       </c>
       <c r="B37" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>128103749</v>
       </c>
       <c r="B38" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>128103800</v>
       </c>
       <c r="B39" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>128103709</v>
       </c>
       <c r="B40" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>128103776</v>
       </c>
       <c r="B41" t="n">
-        <v>80176</v>
+        <v>80180</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>128103841</v>
       </c>
       <c r="B42" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>128103847</v>
       </c>
       <c r="B43" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>128103732</v>
       </c>
       <c r="B44" t="n">
-        <v>98680</v>
+        <v>98690</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>128103707</v>
       </c>
       <c r="B45" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         <v>128103708</v>
       </c>
       <c r="B46" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>128103804</v>
       </c>
       <c r="B47" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>128103802</v>
       </c>
       <c r="B48" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>128103840</v>
       </c>
       <c r="B49" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>128103790</v>
       </c>
       <c r="B50" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>128103848</v>
       </c>
       <c r="B51" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>128103796</v>
       </c>
       <c r="B52" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>128103797</v>
       </c>
       <c r="B53" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>128103726</v>
       </c>
       <c r="B54" t="n">
-        <v>80169</v>
+        <v>80173</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         <v>128103849</v>
       </c>
       <c r="B55" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>128103779</v>
       </c>
       <c r="B56" t="n">
-        <v>80176</v>
+        <v>80180</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>128103855</v>
       </c>
       <c r="B57" t="n">
-        <v>82898</v>
+        <v>82902</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>128103713</v>
       </c>
       <c r="B58" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>128103818</v>
       </c>
       <c r="B59" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -1108,7 +1108,7 @@
         <v>128103821</v>
       </c>
       <c r="B6" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>128103815</v>
       </c>
       <c r="B7" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>128103803</v>
       </c>
       <c r="B8" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>128103861</v>
       </c>
       <c r="B9" t="n">
-        <v>92110</v>
+        <v>92117</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>128103854</v>
       </c>
       <c r="B12" t="n">
-        <v>82902</v>
+        <v>82871</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>128103814</v>
       </c>
       <c r="B13" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>128103795</v>
       </c>
       <c r="B14" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>128103820</v>
       </c>
       <c r="B19" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>128103817</v>
       </c>
       <c r="B21" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>128103805</v>
       </c>
       <c r="B24" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>128103798</v>
       </c>
       <c r="B34" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>128103799</v>
       </c>
       <c r="B35" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>128103816</v>
       </c>
       <c r="B36" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>128103800</v>
       </c>
       <c r="B39" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>128103732</v>
       </c>
       <c r="B44" t="n">
-        <v>98690</v>
+        <v>98697</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>128103804</v>
       </c>
       <c r="B47" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>128103802</v>
       </c>
       <c r="B48" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>128103796</v>
       </c>
       <c r="B52" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>128103797</v>
       </c>
       <c r="B53" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>128103855</v>
       </c>
       <c r="B57" t="n">
-        <v>82902</v>
+        <v>82871</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>128103818</v>
       </c>
       <c r="B59" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128103750</v>
       </c>
       <c r="B2" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128103748</v>
       </c>
       <c r="B3" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>128103715</v>
       </c>
       <c r="B4" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>128103712</v>
       </c>
       <c r="B5" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>128103821</v>
       </c>
       <c r="B6" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>128103815</v>
       </c>
       <c r="B7" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>128103803</v>
       </c>
       <c r="B8" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>128103861</v>
       </c>
       <c r="B9" t="n">
-        <v>92117</v>
+        <v>92119</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>128103760</v>
       </c>
       <c r="B10" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>128103778</v>
       </c>
       <c r="B11" t="n">
-        <v>80180</v>
+        <v>80182</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>128103854</v>
       </c>
       <c r="B12" t="n">
-        <v>82871</v>
+        <v>82873</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>128103814</v>
       </c>
       <c r="B13" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>128103795</v>
       </c>
       <c r="B14" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>128103738</v>
       </c>
       <c r="B15" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>128103747</v>
       </c>
       <c r="B16" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>128103777</v>
       </c>
       <c r="B17" t="n">
-        <v>80180</v>
+        <v>80182</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>128103714</v>
       </c>
       <c r="B18" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>128103820</v>
       </c>
       <c r="B19" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>128103752</v>
       </c>
       <c r="B20" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>128103817</v>
       </c>
       <c r="B21" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>128103780</v>
       </c>
       <c r="B22" t="n">
-        <v>80180</v>
+        <v>80182</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>128103775</v>
       </c>
       <c r="B23" t="n">
-        <v>80180</v>
+        <v>80182</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>128103805</v>
       </c>
       <c r="B24" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>128103693</v>
       </c>
       <c r="B25" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>128103691</v>
       </c>
       <c r="B26" t="n">
-        <v>79071</v>
+        <v>79073</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>128103864</v>
       </c>
       <c r="B27" t="n">
-        <v>80179</v>
+        <v>80181</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>128103751</v>
       </c>
       <c r="B28" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>128103862</v>
       </c>
       <c r="B29" t="n">
-        <v>80179</v>
+        <v>80181</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>128103873</v>
       </c>
       <c r="B30" t="n">
-        <v>78442</v>
+        <v>78444</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>128103846</v>
       </c>
       <c r="B31" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         <v>128103865</v>
       </c>
       <c r="B32" t="n">
-        <v>80179</v>
+        <v>80181</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>128103710</v>
       </c>
       <c r="B33" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>128103798</v>
       </c>
       <c r="B34" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>128103799</v>
       </c>
       <c r="B35" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>128103816</v>
       </c>
       <c r="B36" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>128103789</v>
       </c>
       <c r="B37" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>128103749</v>
       </c>
       <c r="B38" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>128103800</v>
       </c>
       <c r="B39" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>128103709</v>
       </c>
       <c r="B40" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>128103776</v>
       </c>
       <c r="B41" t="n">
-        <v>80180</v>
+        <v>80182</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>128103841</v>
       </c>
       <c r="B42" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>128103847</v>
       </c>
       <c r="B43" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>128103732</v>
       </c>
       <c r="B44" t="n">
-        <v>98697</v>
+        <v>98699</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>128103707</v>
       </c>
       <c r="B45" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         <v>128103708</v>
       </c>
       <c r="B46" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>128103804</v>
       </c>
       <c r="B47" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>128103802</v>
       </c>
       <c r="B48" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>128103840</v>
       </c>
       <c r="B49" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>128103790</v>
       </c>
       <c r="B50" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>128103848</v>
       </c>
       <c r="B51" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>128103796</v>
       </c>
       <c r="B52" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>128103797</v>
       </c>
       <c r="B53" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>128103726</v>
       </c>
       <c r="B54" t="n">
-        <v>80173</v>
+        <v>80175</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         <v>128103849</v>
       </c>
       <c r="B55" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>128103779</v>
       </c>
       <c r="B56" t="n">
-        <v>80180</v>
+        <v>80182</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>128103855</v>
       </c>
       <c r="B57" t="n">
-        <v>82871</v>
+        <v>82873</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>128103713</v>
       </c>
       <c r="B58" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>128103818</v>
       </c>
       <c r="B59" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -1108,7 +1108,7 @@
         <v>128103821</v>
       </c>
       <c r="B6" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>128103815</v>
       </c>
       <c r="B7" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>128103803</v>
       </c>
       <c r="B8" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>128103861</v>
       </c>
       <c r="B9" t="n">
-        <v>92119</v>
+        <v>92134</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>128103814</v>
       </c>
       <c r="B13" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>128103795</v>
       </c>
       <c r="B14" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>128103820</v>
       </c>
       <c r="B19" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>128103817</v>
       </c>
       <c r="B21" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>128103805</v>
       </c>
       <c r="B24" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>128103798</v>
       </c>
       <c r="B34" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>128103799</v>
       </c>
       <c r="B35" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>128103816</v>
       </c>
       <c r="B36" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>128103800</v>
       </c>
       <c r="B39" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>128103732</v>
       </c>
       <c r="B44" t="n">
-        <v>98699</v>
+        <v>98725</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>128103804</v>
       </c>
       <c r="B47" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>128103802</v>
       </c>
       <c r="B48" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>128103796</v>
       </c>
       <c r="B52" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>128103797</v>
       </c>
       <c r="B53" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>128103818</v>
       </c>
       <c r="B59" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -1108,7 +1108,7 @@
         <v>128103821</v>
       </c>
       <c r="B6" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>128103815</v>
       </c>
       <c r="B7" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>128103803</v>
       </c>
       <c r="B8" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>128103861</v>
       </c>
       <c r="B9" t="n">
-        <v>92134</v>
+        <v>92135</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>128103814</v>
       </c>
       <c r="B13" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>128103795</v>
       </c>
       <c r="B14" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>128103820</v>
       </c>
       <c r="B19" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>128103817</v>
       </c>
       <c r="B21" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>128103805</v>
       </c>
       <c r="B24" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>128103798</v>
       </c>
       <c r="B34" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>128103799</v>
       </c>
       <c r="B35" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>128103816</v>
       </c>
       <c r="B36" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>128103800</v>
       </c>
       <c r="B39" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>128103732</v>
       </c>
       <c r="B44" t="n">
-        <v>98725</v>
+        <v>98726</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>128103804</v>
       </c>
       <c r="B47" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>128103802</v>
       </c>
       <c r="B48" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>128103796</v>
       </c>
       <c r="B52" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>128103797</v>
       </c>
       <c r="B53" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>128103818</v>
       </c>
       <c r="B59" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -1108,7 +1108,7 @@
         <v>128103821</v>
       </c>
       <c r="B6" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>128103815</v>
       </c>
       <c r="B7" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>128103803</v>
       </c>
       <c r="B8" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>128103814</v>
       </c>
       <c r="B13" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>128103795</v>
       </c>
       <c r="B14" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>128103820</v>
       </c>
       <c r="B19" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>128103817</v>
       </c>
       <c r="B21" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>128103805</v>
       </c>
       <c r="B24" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>128103798</v>
       </c>
       <c r="B34" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>128103799</v>
       </c>
       <c r="B35" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>128103816</v>
       </c>
       <c r="B36" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>128103800</v>
       </c>
       <c r="B39" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>128103732</v>
       </c>
       <c r="B44" t="n">
-        <v>98726</v>
+        <v>98727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>128103804</v>
       </c>
       <c r="B47" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>128103802</v>
       </c>
       <c r="B48" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>128103796</v>
       </c>
       <c r="B52" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>128103797</v>
       </c>
       <c r="B53" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>128103818</v>
       </c>
       <c r="B59" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128103750</v>
       </c>
       <c r="B2" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128103748</v>
       </c>
       <c r="B3" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>128103821</v>
       </c>
       <c r="B6" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>128103815</v>
       </c>
       <c r="B7" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>128103803</v>
       </c>
       <c r="B8" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>128103861</v>
       </c>
       <c r="B9" t="n">
-        <v>92135</v>
+        <v>92138</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>128103760</v>
       </c>
       <c r="B10" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>128103778</v>
       </c>
       <c r="B11" t="n">
-        <v>80182</v>
+        <v>80184</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>128103854</v>
       </c>
       <c r="B12" t="n">
-        <v>82873</v>
+        <v>82877</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>128103814</v>
       </c>
       <c r="B13" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>128103795</v>
       </c>
       <c r="B14" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>128103738</v>
       </c>
       <c r="B15" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>128103747</v>
       </c>
       <c r="B16" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>128103777</v>
       </c>
       <c r="B17" t="n">
-        <v>80182</v>
+        <v>80184</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>128103820</v>
       </c>
       <c r="B19" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>128103752</v>
       </c>
       <c r="B20" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>128103817</v>
       </c>
       <c r="B21" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>128103780</v>
       </c>
       <c r="B22" t="n">
-        <v>80182</v>
+        <v>80184</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>128103775</v>
       </c>
       <c r="B23" t="n">
-        <v>80182</v>
+        <v>80184</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>128103805</v>
       </c>
       <c r="B24" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>128103693</v>
       </c>
       <c r="B25" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>128103691</v>
       </c>
       <c r="B26" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>128103864</v>
       </c>
       <c r="B27" t="n">
-        <v>80181</v>
+        <v>80183</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>128103751</v>
       </c>
       <c r="B28" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>128103862</v>
       </c>
       <c r="B29" t="n">
-        <v>80181</v>
+        <v>80183</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>128103873</v>
       </c>
       <c r="B30" t="n">
-        <v>78444</v>
+        <v>78446</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>128103846</v>
       </c>
       <c r="B31" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         <v>128103865</v>
       </c>
       <c r="B32" t="n">
-        <v>80181</v>
+        <v>80183</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>128103798</v>
       </c>
       <c r="B34" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>128103799</v>
       </c>
       <c r="B35" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>128103816</v>
       </c>
       <c r="B36" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>128103789</v>
       </c>
       <c r="B37" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>128103749</v>
       </c>
       <c r="B38" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>128103800</v>
       </c>
       <c r="B39" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>128103776</v>
       </c>
       <c r="B41" t="n">
-        <v>80182</v>
+        <v>80184</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>128103841</v>
       </c>
       <c r="B42" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>128103847</v>
       </c>
       <c r="B43" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>128103732</v>
       </c>
       <c r="B44" t="n">
-        <v>98727</v>
+        <v>98731</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>128103804</v>
       </c>
       <c r="B47" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>128103802</v>
       </c>
       <c r="B48" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>128103840</v>
       </c>
       <c r="B49" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>128103790</v>
       </c>
       <c r="B50" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>128103848</v>
       </c>
       <c r="B51" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>128103796</v>
       </c>
       <c r="B52" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>128103797</v>
       </c>
       <c r="B53" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>128103726</v>
       </c>
       <c r="B54" t="n">
-        <v>80175</v>
+        <v>80177</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         <v>128103849</v>
       </c>
       <c r="B55" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>128103779</v>
       </c>
       <c r="B56" t="n">
-        <v>80182</v>
+        <v>80184</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>128103855</v>
       </c>
       <c r="B57" t="n">
-        <v>82873</v>
+        <v>82877</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>128103818</v>
       </c>
       <c r="B59" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128103750</v>
       </c>
       <c r="B2" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128103748</v>
       </c>
       <c r="B3" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>128103821</v>
       </c>
       <c r="B6" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>128103815</v>
       </c>
       <c r="B7" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>128103803</v>
       </c>
       <c r="B8" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>128103861</v>
       </c>
       <c r="B9" t="n">
-        <v>92138</v>
+        <v>92140</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>128103760</v>
       </c>
       <c r="B10" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>128103778</v>
       </c>
       <c r="B11" t="n">
-        <v>80184</v>
+        <v>80185</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>128103854</v>
       </c>
       <c r="B12" t="n">
-        <v>82877</v>
+        <v>82878</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>128103814</v>
       </c>
       <c r="B13" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>128103795</v>
       </c>
       <c r="B14" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>128103738</v>
       </c>
       <c r="B15" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>128103747</v>
       </c>
       <c r="B16" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>128103777</v>
       </c>
       <c r="B17" t="n">
-        <v>80184</v>
+        <v>80185</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>128103820</v>
       </c>
       <c r="B19" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>128103752</v>
       </c>
       <c r="B20" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>128103817</v>
       </c>
       <c r="B21" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>128103780</v>
       </c>
       <c r="B22" t="n">
-        <v>80184</v>
+        <v>80185</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>128103775</v>
       </c>
       <c r="B23" t="n">
-        <v>80184</v>
+        <v>80185</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>128103805</v>
       </c>
       <c r="B24" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>128103693</v>
       </c>
       <c r="B25" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>128103691</v>
       </c>
       <c r="B26" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>128103864</v>
       </c>
       <c r="B27" t="n">
-        <v>80183</v>
+        <v>80184</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>128103751</v>
       </c>
       <c r="B28" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>128103862</v>
       </c>
       <c r="B29" t="n">
-        <v>80183</v>
+        <v>80184</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>128103873</v>
       </c>
       <c r="B30" t="n">
-        <v>78446</v>
+        <v>78447</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>128103846</v>
       </c>
       <c r="B31" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         <v>128103865</v>
       </c>
       <c r="B32" t="n">
-        <v>80183</v>
+        <v>80184</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>128103798</v>
       </c>
       <c r="B34" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>128103799</v>
       </c>
       <c r="B35" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>128103816</v>
       </c>
       <c r="B36" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>128103789</v>
       </c>
       <c r="B37" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>128103749</v>
       </c>
       <c r="B38" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>128103800</v>
       </c>
       <c r="B39" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>128103776</v>
       </c>
       <c r="B41" t="n">
-        <v>80184</v>
+        <v>80185</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>128103841</v>
       </c>
       <c r="B42" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>128103847</v>
       </c>
       <c r="B43" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>128103732</v>
       </c>
       <c r="B44" t="n">
-        <v>98731</v>
+        <v>98733</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>128103804</v>
       </c>
       <c r="B47" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>128103802</v>
       </c>
       <c r="B48" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>128103840</v>
       </c>
       <c r="B49" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>128103790</v>
       </c>
       <c r="B50" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>128103848</v>
       </c>
       <c r="B51" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>128103796</v>
       </c>
       <c r="B52" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>128103797</v>
       </c>
       <c r="B53" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>128103726</v>
       </c>
       <c r="B54" t="n">
-        <v>80177</v>
+        <v>80178</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         <v>128103849</v>
       </c>
       <c r="B55" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>128103779</v>
       </c>
       <c r="B56" t="n">
-        <v>80184</v>
+        <v>80185</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>128103855</v>
       </c>
       <c r="B57" t="n">
-        <v>82877</v>
+        <v>82878</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>128103818</v>
       </c>
       <c r="B59" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -1108,7 +1108,7 @@
         <v>128103821</v>
       </c>
       <c r="B6" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>128103815</v>
       </c>
       <c r="B7" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>128103803</v>
       </c>
       <c r="B8" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>128103861</v>
       </c>
       <c r="B9" t="n">
-        <v>92140</v>
+        <v>92144</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>128103814</v>
       </c>
       <c r="B13" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>128103795</v>
       </c>
       <c r="B14" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>128103820</v>
       </c>
       <c r="B19" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>128103817</v>
       </c>
       <c r="B21" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>128103805</v>
       </c>
       <c r="B24" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>128103798</v>
       </c>
       <c r="B34" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>128103799</v>
       </c>
       <c r="B35" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>128103816</v>
       </c>
       <c r="B36" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>128103800</v>
       </c>
       <c r="B39" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>128103732</v>
       </c>
       <c r="B44" t="n">
-        <v>98733</v>
+        <v>98737</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>128103804</v>
       </c>
       <c r="B47" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>128103802</v>
       </c>
       <c r="B48" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>128103796</v>
       </c>
       <c r="B52" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>128103797</v>
       </c>
       <c r="B53" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>128103818</v>
       </c>
       <c r="B59" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY59"/>
+  <dimension ref="A1:AY64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6645,6 +6645,491 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>134317523</v>
+      </c>
+      <c r="B60" t="n">
+        <v>83208</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Sågmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>626706</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7217224</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>134317476</v>
+      </c>
+      <c r="B61" t="n">
+        <v>80475</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Sågmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>626694</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7217205</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>134317474</v>
+      </c>
+      <c r="B62" t="n">
+        <v>80475</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Sågmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>626814</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7216995</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>134317513</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99180</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Sågmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>626718</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7217256</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>134317472</v>
+      </c>
+      <c r="B64" t="n">
+        <v>80474</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Sågmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>626814</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7216995</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -6648,10 +6648,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>134317523</v>
+        <v>134317476</v>
       </c>
       <c r="B60" t="n">
-        <v>83208</v>
+        <v>80475</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6659,21 +6659,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6683,10 +6683,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>626706</v>
+        <v>626694</v>
       </c>
       <c r="R60" t="n">
-        <v>7217224</v>
+        <v>7217205</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6745,10 +6745,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>134317476</v>
+        <v>134317523</v>
       </c>
       <c r="B61" t="n">
-        <v>80475</v>
+        <v>83208</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6756,21 +6756,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6780,10 +6780,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>626694</v>
+        <v>626706</v>
       </c>
       <c r="R61" t="n">
-        <v>7217205</v>
+        <v>7217224</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>

--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -6648,10 +6648,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>134317523</v>
+        <v>134317476</v>
       </c>
       <c r="B60" t="n">
-        <v>83208</v>
+        <v>80482</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6659,21 +6659,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6683,10 +6683,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>626706</v>
+        <v>626694</v>
       </c>
       <c r="R60" t="n">
-        <v>7217224</v>
+        <v>7217205</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6745,10 +6745,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>134317476</v>
+        <v>134317523</v>
       </c>
       <c r="B61" t="n">
-        <v>80475</v>
+        <v>83215</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6756,21 +6756,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6780,10 +6780,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>626694</v>
+        <v>626706</v>
       </c>
       <c r="R61" t="n">
-        <v>7217205</v>
+        <v>7217224</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6845,7 +6845,7 @@
         <v>134317474</v>
       </c>
       <c r="B62" t="n">
-        <v>80475</v>
+        <v>80482</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6942,7 +6942,7 @@
         <v>134317513</v>
       </c>
       <c r="B63" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
         <v>134317472</v>
       </c>
       <c r="B64" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 36708-2025 artfynd.xlsx
+++ b/artfynd/A 36708-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128103750</v>
+        <v>128103691</v>
       </c>
       <c r="B2" t="n">
-        <v>80149</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626688</v>
+        <v>626657</v>
       </c>
       <c r="R2" t="n">
-        <v>7217164</v>
+        <v>7217200</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128103748</v>
+        <v>128103861</v>
       </c>
       <c r="B3" t="n">
-        <v>80149</v>
+        <v>92509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626663</v>
+        <v>626733</v>
       </c>
       <c r="R3" t="n">
-        <v>7217050</v>
+        <v>7217284</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -849,12 +849,18 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Bild</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -877,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128103715</v>
+        <v>128103854</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,42 +894,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626715</v>
+        <v>626665</v>
       </c>
       <c r="R4" t="n">
-        <v>7217390</v>
+        <v>7217212</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -956,11 +954,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färsk</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +984,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128103712</v>
+        <v>128103855</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,42 +995,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626667</v>
+        <v>626723</v>
       </c>
       <c r="R5" t="n">
-        <v>7217072</v>
+        <v>7217326</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,11 +1055,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Bohål</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,45 +1085,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128103821</v>
+        <v>134317523</v>
       </c>
       <c r="B6" t="n">
-        <v>98716</v>
+        <v>83222</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Burmyrhobben, Ly lm</t>
+          <t>Sågmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626754</v>
+        <v>626706</v>
       </c>
       <c r="R6" t="n">
-        <v>7217270</v>
+        <v>7217224</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,12 +1150,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,48 +1170,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128103815</v>
+        <v>128103738</v>
       </c>
       <c r="B7" t="n">
-        <v>98716</v>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1241,10 +1217,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626821</v>
+        <v>626739</v>
       </c>
       <c r="R7" t="n">
-        <v>7217074</v>
+        <v>7217280</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,45 +1283,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128103803</v>
+        <v>134317474</v>
       </c>
       <c r="B8" t="n">
-        <v>98716</v>
+        <v>80489</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Burmyrhobben, Ly lm</t>
+          <t>Sågmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626709</v>
+        <v>626814</v>
       </c>
       <c r="R8" t="n">
-        <v>7217057</v>
+        <v>7216995</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,12 +1348,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1392,61 +1368,57 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128103861</v>
+        <v>134317476</v>
       </c>
       <c r="B9" t="n">
-        <v>92144</v>
+        <v>80489</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Burmyrhobben, Ly lm</t>
+          <t>Sågmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626733</v>
+        <v>626694</v>
       </c>
       <c r="R9" t="n">
-        <v>7217284</v>
+        <v>7217205</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1473,17 +1445,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Bild</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1492,55 +1459,50 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128103760</v>
+        <v>128103840</v>
       </c>
       <c r="B10" t="n">
-        <v>80149</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1550,10 +1512,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626697</v>
+        <v>626757</v>
       </c>
       <c r="R10" t="n">
-        <v>7217137</v>
+        <v>7217294</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,32 +1578,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128103778</v>
+        <v>128103841</v>
       </c>
       <c r="B11" t="n">
-        <v>80185</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1651,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626745</v>
+        <v>626739</v>
       </c>
       <c r="R11" t="n">
-        <v>7217244</v>
+        <v>7217304</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1717,32 +1679,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128103854</v>
+        <v>128103846</v>
       </c>
       <c r="B12" t="n">
-        <v>82878</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1752,10 +1714,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626665</v>
+        <v>626685</v>
       </c>
       <c r="R12" t="n">
-        <v>7217212</v>
+        <v>7217148</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1818,10 +1780,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128103814</v>
+        <v>128103847</v>
       </c>
       <c r="B13" t="n">
-        <v>98716</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1829,21 +1791,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1853,10 +1815,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626811</v>
+        <v>626677</v>
       </c>
       <c r="R13" t="n">
-        <v>7217114</v>
+        <v>7217181</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1889,6 +1851,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1919,10 +1886,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128103795</v>
+        <v>128103848</v>
       </c>
       <c r="B14" t="n">
-        <v>98716</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1930,21 +1897,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1921,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626797</v>
+        <v>626660</v>
       </c>
       <c r="R14" t="n">
-        <v>7217132</v>
+        <v>7217210</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2020,32 +1987,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128103738</v>
+        <v>128103849</v>
       </c>
       <c r="B15" t="n">
-        <v>80150</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2055,10 +2022,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626739</v>
+        <v>626701</v>
       </c>
       <c r="R15" t="n">
-        <v>7217280</v>
+        <v>7217242</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2121,10 +2088,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128103747</v>
+        <v>128103873</v>
       </c>
       <c r="B16" t="n">
-        <v>80149</v>
+        <v>78730</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2132,21 +2099,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6437</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2156,10 +2123,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626821</v>
+        <v>626652</v>
       </c>
       <c r="R16" t="n">
-        <v>7217089</v>
+        <v>7217184</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2222,32 +2189,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128103777</v>
+        <v>128103789</v>
       </c>
       <c r="B17" t="n">
-        <v>80185</v>
+        <v>79084</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2257,10 +2224,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626745</v>
+        <v>626633</v>
       </c>
       <c r="R17" t="n">
-        <v>7217253</v>
+        <v>7217153</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2323,10 +2290,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128103714</v>
+        <v>128103790</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>79084</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2334,42 +2301,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626724</v>
+        <v>626730</v>
       </c>
       <c r="R18" t="n">
-        <v>7217339</v>
+        <v>7217238</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2402,11 +2361,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2437,32 +2391,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128103820</v>
+        <v>128103693</v>
       </c>
       <c r="B19" t="n">
-        <v>98716</v>
+        <v>79946</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2472,10 +2426,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626749</v>
+        <v>626633</v>
       </c>
       <c r="R19" t="n">
-        <v>7217269</v>
+        <v>7217153</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2538,10 +2492,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128103752</v>
+        <v>128103747</v>
       </c>
       <c r="B20" t="n">
-        <v>80149</v>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2573,10 +2527,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626739</v>
+        <v>626821</v>
       </c>
       <c r="R20" t="n">
-        <v>7217280</v>
+        <v>7217089</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2639,32 +2593,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128103817</v>
+        <v>128103748</v>
       </c>
       <c r="B21" t="n">
-        <v>98716</v>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2674,10 +2628,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626705</v>
+        <v>626663</v>
       </c>
       <c r="R21" t="n">
-        <v>7217045</v>
+        <v>7217050</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2740,32 +2694,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128103780</v>
+        <v>128103749</v>
       </c>
       <c r="B22" t="n">
-        <v>80185</v>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2775,10 +2729,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>626687</v>
+        <v>626686</v>
       </c>
       <c r="R22" t="n">
-        <v>7217145</v>
+        <v>7217075</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2841,32 +2795,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128103775</v>
+        <v>128103750</v>
       </c>
       <c r="B23" t="n">
-        <v>80185</v>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2876,10 +2830,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626673</v>
+        <v>626688</v>
       </c>
       <c r="R23" t="n">
-        <v>7217106</v>
+        <v>7217164</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2942,32 +2896,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128103805</v>
+        <v>128103751</v>
       </c>
       <c r="B24" t="n">
-        <v>98716</v>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2977,10 +2931,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626744</v>
+        <v>626665</v>
       </c>
       <c r="R24" t="n">
-        <v>7217285</v>
+        <v>7217186</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3043,10 +2997,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128103693</v>
+        <v>128103752</v>
       </c>
       <c r="B25" t="n">
-        <v>79663</v>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3054,21 +3008,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3078,10 +3032,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>626633</v>
+        <v>626739</v>
       </c>
       <c r="R25" t="n">
-        <v>7217153</v>
+        <v>7217280</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3144,10 +3098,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128103691</v>
+        <v>128103760</v>
       </c>
       <c r="B26" t="n">
-        <v>79076</v>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3155,21 +3109,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3179,10 +3133,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>626657</v>
+        <v>626697</v>
       </c>
       <c r="R26" t="n">
-        <v>7217200</v>
+        <v>7217137</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3245,45 +3199,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128103864</v>
+        <v>134317472</v>
       </c>
       <c r="B27" t="n">
-        <v>80184</v>
+        <v>80488</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Burmyrhobben, Ly lm</t>
+          <t>Sågmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>626755</v>
+        <v>626814</v>
       </c>
       <c r="R27" t="n">
-        <v>7217274</v>
+        <v>7216995</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3310,12 +3264,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3330,48 +3284,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128103751</v>
+        <v>128103726</v>
       </c>
       <c r="B28" t="n">
-        <v>80149</v>
+        <v>80461</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3381,10 +3331,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>626665</v>
+        <v>626745</v>
       </c>
       <c r="R28" t="n">
-        <v>7217186</v>
+        <v>7217244</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3450,7 +3400,7 @@
         <v>128103862</v>
       </c>
       <c r="B29" t="n">
-        <v>80184</v>
+        <v>80467</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3548,32 +3498,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128103873</v>
+        <v>128103864</v>
       </c>
       <c r="B30" t="n">
-        <v>78447</v>
+        <v>80467</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6437</v>
+        <v>6463</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3583,10 +3533,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>626652</v>
+        <v>626755</v>
       </c>
       <c r="R30" t="n">
-        <v>7217184</v>
+        <v>7217274</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3649,27 +3599,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128103846</v>
+        <v>128103865</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>80467</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3684,10 +3634,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>626685</v>
+        <v>626739</v>
       </c>
       <c r="R31" t="n">
-        <v>7217148</v>
+        <v>7217280</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3750,10 +3700,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128103865</v>
+        <v>128103775</v>
       </c>
       <c r="B32" t="n">
-        <v>80184</v>
+        <v>80468</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3761,21 +3711,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3785,10 +3735,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>626739</v>
+        <v>626673</v>
       </c>
       <c r="R32" t="n">
-        <v>7217280</v>
+        <v>7217106</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3851,53 +3801,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128103710</v>
+        <v>128103776</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>80468</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>626769</v>
+        <v>626665</v>
       </c>
       <c r="R33" t="n">
-        <v>7217062</v>
+        <v>7217186</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3930,11 +3872,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3965,32 +3902,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128103798</v>
+        <v>128103777</v>
       </c>
       <c r="B34" t="n">
-        <v>98716</v>
+        <v>80468</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4000,10 +3937,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>626811</v>
+        <v>626745</v>
       </c>
       <c r="R34" t="n">
-        <v>7217065</v>
+        <v>7217253</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4066,32 +4003,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128103799</v>
+        <v>128103778</v>
       </c>
       <c r="B35" t="n">
-        <v>98716</v>
+        <v>80468</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4101,10 +4038,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>626796</v>
+        <v>626745</v>
       </c>
       <c r="R35" t="n">
-        <v>7217064</v>
+        <v>7217244</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4167,32 +4104,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128103816</v>
+        <v>128103779</v>
       </c>
       <c r="B36" t="n">
-        <v>98716</v>
+        <v>80468</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4202,10 +4139,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>626837</v>
+        <v>626819</v>
       </c>
       <c r="R36" t="n">
-        <v>7217076</v>
+        <v>7217095</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4268,32 +4205,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128103789</v>
+        <v>128103780</v>
       </c>
       <c r="B37" t="n">
-        <v>78801</v>
+        <v>80468</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6464</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4303,10 +4240,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>626633</v>
+        <v>626687</v>
       </c>
       <c r="R37" t="n">
-        <v>7217153</v>
+        <v>7217145</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4369,10 +4306,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128103749</v>
+        <v>128103690</v>
       </c>
       <c r="B38" t="n">
-        <v>80149</v>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4380,34 +4317,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626686</v>
+        <v>626715</v>
       </c>
       <c r="R38" t="n">
-        <v>7217075</v>
+        <v>7217390</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4440,6 +4385,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4470,45 +4420,53 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128103800</v>
+        <v>128103707</v>
       </c>
       <c r="B39" t="n">
-        <v>98716</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626843</v>
+        <v>626786</v>
       </c>
       <c r="R39" t="n">
-        <v>7217062</v>
+        <v>7217295</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4541,6 +4499,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4571,10 +4534,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128103709</v>
+        <v>128103708</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4604,7 +4567,7 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -4614,7 +4577,7 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>626740</v>
+        <v>626743</v>
       </c>
       <c r="R40" t="n">
         <v>7217219</v>
@@ -4654,7 +4617,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4685,45 +4648,53 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128103776</v>
+        <v>128103709</v>
       </c>
       <c r="B41" t="n">
-        <v>80185</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>626665</v>
+        <v>626740</v>
       </c>
       <c r="R41" t="n">
-        <v>7217186</v>
+        <v>7217219</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4756,6 +4727,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4786,10 +4762,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128103841</v>
+        <v>128103710</v>
       </c>
       <c r="B42" t="n">
-        <v>79044</v>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4797,34 +4773,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>626739</v>
+        <v>626769</v>
       </c>
       <c r="R42" t="n">
-        <v>7217304</v>
+        <v>7217062</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4857,6 +4841,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4887,10 +4876,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128103847</v>
+        <v>128103712</v>
       </c>
       <c r="B43" t="n">
-        <v>79044</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4898,34 +4887,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>626677</v>
+        <v>626667</v>
       </c>
       <c r="R43" t="n">
-        <v>7217181</v>
+        <v>7217072</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4962,7 +4959,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Med apothecier</t>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4993,45 +4990,53 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128103732</v>
+        <v>128103713</v>
       </c>
       <c r="B44" t="n">
-        <v>98737</v>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>626665</v>
+        <v>626703</v>
       </c>
       <c r="R44" t="n">
-        <v>7217113</v>
+        <v>7217299</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5064,6 +5069,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5094,10 +5104,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128103707</v>
+        <v>128103714</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5127,7 +5137,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5137,10 +5147,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>626786</v>
+        <v>626724</v>
       </c>
       <c r="R45" t="n">
-        <v>7217295</v>
+        <v>7217339</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5177,7 +5187,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5208,53 +5218,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128103708</v>
+        <v>128103795</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>626743</v>
+        <v>626797</v>
       </c>
       <c r="R46" t="n">
-        <v>7217219</v>
+        <v>7217132</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5287,11 +5289,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Bohål</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5322,10 +5319,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128103804</v>
+        <v>128103796</v>
       </c>
       <c r="B47" t="n">
-        <v>98716</v>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5357,10 +5354,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>626622</v>
+        <v>626803</v>
       </c>
       <c r="R47" t="n">
-        <v>7217121</v>
+        <v>7217099</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5423,10 +5420,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128103802</v>
+        <v>128103797</v>
       </c>
       <c r="B48" t="n">
-        <v>98716</v>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5458,10 +5455,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>626806</v>
+        <v>626820</v>
       </c>
       <c r="R48" t="n">
-        <v>7217042</v>
+        <v>7217037</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5524,32 +5521,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128103840</v>
+        <v>128103798</v>
       </c>
       <c r="B49" t="n">
-        <v>79044</v>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5559,10 +5556,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>626757</v>
+        <v>626811</v>
       </c>
       <c r="R49" t="n">
-        <v>7217294</v>
+        <v>7217065</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5625,32 +5622,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128103790</v>
+        <v>128103799</v>
       </c>
       <c r="B50" t="n">
-        <v>78801</v>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5660,10 +5657,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>626730</v>
+        <v>626796</v>
       </c>
       <c r="R50" t="n">
-        <v>7217238</v>
+        <v>7217064</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5726,32 +5723,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128103848</v>
+        <v>128103800</v>
       </c>
       <c r="B51" t="n">
-        <v>79044</v>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5761,10 +5758,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>626660</v>
+        <v>626843</v>
       </c>
       <c r="R51" t="n">
-        <v>7217210</v>
+        <v>7217062</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5827,10 +5824,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128103796</v>
+        <v>128103802</v>
       </c>
       <c r="B52" t="n">
-        <v>98716</v>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5862,10 +5859,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>626803</v>
+        <v>626806</v>
       </c>
       <c r="R52" t="n">
-        <v>7217099</v>
+        <v>7217042</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5928,10 +5925,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128103797</v>
+        <v>128103803</v>
       </c>
       <c r="B53" t="n">
-        <v>98716</v>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5963,10 +5960,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>626820</v>
+        <v>626709</v>
       </c>
       <c r="R53" t="n">
-        <v>7217037</v>
+        <v>7217057</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6029,32 +6026,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128103726</v>
+        <v>128103804</v>
       </c>
       <c r="B54" t="n">
-        <v>80178</v>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6064,10 +6061,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>626745</v>
+        <v>626622</v>
       </c>
       <c r="R54" t="n">
-        <v>7217244</v>
+        <v>7217121</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6130,32 +6127,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128103849</v>
+        <v>128103805</v>
       </c>
       <c r="B55" t="n">
-        <v>79044</v>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6165,10 +6162,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>626701</v>
+        <v>626744</v>
       </c>
       <c r="R55" t="n">
-        <v>7217242</v>
+        <v>7217285</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6231,32 +6228,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128103779</v>
+        <v>128103814</v>
       </c>
       <c r="B56" t="n">
-        <v>80185</v>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6266,10 +6263,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>626819</v>
+        <v>626811</v>
       </c>
       <c r="R56" t="n">
-        <v>7217095</v>
+        <v>7217114</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6332,32 +6329,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128103855</v>
+        <v>128103815</v>
       </c>
       <c r="B57" t="n">
-        <v>82878</v>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6367,10 +6364,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>626723</v>
+        <v>626821</v>
       </c>
       <c r="R57" t="n">
-        <v>7217326</v>
+        <v>7217074</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6433,53 +6430,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128103713</v>
+        <v>128103816</v>
       </c>
       <c r="B58" t="n">
-        <v>57727</v>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>626703</v>
+        <v>626837</v>
       </c>
       <c r="R58" t="n">
-        <v>7217299</v>
+        <v>7217076</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6512,11 +6501,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6547,10 +6531,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128103818</v>
+        <v>128103817</v>
       </c>
       <c r="B59" t="n">
-        <v>98716</v>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6582,10 +6566,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>626631</v>
+        <v>626705</v>
       </c>
       <c r="R59" t="n">
-        <v>7217081</v>
+        <v>7217045</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6648,45 +6632,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>134317476</v>
+        <v>128103818</v>
       </c>
       <c r="B60" t="n">
-        <v>80482</v>
+        <v>99118</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Sågmyran, Ly lm</t>
+          <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>626694</v>
+        <v>626631</v>
       </c>
       <c r="R60" t="n">
-        <v>7217205</v>
+        <v>7217081</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6713,12 +6697,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6733,57 +6717,61 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>134317523</v>
+        <v>128103820</v>
       </c>
       <c r="B61" t="n">
-        <v>83215</v>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Sågmyran, Ly lm</t>
+          <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>626706</v>
+        <v>626749</v>
       </c>
       <c r="R61" t="n">
-        <v>7217224</v>
+        <v>7217269</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6810,12 +6798,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6830,57 +6818,61 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>134317474</v>
+        <v>128103821</v>
       </c>
       <c r="B62" t="n">
-        <v>80482</v>
+        <v>99118</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sågmyran, Ly lm</t>
+          <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>626814</v>
+        <v>626754</v>
       </c>
       <c r="R62" t="n">
-        <v>7216995</v>
+        <v>7217270</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6907,12 +6899,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6927,22 +6919,26 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
         <v>134317513</v>
       </c>
       <c r="B63" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7036,45 +7032,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>134317472</v>
+        <v>128103732</v>
       </c>
       <c r="B64" t="n">
-        <v>80481</v>
+        <v>99140</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Sågmyran, Ly lm</t>
+          <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>626814</v>
+        <v>626665</v>
       </c>
       <c r="R64" t="n">
-        <v>7216995</v>
+        <v>7217113</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7101,12 +7097,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7121,15 +7117,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
